--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,6 +1044,4357 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129174965</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104124</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>696247</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6617382</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129171407</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>695742</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6617264</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129171403</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100844</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>696219</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6617372</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129171368</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>695888</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6617461</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129171415</v>
+      </c>
+      <c r="B9" t="n">
+        <v>86941</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>696173</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6617344</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129171408</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>695749</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6617315</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129171360</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91488</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>695791</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6617334</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129171392</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>695840</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6617459</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129171404</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>695939</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6617438</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129171374</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>696142</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6617341</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129171405</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>695875</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6617394</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129174970</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>696187</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6617372</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129171373</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>695846</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6617165</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129171402</v>
+      </c>
+      <c r="B18" t="n">
+        <v>88774</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>695905</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6617158</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129171409</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>696020</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6617274</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129171416</v>
+      </c>
+      <c r="B20" t="n">
+        <v>86941</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>696215</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6617356</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129171385</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98690</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>696217</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6617392</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129174973</v>
+      </c>
+      <c r="B22" t="n">
+        <v>75155</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>695810</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6617339</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129174969</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>696014</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6617322</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129171383</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98690</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>695894</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6617351</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129171401</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92852</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>695690</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6617259</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129171386</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58093</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>696062</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6617338</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129171367</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>696155</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6617505</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129174972</v>
+      </c>
+      <c r="B28" t="n">
+        <v>75155</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>695758</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6617314</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129171363</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91523</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>695974</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6617238</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129171395</v>
+      </c>
+      <c r="B30" t="n">
+        <v>87044</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>696012</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6617292</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129171413</v>
+      </c>
+      <c r="B31" t="n">
+        <v>86941</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>695981</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6617228</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129171371</v>
+      </c>
+      <c r="B32" t="n">
+        <v>96002</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>695971</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6617182</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129171414</v>
+      </c>
+      <c r="B33" t="n">
+        <v>86941</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>696014</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6617265</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129171406</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>695870</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6617363</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129171412</v>
+      </c>
+      <c r="B35" t="n">
+        <v>86941</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>695978</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6617179</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129171375</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91296</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>695740</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6617273</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129171391</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>695872</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6617462</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129171394</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90984</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>695956</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6617156</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129171393</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>695996</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6617333</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129171377</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91296</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>696216</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6617354</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129171384</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98690</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>695740</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6617273</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129171411</v>
+      </c>
+      <c r="B42" t="n">
+        <v>86941</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>695740</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6617275</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129171382</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98690</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>695889</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6617161</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129171369</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>695729</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6617282</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129171378</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92808</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>695821</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6617383</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129171417</v>
+      </c>
+      <c r="B46" t="n">
+        <v>86941</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>696217</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6617368</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129171379</v>
+      </c>
+      <c r="B47" t="n">
+        <v>86929</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6003296</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Stor odörspindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius mussivus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>696222</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6617388</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129174965</v>
+        <v>129171415</v>
       </c>
       <c r="B5" t="n">
-        <v>104124</v>
+        <v>86944</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696247</v>
+        <v>696173</v>
       </c>
       <c r="R5" t="n">
-        <v>6617382</v>
+        <v>6617344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,55 +1131,54 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171407</v>
+        <v>129171368</v>
       </c>
       <c r="B6" t="n">
-        <v>8439</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695742</v>
+        <v>695888</v>
       </c>
       <c r="R6" t="n">
-        <v>6617264</v>
+        <v>6617461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1230,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171403</v>
+        <v>129171407</v>
       </c>
       <c r="B7" t="n">
-        <v>100844</v>
+        <v>8439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,34 +1259,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696219</v>
+        <v>695742</v>
       </c>
       <c r="R7" t="n">
-        <v>6617372</v>
+        <v>6617264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,6 +1336,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,53 +1355,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171368</v>
+        <v>129171403</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>100847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695888</v>
+        <v>696219</v>
       </c>
       <c r="R8" t="n">
-        <v>6617461</v>
+        <v>6617372</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171415</v>
+        <v>129174965</v>
       </c>
       <c r="B9" t="n">
-        <v>86941</v>
+        <v>104127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3674</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696173</v>
+        <v>696247</v>
       </c>
       <c r="R9" t="n">
-        <v>6617344</v>
+        <v>6617382</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,12 +1537,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1659,7 +1659,7 @@
         <v>129171360</v>
       </c>
       <c r="B11" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,50 +1753,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171392</v>
+        <v>129171374</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1804,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695840</v>
+        <v>696142</v>
       </c>
       <c r="R12" t="n">
-        <v>6617459</v>
+        <v>6617341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1840,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1867,7 +1858,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171404</v>
+        <v>129171405</v>
       </c>
       <c r="B13" t="n">
         <v>8439</v>
@@ -1911,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695939</v>
+        <v>695875</v>
       </c>
       <c r="R13" t="n">
-        <v>6617438</v>
+        <v>6617394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,40 +1965,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171374</v>
+        <v>129171404</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>8439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2017,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696142</v>
+        <v>695939</v>
       </c>
       <c r="R14" t="n">
-        <v>6617341</v>
+        <v>6617438</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,6 +2053,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2079,43 +2072,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171405</v>
+        <v>129171392</v>
       </c>
       <c r="B15" t="n">
-        <v>8439</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695875</v>
+        <v>695840</v>
       </c>
       <c r="R15" t="n">
-        <v>6617394</v>
+        <v>6617459</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
         <v>129174970</v>
       </c>
       <c r="B16" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,53 +2296,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129171373</v>
+        <v>129171402</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>88777</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>4405</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>695846</v>
+        <v>695905</v>
       </c>
       <c r="R17" t="n">
-        <v>6617165</v>
+        <v>6617158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,45 +2393,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129171402</v>
+        <v>129171373</v>
       </c>
       <c r="B18" t="n">
-        <v>88774</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4405</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695905</v>
+        <v>695846</v>
       </c>
       <c r="R18" t="n">
-        <v>6617158</v>
+        <v>6617165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129171409</v>
+        <v>129171385</v>
       </c>
       <c r="B19" t="n">
-        <v>8439</v>
+        <v>98693</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,43 +2509,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>219874</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696020</v>
+        <v>696217</v>
       </c>
       <c r="R19" t="n">
-        <v>6617274</v>
+        <v>6617392</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,7 +2577,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2608,7 +2598,7 @@
         <v>129171416</v>
       </c>
       <c r="B20" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,10 +2692,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171385</v>
+        <v>129171409</v>
       </c>
       <c r="B21" t="n">
-        <v>98690</v>
+        <v>8439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,34 +2703,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696217</v>
+        <v>696020</v>
       </c>
       <c r="R21" t="n">
-        <v>6617392</v>
+        <v>6617274</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2781,6 +2780,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>129174969</v>
       </c>
       <c r="B23" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>129171383</v>
       </c>
       <c r="B24" t="n">
-        <v>98690</v>
+        <v>98693</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>129171401</v>
       </c>
       <c r="B25" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3503,45 +3503,44 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171363</v>
+        <v>129171395</v>
       </c>
       <c r="B29" t="n">
-        <v>91523</v>
+        <v>87047</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>3624</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695974</v>
+        <v>696012</v>
       </c>
       <c r="R29" t="n">
-        <v>6617238</v>
+        <v>6617292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,6 +3581,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171395</v>
+        <v>129171413</v>
       </c>
       <c r="B30" t="n">
-        <v>87044</v>
+        <v>86944</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,33 +3611,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3624</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696012</v>
+        <v>695981</v>
       </c>
       <c r="R30" t="n">
-        <v>6617292</v>
+        <v>6617228</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,7 +3679,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171413</v>
+        <v>129171363</v>
       </c>
       <c r="B31" t="n">
-        <v>86941</v>
+        <v>91526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695981</v>
+        <v>695974</v>
       </c>
       <c r="R31" t="n">
-        <v>6617228</v>
+        <v>6617238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3797,7 +3797,7 @@
         <v>129171371</v>
       </c>
       <c r="B32" t="n">
-        <v>96002</v>
+        <v>96005</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>129171414</v>
       </c>
       <c r="B33" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171406</v>
+        <v>129171412</v>
       </c>
       <c r="B34" t="n">
-        <v>8439</v>
+        <v>86944</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,43 +3999,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695870</v>
+        <v>695978</v>
       </c>
       <c r="R34" t="n">
-        <v>6617363</v>
+        <v>6617179</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,7 +4067,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4095,10 +4085,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171412</v>
+        <v>129171375</v>
       </c>
       <c r="B35" t="n">
-        <v>86941</v>
+        <v>91299</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4106,21 +4096,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4130,10 +4120,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695978</v>
+        <v>695740</v>
       </c>
       <c r="R35" t="n">
-        <v>6617179</v>
+        <v>6617273</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4192,10 +4182,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171375</v>
+        <v>129171406</v>
       </c>
       <c r="B36" t="n">
-        <v>91296</v>
+        <v>8439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4203,34 +4193,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695740</v>
+        <v>695870</v>
       </c>
       <c r="R36" t="n">
-        <v>6617273</v>
+        <v>6617363</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4271,6 +4270,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>129171391</v>
       </c>
       <c r="B37" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>129171394</v>
       </c>
       <c r="B38" t="n">
-        <v>90984</v>
+        <v>90987</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129171393</v>
       </c>
       <c r="B39" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>129171377</v>
       </c>
       <c r="B40" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129171384</v>
+        <v>129171411</v>
       </c>
       <c r="B41" t="n">
-        <v>98690</v>
+        <v>86944</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,7 +4750,7 @@
         <v>695740</v>
       </c>
       <c r="R41" t="n">
-        <v>6617273</v>
+        <v>6617275</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129171411</v>
+        <v>129171384</v>
       </c>
       <c r="B42" t="n">
-        <v>86941</v>
+        <v>98693</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         <v>695740</v>
       </c>
       <c r="R42" t="n">
-        <v>6617275</v>
+        <v>6617273</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4906,49 +4906,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129171382</v>
+        <v>129171369</v>
       </c>
       <c r="B43" t="n">
-        <v>98690</v>
+        <v>57883</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695889</v>
+        <v>695729</v>
       </c>
       <c r="R43" t="n">
-        <v>6617161</v>
+        <v>6617282</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,7 +4985,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5008,45 +5003,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129171369</v>
+        <v>129171382</v>
       </c>
       <c r="B44" t="n">
-        <v>57883</v>
+        <v>98693</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695729</v>
+        <v>695889</v>
       </c>
       <c r="R44" t="n">
-        <v>6617282</v>
+        <v>6617161</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5087,6 +5086,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>129171378</v>
       </c>
       <c r="B45" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>129171417</v>
       </c>
       <c r="B46" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>129171379</v>
       </c>
       <c r="B47" t="n">
-        <v>86929</v>
+        <v>86932</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1858,7 +1858,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171405</v>
+        <v>129171404</v>
       </c>
       <c r="B13" t="n">
         <v>8439</v>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695875</v>
+        <v>695939</v>
       </c>
       <c r="R13" t="n">
-        <v>6617394</v>
+        <v>6617438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171404</v>
+        <v>129171405</v>
       </c>
       <c r="B14" t="n">
         <v>8439</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695939</v>
+        <v>695875</v>
       </c>
       <c r="R14" t="n">
-        <v>6617438</v>
+        <v>6617394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2296,45 +2296,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129171402</v>
+        <v>129171373</v>
       </c>
       <c r="B17" t="n">
-        <v>88777</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4405</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>695905</v>
+        <v>695846</v>
       </c>
       <c r="R17" t="n">
-        <v>6617158</v>
+        <v>6617165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,53 +2401,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129171373</v>
+        <v>129171402</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>88777</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>4405</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695846</v>
+        <v>695905</v>
       </c>
       <c r="R18" t="n">
-        <v>6617165</v>
+        <v>6617158</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129171385</v>
+        <v>129171416</v>
       </c>
       <c r="B19" t="n">
-        <v>98693</v>
+        <v>86944</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,21 +2509,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696217</v>
+        <v>696215</v>
       </c>
       <c r="R19" t="n">
-        <v>6617392</v>
+        <v>6617356</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171416</v>
+        <v>129171385</v>
       </c>
       <c r="B20" t="n">
-        <v>86944</v>
+        <v>98693</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,21 +2606,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696215</v>
+        <v>696217</v>
       </c>
       <c r="R20" t="n">
-        <v>6617356</v>
+        <v>6617392</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,45 +2799,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174973</v>
+        <v>129174969</v>
       </c>
       <c r="B22" t="n">
-        <v>75155</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695810</v>
+        <v>696014</v>
       </c>
       <c r="R22" t="n">
-        <v>6617339</v>
+        <v>6617322</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2878,6 +2890,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2896,57 +2909,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129174969</v>
+        <v>129174973</v>
       </c>
       <c r="B23" t="n">
-        <v>98659</v>
+        <v>75155</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696014</v>
+        <v>695810</v>
       </c>
       <c r="R23" t="n">
-        <v>6617322</v>
+        <v>6617339</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2988,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129171401</v>
+        <v>129174972</v>
       </c>
       <c r="B25" t="n">
-        <v>92855</v>
+        <v>75155</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,37 +3114,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695690</v>
+        <v>695758</v>
       </c>
       <c r="R25" t="n">
-        <v>6617259</v>
+        <v>6617314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,19 +3182,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3301,42 +3297,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171367</v>
+        <v>129171401</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>92855</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3344,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696155</v>
+        <v>695690</v>
       </c>
       <c r="R27" t="n">
-        <v>6617505</v>
+        <v>6617259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,6 +3379,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3406,45 +3398,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129174972</v>
+        <v>129171367</v>
       </c>
       <c r="B28" t="n">
-        <v>75155</v>
+        <v>57883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695758</v>
+        <v>696155</v>
       </c>
       <c r="R28" t="n">
-        <v>6617314</v>
+        <v>6617505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3491,56 +3491,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171395</v>
+        <v>129171363</v>
       </c>
       <c r="B29" t="n">
-        <v>87047</v>
+        <v>91526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3624</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696012</v>
+        <v>695974</v>
       </c>
       <c r="R29" t="n">
-        <v>6617292</v>
+        <v>6617238</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,7 +3582,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171413</v>
+        <v>129171395</v>
       </c>
       <c r="B30" t="n">
-        <v>86944</v>
+        <v>87047</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,34 +3611,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3674</v>
+        <v>3624</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695981</v>
+        <v>696012</v>
       </c>
       <c r="R30" t="n">
-        <v>6617228</v>
+        <v>6617292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,6 +3678,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171363</v>
+        <v>129171413</v>
       </c>
       <c r="B31" t="n">
-        <v>91526</v>
+        <v>86944</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695974</v>
+        <v>695981</v>
       </c>
       <c r="R31" t="n">
-        <v>6617238</v>
+        <v>6617228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129171371</v>
+        <v>129171414</v>
       </c>
       <c r="B32" t="n">
-        <v>96005</v>
+        <v>86944</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695971</v>
+        <v>696014</v>
       </c>
       <c r="R32" t="n">
-        <v>6617182</v>
+        <v>6617265</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129171414</v>
+        <v>129171371</v>
       </c>
       <c r="B33" t="n">
-        <v>86944</v>
+        <v>96005</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696014</v>
+        <v>695971</v>
       </c>
       <c r="R33" t="n">
-        <v>6617265</v>
+        <v>6617182</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1143,42 +1143,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171368</v>
+        <v>129171407</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>8439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695888</v>
+        <v>695742</v>
       </c>
       <c r="R6" t="n">
-        <v>6617461</v>
+        <v>6617264</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,6 +1231,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1248,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171407</v>
+        <v>129171403</v>
       </c>
       <c r="B7" t="n">
-        <v>8439</v>
+        <v>100847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,43 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695742</v>
+        <v>696219</v>
       </c>
       <c r="R7" t="n">
-        <v>6617264</v>
+        <v>6617372</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1355,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171403</v>
+        <v>129174965</v>
       </c>
       <c r="B8" t="n">
-        <v>100847</v>
+        <v>104127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696219</v>
+        <v>696247</v>
       </c>
       <c r="R8" t="n">
-        <v>6617372</v>
+        <v>6617382</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,57 +1432,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129174965</v>
+        <v>129171368</v>
       </c>
       <c r="B9" t="n">
-        <v>104127</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696247</v>
+        <v>695888</v>
       </c>
       <c r="R9" t="n">
-        <v>6617382</v>
+        <v>6617461</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,12 +1537,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171385</v>
+        <v>129171409</v>
       </c>
       <c r="B20" t="n">
-        <v>98693</v>
+        <v>8439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,34 +2606,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696217</v>
+        <v>696020</v>
       </c>
       <c r="R20" t="n">
-        <v>6617392</v>
+        <v>6617274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2674,6 +2683,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2692,10 +2702,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171409</v>
+        <v>129171385</v>
       </c>
       <c r="B21" t="n">
-        <v>8439</v>
+        <v>98693</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,43 +2713,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696020</v>
+        <v>696217</v>
       </c>
       <c r="R21" t="n">
-        <v>6617274</v>
+        <v>6617392</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,7 +2781,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3297,37 +3297,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171401</v>
+        <v>129171367</v>
       </c>
       <c r="B27" t="n">
-        <v>92855</v>
+        <v>57883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3335,10 +3340,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695690</v>
+        <v>696155</v>
       </c>
       <c r="R27" t="n">
-        <v>6617259</v>
+        <v>6617505</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3379,7 +3384,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3398,42 +3402,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171367</v>
+        <v>129171401</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>92855</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3441,10 +3440,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696155</v>
+        <v>695690</v>
       </c>
       <c r="R28" t="n">
-        <v>6617505</v>
+        <v>6617259</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,6 +3484,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171377</v>
+        <v>129171411</v>
       </c>
       <c r="B40" t="n">
-        <v>91299</v>
+        <v>86944</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696216</v>
+        <v>695740</v>
       </c>
       <c r="R40" t="n">
-        <v>6617354</v>
+        <v>6617275</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129171411</v>
+        <v>129171377</v>
       </c>
       <c r="B41" t="n">
-        <v>86944</v>
+        <v>91299</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695740</v>
+        <v>696216</v>
       </c>
       <c r="R41" t="n">
-        <v>6617275</v>
+        <v>6617354</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,45 +1046,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171415</v>
+        <v>129171368</v>
       </c>
       <c r="B5" t="n">
-        <v>86944</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696173</v>
+        <v>695888</v>
       </c>
       <c r="R5" t="n">
-        <v>6617344</v>
+        <v>6617461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1444,53 +1452,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171368</v>
+        <v>129171415</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>86944</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>695888</v>
+        <v>696173</v>
       </c>
       <c r="R9" t="n">
-        <v>6617461</v>
+        <v>6617344</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171392</v>
+        <v>129174970</v>
       </c>
       <c r="B15" t="n">
         <v>98659</v>
@@ -2110,11 +2110,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2123,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695840</v>
+        <v>696187</v>
       </c>
       <c r="R15" t="n">
-        <v>6617459</v>
+        <v>6617372</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,19 +2170,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129174970</v>
+        <v>129171392</v>
       </c>
       <c r="B16" t="n">
         <v>98659</v>
@@ -2224,7 +2220,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696187</v>
+        <v>695840</v>
       </c>
       <c r="R16" t="n">
-        <v>6617372</v>
+        <v>6617459</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,65 +2284,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129171373</v>
+        <v>129171402</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>88777</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>4405</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>695846</v>
+        <v>695905</v>
       </c>
       <c r="R17" t="n">
-        <v>6617165</v>
+        <v>6617158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,45 +2393,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129171402</v>
+        <v>129171373</v>
       </c>
       <c r="B18" t="n">
-        <v>88777</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4405</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695905</v>
+        <v>695846</v>
       </c>
       <c r="R18" t="n">
-        <v>6617158</v>
+        <v>6617165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129174972</v>
+        <v>129171401</v>
       </c>
       <c r="B25" t="n">
-        <v>75155</v>
+        <v>92855</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,34 +3114,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695758</v>
+        <v>695690</v>
       </c>
       <c r="R25" t="n">
-        <v>6617314</v>
+        <v>6617259</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3182,28 +3185,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129171386</v>
+        <v>129174972</v>
       </c>
       <c r="B26" t="n">
-        <v>58093</v>
+        <v>75155</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3211,21 +3215,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3239,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696062</v>
+        <v>695758</v>
       </c>
       <c r="R26" t="n">
-        <v>6617338</v>
+        <v>6617314</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3285,65 +3289,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171367</v>
+        <v>129171386</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>58093</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696155</v>
+        <v>696062</v>
       </c>
       <c r="R27" t="n">
-        <v>6617505</v>
+        <v>6617338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,37 +3398,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171401</v>
+        <v>129171367</v>
       </c>
       <c r="B28" t="n">
-        <v>92855</v>
+        <v>57883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3440,10 +3441,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695690</v>
+        <v>696155</v>
       </c>
       <c r="R28" t="n">
-        <v>6617259</v>
+        <v>6617505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,7 +3485,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171412</v>
+        <v>129171375</v>
       </c>
       <c r="B34" t="n">
-        <v>86944</v>
+        <v>91299</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695978</v>
+        <v>695740</v>
       </c>
       <c r="R34" t="n">
-        <v>6617179</v>
+        <v>6617273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171375</v>
+        <v>129171412</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
+        <v>86944</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695740</v>
+        <v>695978</v>
       </c>
       <c r="R35" t="n">
-        <v>6617273</v>
+        <v>6617179</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4906,45 +4906,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129171369</v>
+        <v>129171382</v>
       </c>
       <c r="B43" t="n">
-        <v>57883</v>
+        <v>98693</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695729</v>
+        <v>695889</v>
       </c>
       <c r="R43" t="n">
-        <v>6617282</v>
+        <v>6617161</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4985,6 +4989,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5003,49 +5008,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129171382</v>
+        <v>129171369</v>
       </c>
       <c r="B44" t="n">
-        <v>98693</v>
+        <v>57883</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695889</v>
+        <v>695729</v>
       </c>
       <c r="R44" t="n">
-        <v>6617161</v>
+        <v>6617282</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5087,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171378</v>
+        <v>129171417</v>
       </c>
       <c r="B45" t="n">
-        <v>92811</v>
+        <v>86944</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>3674</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695821</v>
+        <v>696217</v>
       </c>
       <c r="R45" t="n">
-        <v>6617383</v>
+        <v>6617368</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5202,32 +5202,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129171417</v>
+        <v>129171378</v>
       </c>
       <c r="B46" t="n">
-        <v>86944</v>
+        <v>92811</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3674</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696217</v>
+        <v>695821</v>
       </c>
       <c r="R46" t="n">
-        <v>6617368</v>
+        <v>6617383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>129171368</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171407</v>
+        <v>129174965</v>
       </c>
       <c r="B6" t="n">
-        <v>8439</v>
+        <v>104137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,43 +1162,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695742</v>
+        <v>696247</v>
       </c>
       <c r="R6" t="n">
-        <v>6617264</v>
+        <v>6617382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,29 +1230,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171403</v>
+        <v>129171407</v>
       </c>
       <c r="B7" t="n">
-        <v>100847</v>
+        <v>8439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,34 +1259,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696219</v>
+        <v>695742</v>
       </c>
       <c r="R7" t="n">
-        <v>6617372</v>
+        <v>6617264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,6 +1336,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129174965</v>
+        <v>129171403</v>
       </c>
       <c r="B8" t="n">
-        <v>104127</v>
+        <v>100857</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696247</v>
+        <v>696219</v>
       </c>
       <c r="R8" t="n">
-        <v>6617382</v>
+        <v>6617372</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,12 +1440,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
         <v>129171415</v>
       </c>
       <c r="B9" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>129171360</v>
       </c>
       <c r="B11" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>129171374</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,43 +1858,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171404</v>
+        <v>129171392</v>
       </c>
       <c r="B13" t="n">
-        <v>8439</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1902,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695939</v>
+        <v>695840</v>
       </c>
       <c r="R13" t="n">
-        <v>6617438</v>
+        <v>6617459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,43 +1972,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171405</v>
+        <v>129174970</v>
       </c>
       <c r="B14" t="n">
-        <v>8439</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2009,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695875</v>
+        <v>696187</v>
       </c>
       <c r="R14" t="n">
-        <v>6617394</v>
+        <v>6617372</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,58 +2070,55 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129174970</v>
+        <v>129171405</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>8439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2119,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696187</v>
+        <v>695875</v>
       </c>
       <c r="R15" t="n">
-        <v>6617372</v>
+        <v>6617394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,62 +2177,55 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129171392</v>
+        <v>129171404</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>8439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695840</v>
+        <v>695939</v>
       </c>
       <c r="R16" t="n">
-        <v>6617459</v>
+        <v>6617438</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2299,7 +2299,7 @@
         <v>129171402</v>
       </c>
       <c r="B17" t="n">
-        <v>88777</v>
+        <v>88781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129171373</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>129171416</v>
       </c>
       <c r="B19" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171409</v>
+        <v>129171385</v>
       </c>
       <c r="B20" t="n">
-        <v>8439</v>
+        <v>98703</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,43 +2606,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696020</v>
+        <v>696217</v>
       </c>
       <c r="R20" t="n">
-        <v>6617274</v>
+        <v>6617392</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2674,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2702,10 +2692,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171385</v>
+        <v>129171409</v>
       </c>
       <c r="B21" t="n">
-        <v>98693</v>
+        <v>8439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,34 +2703,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696217</v>
+        <v>696020</v>
       </c>
       <c r="R21" t="n">
-        <v>6617392</v>
+        <v>6617274</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2781,6 +2780,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2799,57 +2799,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174969</v>
+        <v>129174973</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>75157</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696014</v>
+        <v>695810</v>
       </c>
       <c r="R22" t="n">
-        <v>6617322</v>
+        <v>6617339</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2878,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2909,45 +2896,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129174973</v>
+        <v>129174969</v>
       </c>
       <c r="B23" t="n">
-        <v>75155</v>
+        <v>98669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695810</v>
+        <v>696014</v>
       </c>
       <c r="R23" t="n">
-        <v>6617339</v>
+        <v>6617322</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,6 +2987,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>129171383</v>
       </c>
       <c r="B24" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129171401</v>
+        <v>129174972</v>
       </c>
       <c r="B25" t="n">
-        <v>92855</v>
+        <v>75157</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,37 +3114,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695690</v>
+        <v>695758</v>
       </c>
       <c r="R25" t="n">
-        <v>6617259</v>
+        <v>6617314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,64 +3182,71 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129174972</v>
+        <v>129171367</v>
       </c>
       <c r="B26" t="n">
-        <v>75155</v>
+        <v>57885</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695758</v>
+        <v>696155</v>
       </c>
       <c r="R26" t="n">
-        <v>6617314</v>
+        <v>6617505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3289,12 +3293,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3304,7 +3308,7 @@
         <v>129171386</v>
       </c>
       <c r="B27" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3398,42 +3402,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171367</v>
+        <v>129171401</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>92862</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3441,10 +3440,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696155</v>
+        <v>695690</v>
       </c>
       <c r="R28" t="n">
-        <v>6617505</v>
+        <v>6617259</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,6 +3484,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3503,45 +3503,44 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171363</v>
+        <v>129171395</v>
       </c>
       <c r="B29" t="n">
-        <v>91526</v>
+        <v>87051</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>3624</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695974</v>
+        <v>696012</v>
       </c>
       <c r="R29" t="n">
-        <v>6617238</v>
+        <v>6617292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,6 +3581,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171395</v>
+        <v>129171413</v>
       </c>
       <c r="B30" t="n">
-        <v>87047</v>
+        <v>86948</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,33 +3611,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3624</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696012</v>
+        <v>695981</v>
       </c>
       <c r="R30" t="n">
-        <v>6617292</v>
+        <v>6617228</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,7 +3679,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171413</v>
+        <v>129171363</v>
       </c>
       <c r="B31" t="n">
-        <v>86944</v>
+        <v>91533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695981</v>
+        <v>695974</v>
       </c>
       <c r="R31" t="n">
-        <v>6617228</v>
+        <v>6617238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129171414</v>
+        <v>129171371</v>
       </c>
       <c r="B32" t="n">
-        <v>86944</v>
+        <v>96015</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>2818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696014</v>
+        <v>695971</v>
       </c>
       <c r="R32" t="n">
-        <v>6617265</v>
+        <v>6617182</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129171371</v>
+        <v>129171414</v>
       </c>
       <c r="B33" t="n">
-        <v>96005</v>
+        <v>86948</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2818</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695971</v>
+        <v>696014</v>
       </c>
       <c r="R33" t="n">
-        <v>6617182</v>
+        <v>6617265</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171375</v>
+        <v>129171406</v>
       </c>
       <c r="B34" t="n">
-        <v>91299</v>
+        <v>8439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,34 +3999,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3215</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695740</v>
+        <v>695870</v>
       </c>
       <c r="R34" t="n">
-        <v>6617273</v>
+        <v>6617363</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,6 +4076,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4085,45 +4095,61 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171412</v>
+        <v>129171391</v>
       </c>
       <c r="B35" t="n">
-        <v>86944</v>
+        <v>98669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695978</v>
+        <v>695872</v>
       </c>
       <c r="R35" t="n">
-        <v>6617179</v>
+        <v>6617462</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4164,6 +4190,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4182,10 +4209,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171406</v>
+        <v>129171412</v>
       </c>
       <c r="B36" t="n">
-        <v>8439</v>
+        <v>86948</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4193,43 +4220,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695870</v>
+        <v>695978</v>
       </c>
       <c r="R36" t="n">
-        <v>6617363</v>
+        <v>6617179</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4288,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4289,61 +4306,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171391</v>
+        <v>129171375</v>
       </c>
       <c r="B37" t="n">
-        <v>98659</v>
+        <v>91305</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695872</v>
+        <v>695740</v>
       </c>
       <c r="R37" t="n">
-        <v>6617462</v>
+        <v>6617273</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4384,7 +4385,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>129171394</v>
       </c>
       <c r="B38" t="n">
-        <v>90987</v>
+        <v>90991</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129171393</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171411</v>
+        <v>129171384</v>
       </c>
       <c r="B40" t="n">
-        <v>86944</v>
+        <v>98703</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4653,7 +4653,7 @@
         <v>695740</v>
       </c>
       <c r="R40" t="n">
-        <v>6617275</v>
+        <v>6617273</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4715,7 +4715,7 @@
         <v>129171377</v>
       </c>
       <c r="B41" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129171384</v>
+        <v>129171411</v>
       </c>
       <c r="B42" t="n">
-        <v>98693</v>
+        <v>86948</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         <v>695740</v>
       </c>
       <c r="R42" t="n">
-        <v>6617273</v>
+        <v>6617275</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4909,7 +4909,7 @@
         <v>129171382</v>
       </c>
       <c r="B43" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>129171369</v>
       </c>
       <c r="B44" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171417</v>
+        <v>129171378</v>
       </c>
       <c r="B45" t="n">
-        <v>86944</v>
+        <v>92818</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3674</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696217</v>
+        <v>695821</v>
       </c>
       <c r="R45" t="n">
-        <v>6617368</v>
+        <v>6617383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5202,32 +5202,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129171378</v>
+        <v>129171379</v>
       </c>
       <c r="B46" t="n">
-        <v>92811</v>
+        <v>86936</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>6003296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695821</v>
+        <v>696222</v>
       </c>
       <c r="R46" t="n">
-        <v>6617383</v>
+        <v>6617388</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5281,6 +5281,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5299,32 +5300,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171379</v>
+        <v>129171417</v>
       </c>
       <c r="B47" t="n">
-        <v>86932</v>
+        <v>86948</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003296</v>
+        <v>3674</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5334,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696222</v>
+        <v>696217</v>
       </c>
       <c r="R47" t="n">
-        <v>6617388</v>
+        <v>6617368</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,7 +5379,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -3503,44 +3503,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171395</v>
+        <v>129171363</v>
       </c>
       <c r="B29" t="n">
-        <v>87051</v>
+        <v>91533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3624</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696012</v>
+        <v>695974</v>
       </c>
       <c r="R29" t="n">
-        <v>6617292</v>
+        <v>6617238</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,7 +3582,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171413</v>
+        <v>129171395</v>
       </c>
       <c r="B30" t="n">
-        <v>86948</v>
+        <v>87051</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,34 +3611,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3674</v>
+        <v>3624</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695981</v>
+        <v>696012</v>
       </c>
       <c r="R30" t="n">
-        <v>6617228</v>
+        <v>6617292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,6 +3678,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171363</v>
+        <v>129171413</v>
       </c>
       <c r="B31" t="n">
-        <v>91533</v>
+        <v>86948</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695974</v>
+        <v>695981</v>
       </c>
       <c r="R31" t="n">
-        <v>6617238</v>
+        <v>6617228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3988,43 +3988,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171406</v>
+        <v>129171391</v>
       </c>
       <c r="B34" t="n">
-        <v>8439</v>
+        <v>98669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4032,10 +4039,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695870</v>
+        <v>695872</v>
       </c>
       <c r="R34" t="n">
-        <v>6617363</v>
+        <v>6617462</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4095,61 +4102,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171391</v>
+        <v>129171412</v>
       </c>
       <c r="B35" t="n">
-        <v>98669</v>
+        <v>86948</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695872</v>
+        <v>695978</v>
       </c>
       <c r="R35" t="n">
-        <v>6617462</v>
+        <v>6617179</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4190,7 +4181,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4209,10 +4199,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171412</v>
+        <v>129171375</v>
       </c>
       <c r="B36" t="n">
-        <v>86948</v>
+        <v>91305</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4220,21 +4210,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4244,10 +4234,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695978</v>
+        <v>695740</v>
       </c>
       <c r="R36" t="n">
-        <v>6617179</v>
+        <v>6617273</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4306,10 +4296,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171375</v>
+        <v>129171406</v>
       </c>
       <c r="B37" t="n">
-        <v>91305</v>
+        <v>8439</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4317,34 +4307,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3215</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695740</v>
+        <v>695870</v>
       </c>
       <c r="R37" t="n">
-        <v>6617273</v>
+        <v>6617363</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4385,6 +4384,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171384</v>
+        <v>129171377</v>
       </c>
       <c r="B40" t="n">
-        <v>98703</v>
+        <v>91305</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695740</v>
+        <v>696216</v>
       </c>
       <c r="R40" t="n">
-        <v>6617273</v>
+        <v>6617354</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129171377</v>
+        <v>129171411</v>
       </c>
       <c r="B41" t="n">
-        <v>91305</v>
+        <v>86948</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696216</v>
+        <v>695740</v>
       </c>
       <c r="R41" t="n">
-        <v>6617354</v>
+        <v>6617275</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129171411</v>
+        <v>129171384</v>
       </c>
       <c r="B42" t="n">
-        <v>86948</v>
+        <v>98703</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         <v>695740</v>
       </c>
       <c r="R42" t="n">
-        <v>6617275</v>
+        <v>6617273</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171378</v>
+        <v>129171417</v>
       </c>
       <c r="B45" t="n">
-        <v>92818</v>
+        <v>86948</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>3674</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695821</v>
+        <v>696217</v>
       </c>
       <c r="R45" t="n">
-        <v>6617383</v>
+        <v>6617368</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5300,32 +5300,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171417</v>
+        <v>129171378</v>
       </c>
       <c r="B47" t="n">
-        <v>86948</v>
+        <v>92818</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696217</v>
+        <v>695821</v>
       </c>
       <c r="R47" t="n">
-        <v>6617368</v>
+        <v>6617383</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,53 +1046,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171368</v>
+        <v>129171415</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>86955</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695888</v>
+        <v>696173</v>
       </c>
       <c r="R5" t="n">
-        <v>6617461</v>
+        <v>6617344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129174965</v>
+        <v>129171407</v>
       </c>
       <c r="B6" t="n">
-        <v>104137</v>
+        <v>8439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,34 +1154,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696247</v>
+        <v>695742</v>
       </c>
       <c r="R6" t="n">
-        <v>6617382</v>
+        <v>6617264</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,28 +1231,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171407</v>
+        <v>129171403</v>
       </c>
       <c r="B7" t="n">
-        <v>8439</v>
+        <v>100864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,43 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695742</v>
+        <v>696219</v>
       </c>
       <c r="R7" t="n">
-        <v>6617264</v>
+        <v>6617372</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1355,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171403</v>
+        <v>129174965</v>
       </c>
       <c r="B8" t="n">
-        <v>100857</v>
+        <v>104144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696219</v>
+        <v>696247</v>
       </c>
       <c r="R8" t="n">
-        <v>6617372</v>
+        <v>6617382</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,57 +1432,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171415</v>
+        <v>129171368</v>
       </c>
       <c r="B9" t="n">
-        <v>86948</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3674</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696173</v>
+        <v>695888</v>
       </c>
       <c r="R9" t="n">
-        <v>6617344</v>
+        <v>6617461</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
         <v>129171360</v>
       </c>
       <c r="B11" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,50 +1858,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171392</v>
+        <v>129171404</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>8439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1909,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695840</v>
+        <v>695939</v>
       </c>
       <c r="R13" t="n">
-        <v>6617459</v>
+        <v>6617438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,46 +1965,43 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129174970</v>
+        <v>129171405</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>8439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2019,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696187</v>
+        <v>695875</v>
       </c>
       <c r="R14" t="n">
-        <v>6617372</v>
+        <v>6617394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,55 +2060,62 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171405</v>
+        <v>129171392</v>
       </c>
       <c r="B15" t="n">
-        <v>8439</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2126,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695875</v>
+        <v>695840</v>
       </c>
       <c r="R15" t="n">
-        <v>6617394</v>
+        <v>6617459</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,43 +2186,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129171404</v>
+        <v>129174970</v>
       </c>
       <c r="B16" t="n">
-        <v>8439</v>
+        <v>98676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695939</v>
+        <v>696187</v>
       </c>
       <c r="R16" t="n">
-        <v>6617438</v>
+        <v>6617372</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,12 +2284,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2299,7 +2299,7 @@
         <v>129171402</v>
       </c>
       <c r="B17" t="n">
-        <v>88781</v>
+        <v>88788</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>129171416</v>
       </c>
       <c r="B19" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171385</v>
+        <v>129171409</v>
       </c>
       <c r="B20" t="n">
-        <v>98703</v>
+        <v>8439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,34 +2606,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696217</v>
+        <v>696020</v>
       </c>
       <c r="R20" t="n">
-        <v>6617392</v>
+        <v>6617274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2674,6 +2683,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2692,10 +2702,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171409</v>
+        <v>129171385</v>
       </c>
       <c r="B21" t="n">
-        <v>8439</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,43 +2713,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696020</v>
+        <v>696217</v>
       </c>
       <c r="R21" t="n">
-        <v>6617274</v>
+        <v>6617392</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,7 +2781,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>129174969</v>
       </c>
       <c r="B23" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>129171383</v>
       </c>
       <c r="B24" t="n">
-        <v>98703</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129174972</v>
+        <v>129171401</v>
       </c>
       <c r="B25" t="n">
-        <v>75157</v>
+        <v>92869</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,34 +3114,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695758</v>
+        <v>695690</v>
       </c>
       <c r="R25" t="n">
-        <v>6617314</v>
+        <v>6617259</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3182,18 +3185,19 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3402,10 +3406,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171401</v>
+        <v>129174972</v>
       </c>
       <c r="B28" t="n">
-        <v>92862</v>
+        <v>75157</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,37 +3417,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695690</v>
+        <v>695758</v>
       </c>
       <c r="R28" t="n">
-        <v>6617259</v>
+        <v>6617314</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,19 +3485,18 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3506,7 +3506,7 @@
         <v>129171363</v>
       </c>
       <c r="B29" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>129171395</v>
       </c>
       <c r="B30" t="n">
-        <v>87051</v>
+        <v>87058</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>129171413</v>
       </c>
       <c r="B31" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>129171371</v>
       </c>
       <c r="B32" t="n">
-        <v>96015</v>
+        <v>96022</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>129171414</v>
       </c>
       <c r="B33" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3988,50 +3988,43 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171391</v>
+        <v>129171406</v>
       </c>
       <c r="B34" t="n">
-        <v>98669</v>
+        <v>8439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4039,10 +4032,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695872</v>
+        <v>695870</v>
       </c>
       <c r="R34" t="n">
-        <v>6617462</v>
+        <v>6617363</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4102,45 +4095,61 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171412</v>
+        <v>129171391</v>
       </c>
       <c r="B35" t="n">
-        <v>86948</v>
+        <v>98676</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695978</v>
+        <v>695872</v>
       </c>
       <c r="R35" t="n">
-        <v>6617179</v>
+        <v>6617462</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4181,6 +4190,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4199,10 +4209,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171375</v>
+        <v>129171412</v>
       </c>
       <c r="B36" t="n">
-        <v>91305</v>
+        <v>86955</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4210,21 +4220,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4234,10 +4244,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695740</v>
+        <v>695978</v>
       </c>
       <c r="R36" t="n">
-        <v>6617273</v>
+        <v>6617179</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4296,10 +4306,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171406</v>
+        <v>129171375</v>
       </c>
       <c r="B37" t="n">
-        <v>8439</v>
+        <v>91312</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4307,43 +4317,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>3215</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695870</v>
+        <v>695740</v>
       </c>
       <c r="R37" t="n">
-        <v>6617363</v>
+        <v>6617273</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4384,7 +4385,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>129171394</v>
       </c>
       <c r="B38" t="n">
-        <v>90991</v>
+        <v>90998</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129171393</v>
       </c>
       <c r="B39" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171377</v>
+        <v>129171384</v>
       </c>
       <c r="B40" t="n">
-        <v>91305</v>
+        <v>98710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696216</v>
+        <v>695740</v>
       </c>
       <c r="R40" t="n">
-        <v>6617354</v>
+        <v>6617273</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129171411</v>
+        <v>129171377</v>
       </c>
       <c r="B41" t="n">
-        <v>86948</v>
+        <v>91312</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695740</v>
+        <v>696216</v>
       </c>
       <c r="R41" t="n">
-        <v>6617275</v>
+        <v>6617354</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129171384</v>
+        <v>129171411</v>
       </c>
       <c r="B42" t="n">
-        <v>98703</v>
+        <v>86955</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         <v>695740</v>
       </c>
       <c r="R42" t="n">
-        <v>6617273</v>
+        <v>6617275</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4906,49 +4906,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129171382</v>
+        <v>129171369</v>
       </c>
       <c r="B43" t="n">
-        <v>98703</v>
+        <v>57885</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695889</v>
+        <v>695729</v>
       </c>
       <c r="R43" t="n">
-        <v>6617161</v>
+        <v>6617282</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,7 +4985,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5008,45 +5003,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129171369</v>
+        <v>129171382</v>
       </c>
       <c r="B44" t="n">
-        <v>57885</v>
+        <v>98710</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695729</v>
+        <v>695889</v>
       </c>
       <c r="R44" t="n">
-        <v>6617282</v>
+        <v>6617161</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5087,6 +5086,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>129171417</v>
       </c>
       <c r="B45" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5202,32 +5202,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129171379</v>
+        <v>129171378</v>
       </c>
       <c r="B46" t="n">
-        <v>86936</v>
+        <v>92825</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003296</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696222</v>
+        <v>695821</v>
       </c>
       <c r="R46" t="n">
-        <v>6617388</v>
+        <v>6617383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5281,7 +5281,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5300,32 +5299,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171378</v>
+        <v>129171379</v>
       </c>
       <c r="B47" t="n">
-        <v>92818</v>
+        <v>86943</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>6003296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5335,10 +5334,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>695821</v>
+        <v>696222</v>
       </c>
       <c r="R47" t="n">
-        <v>6617383</v>
+        <v>6617388</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5379,6 +5378,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>129171415</v>
       </c>
       <c r="B5" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,43 +1143,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171407</v>
+        <v>129171368</v>
       </c>
       <c r="B6" t="n">
-        <v>8439</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695742</v>
+        <v>695888</v>
       </c>
       <c r="R6" t="n">
-        <v>6617264</v>
+        <v>6617461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1230,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1253,7 +1251,7 @@
         <v>129171403</v>
       </c>
       <c r="B7" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1348,7 @@
         <v>129174965</v>
       </c>
       <c r="B8" t="n">
-        <v>104144</v>
+        <v>104146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,42 +1442,43 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171368</v>
+        <v>129171407</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>8439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1487,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>695888</v>
+        <v>695742</v>
       </c>
       <c r="R9" t="n">
-        <v>6617461</v>
+        <v>6617264</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,6 +1530,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>129171360</v>
       </c>
       <c r="B11" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>129171374</v>
       </c>
       <c r="B12" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>129171392</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>129174970</v>
       </c>
       <c r="B16" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>129171402</v>
       </c>
       <c r="B17" t="n">
-        <v>88788</v>
+        <v>88790</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129171373</v>
       </c>
       <c r="B18" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>129171416</v>
       </c>
       <c r="B19" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>129171385</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>129174973</v>
       </c>
       <c r="B22" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>129174969</v>
       </c>
       <c r="B23" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>129171383</v>
       </c>
       <c r="B24" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129171401</v>
+        <v>129174972</v>
       </c>
       <c r="B25" t="n">
-        <v>92869</v>
+        <v>75159</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,37 +3114,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695690</v>
+        <v>695758</v>
       </c>
       <c r="R25" t="n">
-        <v>6617259</v>
+        <v>6617314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,61 +3182,55 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129171367</v>
+        <v>129171401</v>
       </c>
       <c r="B26" t="n">
-        <v>57885</v>
+        <v>92871</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3247,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696155</v>
+        <v>695690</v>
       </c>
       <c r="R26" t="n">
-        <v>6617505</v>
+        <v>6617259</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3291,6 +3282,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3312,7 +3304,7 @@
         <v>129171386</v>
       </c>
       <c r="B27" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3406,45 +3398,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129174972</v>
+        <v>129171367</v>
       </c>
       <c r="B28" t="n">
-        <v>75157</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695758</v>
+        <v>696155</v>
       </c>
       <c r="R28" t="n">
-        <v>6617314</v>
+        <v>6617505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3491,12 +3491,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3506,7 +3506,7 @@
         <v>129171363</v>
       </c>
       <c r="B29" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>129171395</v>
       </c>
       <c r="B30" t="n">
-        <v>87058</v>
+        <v>87060</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>129171413</v>
       </c>
       <c r="B31" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>129171371</v>
       </c>
       <c r="B32" t="n">
-        <v>96022</v>
+        <v>96024</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>129171414</v>
       </c>
       <c r="B33" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171406</v>
+        <v>129171412</v>
       </c>
       <c r="B34" t="n">
-        <v>8439</v>
+        <v>86957</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,43 +3999,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695870</v>
+        <v>695978</v>
       </c>
       <c r="R34" t="n">
-        <v>6617363</v>
+        <v>6617179</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,7 +4067,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4095,61 +4085,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171391</v>
+        <v>129171375</v>
       </c>
       <c r="B35" t="n">
-        <v>98676</v>
+        <v>91314</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695872</v>
+        <v>695740</v>
       </c>
       <c r="R35" t="n">
-        <v>6617462</v>
+        <v>6617273</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4190,7 +4164,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4209,10 +4182,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171412</v>
+        <v>129171406</v>
       </c>
       <c r="B36" t="n">
-        <v>86955</v>
+        <v>8439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4220,34 +4193,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695978</v>
+        <v>695870</v>
       </c>
       <c r="R36" t="n">
-        <v>6617179</v>
+        <v>6617363</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4288,6 +4270,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4306,45 +4289,61 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171375</v>
+        <v>129171391</v>
       </c>
       <c r="B37" t="n">
-        <v>91312</v>
+        <v>98678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695740</v>
+        <v>695872</v>
       </c>
       <c r="R37" t="n">
-        <v>6617273</v>
+        <v>6617462</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4385,6 +4384,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>129171394</v>
       </c>
       <c r="B38" t="n">
-        <v>90998</v>
+        <v>91000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129171393</v>
       </c>
       <c r="B39" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171384</v>
+        <v>129171377</v>
       </c>
       <c r="B40" t="n">
-        <v>98710</v>
+        <v>91314</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695740</v>
+        <v>696216</v>
       </c>
       <c r="R40" t="n">
-        <v>6617273</v>
+        <v>6617354</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129171377</v>
+        <v>129171411</v>
       </c>
       <c r="B41" t="n">
-        <v>91312</v>
+        <v>86957</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696216</v>
+        <v>695740</v>
       </c>
       <c r="R41" t="n">
-        <v>6617354</v>
+        <v>6617275</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129171411</v>
+        <v>129171384</v>
       </c>
       <c r="B42" t="n">
-        <v>86955</v>
+        <v>98712</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         <v>695740</v>
       </c>
       <c r="R42" t="n">
-        <v>6617275</v>
+        <v>6617273</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4906,45 +4906,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129171369</v>
+        <v>129171382</v>
       </c>
       <c r="B43" t="n">
-        <v>57885</v>
+        <v>98712</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695729</v>
+        <v>695889</v>
       </c>
       <c r="R43" t="n">
-        <v>6617282</v>
+        <v>6617161</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4985,6 +4989,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5003,49 +5008,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129171382</v>
+        <v>129171369</v>
       </c>
       <c r="B44" t="n">
-        <v>98710</v>
+        <v>57887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695889</v>
+        <v>695729</v>
       </c>
       <c r="R44" t="n">
-        <v>6617161</v>
+        <v>6617282</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5087,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171417</v>
+        <v>129171378</v>
       </c>
       <c r="B45" t="n">
-        <v>86955</v>
+        <v>92827</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3674</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696217</v>
+        <v>695821</v>
       </c>
       <c r="R45" t="n">
-        <v>6617368</v>
+        <v>6617383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5202,32 +5202,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129171378</v>
+        <v>129171417</v>
       </c>
       <c r="B46" t="n">
-        <v>92825</v>
+        <v>86957</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>3674</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695821</v>
+        <v>696217</v>
       </c>
       <c r="R46" t="n">
-        <v>6617383</v>
+        <v>6617368</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5302,7 +5302,7 @@
         <v>129171379</v>
       </c>
       <c r="B47" t="n">
-        <v>86943</v>
+        <v>86945</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1143,42 +1143,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171368</v>
+        <v>129171407</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>8439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695888</v>
+        <v>695742</v>
       </c>
       <c r="R6" t="n">
-        <v>6617461</v>
+        <v>6617264</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,6 +1231,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1442,43 +1444,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171407</v>
+        <v>129171368</v>
       </c>
       <c r="B9" t="n">
-        <v>8439</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1486,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>695742</v>
+        <v>695888</v>
       </c>
       <c r="R9" t="n">
-        <v>6617264</v>
+        <v>6617461</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1531,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1753,40 +1753,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171374</v>
+        <v>129171405</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>8439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1796,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696142</v>
+        <v>695875</v>
       </c>
       <c r="R12" t="n">
-        <v>6617341</v>
+        <v>6617394</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,6 +1841,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1858,43 +1860,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171404</v>
+        <v>129171392</v>
       </c>
       <c r="B13" t="n">
-        <v>8439</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1902,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695939</v>
+        <v>695840</v>
       </c>
       <c r="R13" t="n">
-        <v>6617438</v>
+        <v>6617459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,43 +1974,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171405</v>
+        <v>129174970</v>
       </c>
       <c r="B14" t="n">
-        <v>8439</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2009,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695875</v>
+        <v>696187</v>
       </c>
       <c r="R14" t="n">
-        <v>6617394</v>
+        <v>6617372</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,62 +2072,55 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171392</v>
+        <v>129171404</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>8439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2123,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695840</v>
+        <v>695939</v>
       </c>
       <c r="R15" t="n">
-        <v>6617459</v>
+        <v>6617438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,46 +2191,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129174970</v>
+        <v>129171374</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696187</v>
+        <v>696142</v>
       </c>
       <c r="R16" t="n">
-        <v>6617372</v>
+        <v>6617341</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,64 +2278,71 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129171402</v>
+        <v>129171373</v>
       </c>
       <c r="B17" t="n">
-        <v>88790</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4405</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>695905</v>
+        <v>695846</v>
       </c>
       <c r="R17" t="n">
-        <v>6617158</v>
+        <v>6617165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,53 +2401,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129171373</v>
+        <v>129171402</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>88790</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>4405</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695846</v>
+        <v>695905</v>
       </c>
       <c r="R18" t="n">
-        <v>6617165</v>
+        <v>6617158</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129174972</v>
+        <v>129171386</v>
       </c>
       <c r="B25" t="n">
-        <v>75159</v>
+        <v>58097</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,21 +3114,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695758</v>
+        <v>696062</v>
       </c>
       <c r="R25" t="n">
-        <v>6617314</v>
+        <v>6617338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,12 +3188,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171386</v>
+        <v>129174972</v>
       </c>
       <c r="B27" t="n">
-        <v>58097</v>
+        <v>75159</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696062</v>
+        <v>695758</v>
       </c>
       <c r="R27" t="n">
-        <v>6617338</v>
+        <v>6617314</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4182,43 +4182,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171406</v>
+        <v>129171391</v>
       </c>
       <c r="B36" t="n">
-        <v>8439</v>
+        <v>98678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4226,10 +4233,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695870</v>
+        <v>695872</v>
       </c>
       <c r="R36" t="n">
-        <v>6617363</v>
+        <v>6617462</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4289,50 +4296,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171391</v>
+        <v>129171406</v>
       </c>
       <c r="B37" t="n">
-        <v>98678</v>
+        <v>8439</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695872</v>
+        <v>695870</v>
       </c>
       <c r="R37" t="n">
-        <v>6617462</v>
+        <v>6617363</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4906,49 +4906,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129171382</v>
+        <v>129171369</v>
       </c>
       <c r="B43" t="n">
-        <v>98712</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695889</v>
+        <v>695729</v>
       </c>
       <c r="R43" t="n">
-        <v>6617161</v>
+        <v>6617282</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,7 +4985,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5008,45 +5003,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129171369</v>
+        <v>129171382</v>
       </c>
       <c r="B44" t="n">
-        <v>57887</v>
+        <v>98712</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695729</v>
+        <v>695889</v>
       </c>
       <c r="R44" t="n">
-        <v>6617282</v>
+        <v>6617161</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5087,6 +5086,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,45 +1046,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171415</v>
+        <v>129171368</v>
       </c>
       <c r="B5" t="n">
-        <v>86957</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696173</v>
+        <v>695888</v>
       </c>
       <c r="R5" t="n">
-        <v>6617344</v>
+        <v>6617461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171407</v>
+        <v>129171415</v>
       </c>
       <c r="B6" t="n">
-        <v>8439</v>
+        <v>86957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,43 +1162,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695742</v>
+        <v>696173</v>
       </c>
       <c r="R6" t="n">
-        <v>6617264</v>
+        <v>6617344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1230,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171403</v>
+        <v>129171407</v>
       </c>
       <c r="B7" t="n">
-        <v>100866</v>
+        <v>8439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,34 +1259,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696219</v>
+        <v>695742</v>
       </c>
       <c r="R7" t="n">
-        <v>6617372</v>
+        <v>6617264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,6 +1336,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129174965</v>
+        <v>129171403</v>
       </c>
       <c r="B8" t="n">
-        <v>104146</v>
+        <v>100866</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696247</v>
+        <v>696219</v>
       </c>
       <c r="R8" t="n">
-        <v>6617382</v>
+        <v>6617372</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,65 +1440,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171368</v>
+        <v>129174965</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>104146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>695888</v>
+        <v>696247</v>
       </c>
       <c r="R9" t="n">
-        <v>6617461</v>
+        <v>6617382</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,12 +1537,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1753,41 +1753,40 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171405</v>
+        <v>129171374</v>
       </c>
       <c r="B12" t="n">
-        <v>8439</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1797,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695875</v>
+        <v>696142</v>
       </c>
       <c r="R12" t="n">
-        <v>6617394</v>
+        <v>6617341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1840,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1860,50 +1858,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171392</v>
+        <v>129171405</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>8439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1911,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695840</v>
+        <v>695875</v>
       </c>
       <c r="R13" t="n">
-        <v>6617459</v>
+        <v>6617394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129174970</v>
+        <v>129171392</v>
       </c>
       <c r="B14" t="n">
         <v>98678</v>
@@ -2012,7 +2003,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2021,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696187</v>
+        <v>695840</v>
       </c>
       <c r="R14" t="n">
-        <v>6617372</v>
+        <v>6617459</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,55 +2067,58 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171404</v>
+        <v>129174970</v>
       </c>
       <c r="B15" t="n">
-        <v>8439</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2128,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695939</v>
+        <v>696187</v>
       </c>
       <c r="R15" t="n">
-        <v>6617438</v>
+        <v>6617372</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,52 +2177,53 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129171374</v>
+        <v>129171404</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>8439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2234,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696142</v>
+        <v>695939</v>
       </c>
       <c r="R16" t="n">
-        <v>6617341</v>
+        <v>6617438</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,6 +2277,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -3503,45 +3503,44 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171363</v>
+        <v>129171395</v>
       </c>
       <c r="B29" t="n">
-        <v>91542</v>
+        <v>87060</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>3624</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695974</v>
+        <v>696012</v>
       </c>
       <c r="R29" t="n">
-        <v>6617238</v>
+        <v>6617292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,6 +3581,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171395</v>
+        <v>129171413</v>
       </c>
       <c r="B30" t="n">
-        <v>87060</v>
+        <v>86957</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,33 +3611,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3624</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696012</v>
+        <v>695981</v>
       </c>
       <c r="R30" t="n">
-        <v>6617292</v>
+        <v>6617228</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,7 +3679,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171413</v>
+        <v>129171363</v>
       </c>
       <c r="B31" t="n">
-        <v>86957</v>
+        <v>91542</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695981</v>
+        <v>695974</v>
       </c>
       <c r="R31" t="n">
-        <v>6617228</v>
+        <v>6617238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4182,50 +4182,43 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171391</v>
+        <v>129171406</v>
       </c>
       <c r="B36" t="n">
-        <v>98678</v>
+        <v>8439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4233,10 +4226,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695872</v>
+        <v>695870</v>
       </c>
       <c r="R36" t="n">
-        <v>6617462</v>
+        <v>6617363</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4296,43 +4289,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171406</v>
+        <v>129171391</v>
       </c>
       <c r="B37" t="n">
-        <v>8439</v>
+        <v>98678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695870</v>
+        <v>695872</v>
       </c>
       <c r="R37" t="n">
-        <v>6617363</v>
+        <v>6617462</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,53 +1046,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171368</v>
+        <v>129171415</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>86958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695888</v>
+        <v>696173</v>
       </c>
       <c r="R5" t="n">
-        <v>6617461</v>
+        <v>6617344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,45 +1143,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171415</v>
+        <v>129171368</v>
       </c>
       <c r="B6" t="n">
-        <v>86957</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696173</v>
+        <v>695888</v>
       </c>
       <c r="R6" t="n">
-        <v>6617344</v>
+        <v>6617461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171403</v>
+        <v>129174965</v>
       </c>
       <c r="B8" t="n">
-        <v>100866</v>
+        <v>104172</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696219</v>
+        <v>696247</v>
       </c>
       <c r="R8" t="n">
-        <v>6617372</v>
+        <v>6617382</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,22 +1440,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129174965</v>
+        <v>129171403</v>
       </c>
       <c r="B9" t="n">
-        <v>104146</v>
+        <v>100892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696247</v>
+        <v>696219</v>
       </c>
       <c r="R9" t="n">
-        <v>6617382</v>
+        <v>6617372</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,12 +1537,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1659,7 +1659,7 @@
         <v>129171360</v>
       </c>
       <c r="B11" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171405</v>
+        <v>129171404</v>
       </c>
       <c r="B13" t="n">
         <v>8439</v>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695875</v>
+        <v>695939</v>
       </c>
       <c r="R13" t="n">
-        <v>6617394</v>
+        <v>6617438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,50 +1965,43 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171392</v>
+        <v>129171405</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>8439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2016,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695840</v>
+        <v>695875</v>
       </c>
       <c r="R14" t="n">
-        <v>6617459</v>
+        <v>6617394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,10 +2072,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129174970</v>
+        <v>129171392</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,7 +2110,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2126,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696187</v>
+        <v>695840</v>
       </c>
       <c r="R15" t="n">
-        <v>6617372</v>
+        <v>6617459</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2177,55 +2174,58 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129171404</v>
+        <v>129174970</v>
       </c>
       <c r="B16" t="n">
-        <v>8439</v>
+        <v>98704</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695939</v>
+        <v>696187</v>
       </c>
       <c r="R16" t="n">
-        <v>6617438</v>
+        <v>6617372</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,65 +2284,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129171373</v>
+        <v>129171402</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>88791</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>4405</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>695846</v>
+        <v>695905</v>
       </c>
       <c r="R17" t="n">
-        <v>6617165</v>
+        <v>6617158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,45 +2393,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129171402</v>
+        <v>129171373</v>
       </c>
       <c r="B18" t="n">
-        <v>88790</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4405</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695905</v>
+        <v>695846</v>
       </c>
       <c r="R18" t="n">
-        <v>6617158</v>
+        <v>6617165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
         <v>129171416</v>
       </c>
       <c r="B19" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>129171385</v>
       </c>
       <c r="B21" t="n">
-        <v>98712</v>
+        <v>98738</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,45 +2799,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174973</v>
+        <v>129174969</v>
       </c>
       <c r="B22" t="n">
-        <v>75159</v>
+        <v>98704</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695810</v>
+        <v>696014</v>
       </c>
       <c r="R22" t="n">
-        <v>6617339</v>
+        <v>6617322</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2878,6 +2890,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2896,57 +2909,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129174969</v>
+        <v>129174973</v>
       </c>
       <c r="B23" t="n">
-        <v>98678</v>
+        <v>75159</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696014</v>
+        <v>695810</v>
       </c>
       <c r="R23" t="n">
-        <v>6617322</v>
+        <v>6617339</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2988,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>129171383</v>
       </c>
       <c r="B24" t="n">
-        <v>98712</v>
+        <v>98738</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129171386</v>
+        <v>129174972</v>
       </c>
       <c r="B25" t="n">
-        <v>58097</v>
+        <v>75159</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,21 +3114,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696062</v>
+        <v>695758</v>
       </c>
       <c r="R25" t="n">
-        <v>6617338</v>
+        <v>6617314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,12 +3188,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3203,7 +3203,7 @@
         <v>129171401</v>
       </c>
       <c r="B26" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3301,10 +3301,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129174972</v>
+        <v>129171386</v>
       </c>
       <c r="B27" t="n">
-        <v>75159</v>
+        <v>58097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695758</v>
+        <v>696062</v>
       </c>
       <c r="R27" t="n">
-        <v>6617314</v>
+        <v>6617338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3506,7 +3506,7 @@
         <v>129171395</v>
       </c>
       <c r="B29" t="n">
-        <v>87060</v>
+        <v>87061</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,32 +3600,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171413</v>
+        <v>129171363</v>
       </c>
       <c r="B30" t="n">
-        <v>86957</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695981</v>
+        <v>695974</v>
       </c>
       <c r="R30" t="n">
-        <v>6617228</v>
+        <v>6617238</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171363</v>
+        <v>129171413</v>
       </c>
       <c r="B31" t="n">
-        <v>91542</v>
+        <v>86958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695974</v>
+        <v>695981</v>
       </c>
       <c r="R31" t="n">
-        <v>6617238</v>
+        <v>6617228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3797,7 +3797,7 @@
         <v>129171371</v>
       </c>
       <c r="B32" t="n">
-        <v>96024</v>
+        <v>96050</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>129171414</v>
       </c>
       <c r="B33" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171412</v>
+        <v>129171375</v>
       </c>
       <c r="B34" t="n">
-        <v>86957</v>
+        <v>91313</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695978</v>
+        <v>695740</v>
       </c>
       <c r="R34" t="n">
-        <v>6617179</v>
+        <v>6617273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171375</v>
+        <v>129171406</v>
       </c>
       <c r="B35" t="n">
-        <v>91314</v>
+        <v>8439</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4096,34 +4096,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3215</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695740</v>
+        <v>695870</v>
       </c>
       <c r="R35" t="n">
-        <v>6617273</v>
+        <v>6617363</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4164,6 +4173,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4182,10 +4192,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171406</v>
+        <v>129171412</v>
       </c>
       <c r="B36" t="n">
-        <v>8439</v>
+        <v>86958</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4193,43 +4203,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695870</v>
+        <v>695978</v>
       </c>
       <c r="R36" t="n">
-        <v>6617363</v>
+        <v>6617179</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4271,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>129171391</v>
       </c>
       <c r="B37" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>129171394</v>
       </c>
       <c r="B38" t="n">
-        <v>91000</v>
+        <v>91001</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129171393</v>
       </c>
       <c r="B39" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171377</v>
+        <v>129171384</v>
       </c>
       <c r="B40" t="n">
-        <v>91314</v>
+        <v>98738</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696216</v>
+        <v>695740</v>
       </c>
       <c r="R40" t="n">
-        <v>6617354</v>
+        <v>6617273</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4715,7 +4715,7 @@
         <v>129171411</v>
       </c>
       <c r="B41" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129171384</v>
+        <v>129171377</v>
       </c>
       <c r="B42" t="n">
-        <v>98712</v>
+        <v>91313</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695740</v>
+        <v>696216</v>
       </c>
       <c r="R42" t="n">
-        <v>6617273</v>
+        <v>6617354</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5006,7 +5006,7 @@
         <v>129171382</v>
       </c>
       <c r="B44" t="n">
-        <v>98712</v>
+        <v>98738</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171378</v>
+        <v>129171379</v>
       </c>
       <c r="B45" t="n">
-        <v>92827</v>
+        <v>86946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>6003296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695821</v>
+        <v>696222</v>
       </c>
       <c r="R45" t="n">
-        <v>6617383</v>
+        <v>6617388</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5184,6 +5184,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5202,32 +5203,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129171417</v>
+        <v>129171378</v>
       </c>
       <c r="B46" t="n">
-        <v>86957</v>
+        <v>92813</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3674</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5237,10 +5238,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696217</v>
+        <v>695821</v>
       </c>
       <c r="R46" t="n">
-        <v>6617368</v>
+        <v>6617383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5299,32 +5300,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171379</v>
+        <v>129171417</v>
       </c>
       <c r="B47" t="n">
-        <v>86945</v>
+        <v>86958</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003296</v>
+        <v>3674</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5334,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696222</v>
+        <v>696217</v>
       </c>
       <c r="R47" t="n">
-        <v>6617388</v>
+        <v>6617368</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,7 +5379,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171415</v>
+        <v>129171407</v>
       </c>
       <c r="B5" t="n">
-        <v>86958</v>
+        <v>8439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,34 +1057,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696173</v>
+        <v>695742</v>
       </c>
       <c r="R5" t="n">
-        <v>6617344</v>
+        <v>6617264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,6 +1134,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,53 +1153,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171368</v>
+        <v>129174965</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>104174</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695888</v>
+        <v>696247</v>
       </c>
       <c r="R6" t="n">
-        <v>6617461</v>
+        <v>6617382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,22 +1238,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171407</v>
+        <v>129171403</v>
       </c>
       <c r="B7" t="n">
-        <v>8439</v>
+        <v>100894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,43 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695742</v>
+        <v>696219</v>
       </c>
       <c r="R7" t="n">
-        <v>6617264</v>
+        <v>6617372</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1355,45 +1347,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129174965</v>
+        <v>129171368</v>
       </c>
       <c r="B8" t="n">
-        <v>104172</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696247</v>
+        <v>695888</v>
       </c>
       <c r="R8" t="n">
-        <v>6617382</v>
+        <v>6617461</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,22 +1440,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171403</v>
+        <v>129171415</v>
       </c>
       <c r="B9" t="n">
-        <v>100892</v>
+        <v>86958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696219</v>
+        <v>696173</v>
       </c>
       <c r="R9" t="n">
-        <v>6617372</v>
+        <v>6617344</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1753,40 +1753,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171374</v>
+        <v>129171404</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>8439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1796,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696142</v>
+        <v>695939</v>
       </c>
       <c r="R12" t="n">
-        <v>6617341</v>
+        <v>6617438</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,6 +1841,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1858,7 +1860,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171404</v>
+        <v>129171405</v>
       </c>
       <c r="B13" t="n">
         <v>8439</v>
@@ -1902,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695939</v>
+        <v>695875</v>
       </c>
       <c r="R13" t="n">
-        <v>6617438</v>
+        <v>6617394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,41 +1967,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171405</v>
+        <v>129171374</v>
       </c>
       <c r="B14" t="n">
-        <v>8439</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2009,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695875</v>
+        <v>696142</v>
       </c>
       <c r="R14" t="n">
-        <v>6617394</v>
+        <v>6617341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2054,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>129171392</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>129174970</v>
       </c>
       <c r="B16" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129171416</v>
+        <v>129171409</v>
       </c>
       <c r="B19" t="n">
-        <v>86958</v>
+        <v>8439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,34 +2509,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696215</v>
+        <v>696020</v>
       </c>
       <c r="R19" t="n">
-        <v>6617356</v>
+        <v>6617274</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,6 +2586,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2595,10 +2605,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171409</v>
+        <v>129171416</v>
       </c>
       <c r="B20" t="n">
-        <v>8439</v>
+        <v>86958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,43 +2616,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696020</v>
+        <v>696215</v>
       </c>
       <c r="R20" t="n">
-        <v>6617274</v>
+        <v>6617356</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2684,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>129171385</v>
       </c>
       <c r="B21" t="n">
-        <v>98738</v>
+        <v>98739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>129174969</v>
       </c>
       <c r="B22" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>129171383</v>
       </c>
       <c r="B24" t="n">
-        <v>98738</v>
+        <v>98739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3200,37 +3200,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129171401</v>
+        <v>129171367</v>
       </c>
       <c r="B26" t="n">
-        <v>92857</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3238,10 +3243,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695690</v>
+        <v>696155</v>
       </c>
       <c r="R26" t="n">
-        <v>6617259</v>
+        <v>6617505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3282,7 +3287,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3301,10 +3305,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171386</v>
+        <v>129171401</v>
       </c>
       <c r="B27" t="n">
-        <v>58097</v>
+        <v>92858</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3312,34 +3316,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696062</v>
+        <v>695690</v>
       </c>
       <c r="R27" t="n">
-        <v>6617338</v>
+        <v>6617259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3380,6 +3387,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3398,53 +3406,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171367</v>
+        <v>129171386</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>58097</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696155</v>
+        <v>696062</v>
       </c>
       <c r="R28" t="n">
-        <v>6617505</v>
+        <v>6617338</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,44 +3503,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171395</v>
+        <v>129171363</v>
       </c>
       <c r="B29" t="n">
-        <v>87061</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3624</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696012</v>
+        <v>695974</v>
       </c>
       <c r="R29" t="n">
-        <v>6617292</v>
+        <v>6617238</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,7 +3582,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,45 +3600,44 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171363</v>
+        <v>129171395</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>87061</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>3624</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695974</v>
+        <v>696012</v>
       </c>
       <c r="R30" t="n">
-        <v>6617238</v>
+        <v>6617292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,6 +3678,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>129171371</v>
       </c>
       <c r="B32" t="n">
-        <v>96050</v>
+        <v>96051</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171375</v>
+        <v>129171412</v>
       </c>
       <c r="B34" t="n">
-        <v>91313</v>
+        <v>86958</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695740</v>
+        <v>695978</v>
       </c>
       <c r="R34" t="n">
-        <v>6617273</v>
+        <v>6617179</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171406</v>
+        <v>129171375</v>
       </c>
       <c r="B35" t="n">
-        <v>8439</v>
+        <v>91313</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4096,43 +4096,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>3215</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695870</v>
+        <v>695740</v>
       </c>
       <c r="R35" t="n">
-        <v>6617363</v>
+        <v>6617273</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,7 +4164,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4192,10 +4182,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171412</v>
+        <v>129171406</v>
       </c>
       <c r="B36" t="n">
-        <v>86958</v>
+        <v>8439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4203,34 +4193,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695978</v>
+        <v>695870</v>
       </c>
       <c r="R36" t="n">
-        <v>6617179</v>
+        <v>6617363</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4271,6 +4270,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>129171391</v>
       </c>
       <c r="B37" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129171393</v>
       </c>
       <c r="B39" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171384</v>
+        <v>129171377</v>
       </c>
       <c r="B40" t="n">
-        <v>98738</v>
+        <v>91313</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695740</v>
+        <v>696216</v>
       </c>
       <c r="R40" t="n">
-        <v>6617273</v>
+        <v>6617354</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129171377</v>
+        <v>129171384</v>
       </c>
       <c r="B42" t="n">
-        <v>91313</v>
+        <v>98739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696216</v>
+        <v>695740</v>
       </c>
       <c r="R42" t="n">
-        <v>6617354</v>
+        <v>6617273</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4906,45 +4906,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129171369</v>
+        <v>129171382</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>98739</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695729</v>
+        <v>695889</v>
       </c>
       <c r="R43" t="n">
-        <v>6617282</v>
+        <v>6617161</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4985,6 +4989,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5003,49 +5008,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129171382</v>
+        <v>129171369</v>
       </c>
       <c r="B44" t="n">
-        <v>98738</v>
+        <v>57887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695889</v>
+        <v>695729</v>
       </c>
       <c r="R44" t="n">
-        <v>6617161</v>
+        <v>6617282</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5087,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171379</v>
+        <v>129171378</v>
       </c>
       <c r="B45" t="n">
-        <v>86946</v>
+        <v>92814</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003296</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696222</v>
+        <v>695821</v>
       </c>
       <c r="R45" t="n">
-        <v>6617388</v>
+        <v>6617383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5184,7 +5184,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5203,32 +5202,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129171378</v>
+        <v>129171417</v>
       </c>
       <c r="B46" t="n">
-        <v>92813</v>
+        <v>86958</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>3674</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5238,10 +5237,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695821</v>
+        <v>696217</v>
       </c>
       <c r="R46" t="n">
-        <v>6617383</v>
+        <v>6617368</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5300,32 +5299,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171417</v>
+        <v>129171379</v>
       </c>
       <c r="B47" t="n">
-        <v>86958</v>
+        <v>86946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>6003296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5335,10 +5334,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696217</v>
+        <v>696222</v>
       </c>
       <c r="R47" t="n">
-        <v>6617368</v>
+        <v>6617388</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5379,6 +5378,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171407</v>
+        <v>129171403</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>100895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,43 +1057,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695742</v>
+        <v>696219</v>
       </c>
       <c r="R5" t="n">
-        <v>6617264</v>
+        <v>6617372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,7 +1125,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1156,7 +1146,7 @@
         <v>129174965</v>
       </c>
       <c r="B6" t="n">
-        <v>104174</v>
+        <v>104175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171403</v>
+        <v>129171415</v>
       </c>
       <c r="B7" t="n">
-        <v>100894</v>
+        <v>86958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696219</v>
+        <v>696173</v>
       </c>
       <c r="R7" t="n">
-        <v>6617372</v>
+        <v>6617344</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1452,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171415</v>
+        <v>129171407</v>
       </c>
       <c r="B9" t="n">
-        <v>86958</v>
+        <v>8439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,34 +1453,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696173</v>
+        <v>695742</v>
       </c>
       <c r="R9" t="n">
-        <v>6617344</v>
+        <v>6617264</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,6 +1530,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1753,41 +1753,40 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171404</v>
+        <v>129171374</v>
       </c>
       <c r="B12" t="n">
-        <v>8439</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1797,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695939</v>
+        <v>696142</v>
       </c>
       <c r="R12" t="n">
-        <v>6617438</v>
+        <v>6617341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1840,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1860,43 +1858,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171405</v>
+        <v>129171392</v>
       </c>
       <c r="B13" t="n">
-        <v>8439</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1904,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695875</v>
+        <v>695840</v>
       </c>
       <c r="R13" t="n">
-        <v>6617394</v>
+        <v>6617459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,42 +1972,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171374</v>
+        <v>129174970</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2010,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696142</v>
+        <v>696187</v>
       </c>
       <c r="R14" t="n">
-        <v>6617341</v>
+        <v>6617372</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,68 +2063,62 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171392</v>
+        <v>129171404</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>8439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2123,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695840</v>
+        <v>695939</v>
       </c>
       <c r="R15" t="n">
-        <v>6617459</v>
+        <v>6617438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,46 +2189,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129174970</v>
+        <v>129171405</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>8439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696187</v>
+        <v>695875</v>
       </c>
       <c r="R16" t="n">
-        <v>6617372</v>
+        <v>6617394</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,12 +2284,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129171409</v>
+        <v>129171416</v>
       </c>
       <c r="B19" t="n">
-        <v>8439</v>
+        <v>86958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,43 +2509,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696020</v>
+        <v>696215</v>
       </c>
       <c r="R19" t="n">
-        <v>6617274</v>
+        <v>6617356</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,7 +2577,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2605,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171416</v>
+        <v>129171409</v>
       </c>
       <c r="B20" t="n">
-        <v>86958</v>
+        <v>8439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,34 +2606,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696215</v>
+        <v>696020</v>
       </c>
       <c r="R20" t="n">
-        <v>6617356</v>
+        <v>6617274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2684,6 +2683,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>129171385</v>
       </c>
       <c r="B21" t="n">
-        <v>98739</v>
+        <v>98740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,57 +2799,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174969</v>
+        <v>129174973</v>
       </c>
       <c r="B22" t="n">
-        <v>98705</v>
+        <v>75159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696014</v>
+        <v>695810</v>
       </c>
       <c r="R22" t="n">
-        <v>6617322</v>
+        <v>6617339</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2878,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2909,45 +2896,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129174973</v>
+        <v>129174969</v>
       </c>
       <c r="B23" t="n">
-        <v>75159</v>
+        <v>98706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695810</v>
+        <v>696014</v>
       </c>
       <c r="R23" t="n">
-        <v>6617339</v>
+        <v>6617322</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,6 +2987,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>129171383</v>
       </c>
       <c r="B24" t="n">
-        <v>98739</v>
+        <v>98740</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129174972</v>
+        <v>129171401</v>
       </c>
       <c r="B25" t="n">
-        <v>75159</v>
+        <v>92858</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,34 +3114,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695758</v>
+        <v>695690</v>
       </c>
       <c r="R25" t="n">
-        <v>6617314</v>
+        <v>6617259</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3182,71 +3185,64 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129171367</v>
+        <v>129174972</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>75159</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696155</v>
+        <v>695758</v>
       </c>
       <c r="R26" t="n">
-        <v>6617505</v>
+        <v>6617314</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3293,22 +3289,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171401</v>
+        <v>129171386</v>
       </c>
       <c r="B27" t="n">
-        <v>92858</v>
+        <v>58097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3316,37 +3312,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695690</v>
+        <v>696062</v>
       </c>
       <c r="R27" t="n">
-        <v>6617259</v>
+        <v>6617338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,7 +3380,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3406,45 +3398,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171386</v>
+        <v>129171367</v>
       </c>
       <c r="B28" t="n">
-        <v>58097</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696062</v>
+        <v>696155</v>
       </c>
       <c r="R28" t="n">
-        <v>6617338</v>
+        <v>6617505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3797,7 +3797,7 @@
         <v>129171371</v>
       </c>
       <c r="B32" t="n">
-        <v>96051</v>
+        <v>96052</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>129171391</v>
       </c>
       <c r="B37" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129171393</v>
       </c>
       <c r="B39" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>129171384</v>
       </c>
       <c r="B42" t="n">
-        <v>98739</v>
+        <v>98740</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>129171382</v>
       </c>
       <c r="B43" t="n">
-        <v>98739</v>
+        <v>98740</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171403</v>
+        <v>129171415</v>
       </c>
       <c r="B5" t="n">
-        <v>100895</v>
+        <v>86961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696219</v>
+        <v>696173</v>
       </c>
       <c r="R5" t="n">
-        <v>6617372</v>
+        <v>6617344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129174965</v>
+        <v>129171407</v>
       </c>
       <c r="B6" t="n">
-        <v>104175</v>
+        <v>8439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,34 +1154,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696247</v>
+        <v>695742</v>
       </c>
       <c r="R6" t="n">
-        <v>6617382</v>
+        <v>6617264</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,63 +1231,72 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171415</v>
+        <v>129171368</v>
       </c>
       <c r="B7" t="n">
-        <v>86958</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696173</v>
+        <v>695888</v>
       </c>
       <c r="R7" t="n">
-        <v>6617344</v>
+        <v>6617461</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,53 +1355,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171368</v>
+        <v>129171403</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>100899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695888</v>
+        <v>696219</v>
       </c>
       <c r="R8" t="n">
-        <v>6617461</v>
+        <v>6617372</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171407</v>
+        <v>129174965</v>
       </c>
       <c r="B9" t="n">
-        <v>8439</v>
+        <v>104179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,43 +1463,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>695742</v>
+        <v>696247</v>
       </c>
       <c r="R9" t="n">
-        <v>6617264</v>
+        <v>6617382</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,19 +1531,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1659,7 +1659,7 @@
         <v>129171360</v>
       </c>
       <c r="B11" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171392</v>
+        <v>129174970</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,11 +1896,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1909,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695840</v>
+        <v>696187</v>
       </c>
       <c r="R13" t="n">
-        <v>6617459</v>
+        <v>6617372</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,58 +1956,55 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129174970</v>
+        <v>129171404</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>8439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2019,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696187</v>
+        <v>695939</v>
       </c>
       <c r="R14" t="n">
-        <v>6617372</v>
+        <v>6617438</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,19 +2063,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171404</v>
+        <v>129171405</v>
       </c>
       <c r="B15" t="n">
         <v>8439</v>
@@ -2126,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695939</v>
+        <v>695875</v>
       </c>
       <c r="R15" t="n">
-        <v>6617438</v>
+        <v>6617394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,43 +2182,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129171405</v>
+        <v>129171392</v>
       </c>
       <c r="B16" t="n">
-        <v>8439</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695875</v>
+        <v>695840</v>
       </c>
       <c r="R16" t="n">
-        <v>6617394</v>
+        <v>6617459</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2299,7 +2299,7 @@
         <v>129171402</v>
       </c>
       <c r="B17" t="n">
-        <v>88791</v>
+        <v>88794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>129171416</v>
       </c>
       <c r="B19" t="n">
-        <v>86958</v>
+        <v>86961</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171409</v>
+        <v>129171385</v>
       </c>
       <c r="B20" t="n">
-        <v>8439</v>
+        <v>98744</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,43 +2606,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696020</v>
+        <v>696217</v>
       </c>
       <c r="R20" t="n">
-        <v>6617274</v>
+        <v>6617392</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2674,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2702,10 +2692,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171385</v>
+        <v>129171409</v>
       </c>
       <c r="B21" t="n">
-        <v>98740</v>
+        <v>8439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,34 +2703,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696217</v>
+        <v>696020</v>
       </c>
       <c r="R21" t="n">
-        <v>6617392</v>
+        <v>6617274</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2781,6 +2780,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>129174973</v>
       </c>
       <c r="B22" t="n">
-        <v>75159</v>
+        <v>75161</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>129174969</v>
       </c>
       <c r="B23" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>129171383</v>
       </c>
       <c r="B24" t="n">
-        <v>98740</v>
+        <v>98744</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129171401</v>
+        <v>129174972</v>
       </c>
       <c r="B25" t="n">
-        <v>92858</v>
+        <v>75161</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,37 +3114,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695690</v>
+        <v>695758</v>
       </c>
       <c r="R25" t="n">
-        <v>6617259</v>
+        <v>6617314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,29 +3182,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129174972</v>
+        <v>129171386</v>
       </c>
       <c r="B26" t="n">
-        <v>75159</v>
+        <v>58097</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3215,21 +3211,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3239,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695758</v>
+        <v>696062</v>
       </c>
       <c r="R26" t="n">
-        <v>6617314</v>
+        <v>6617338</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3289,57 +3285,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171386</v>
+        <v>129171367</v>
       </c>
       <c r="B27" t="n">
-        <v>58097</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696062</v>
+        <v>696155</v>
       </c>
       <c r="R27" t="n">
-        <v>6617338</v>
+        <v>6617505</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3398,42 +3402,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171367</v>
+        <v>129171401</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>92861</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3441,10 +3440,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696155</v>
+        <v>695690</v>
       </c>
       <c r="R28" t="n">
-        <v>6617505</v>
+        <v>6617259</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,6 +3484,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>129171363</v>
       </c>
       <c r="B29" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>129171395</v>
       </c>
       <c r="B30" t="n">
-        <v>87061</v>
+        <v>87064</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>129171413</v>
       </c>
       <c r="B31" t="n">
-        <v>86958</v>
+        <v>86961</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>129171371</v>
       </c>
       <c r="B32" t="n">
-        <v>96052</v>
+        <v>96056</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>129171414</v>
       </c>
       <c r="B33" t="n">
-        <v>86958</v>
+        <v>86961</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3988,45 +3988,61 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171412</v>
+        <v>129171391</v>
       </c>
       <c r="B34" t="n">
-        <v>86958</v>
+        <v>98710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695978</v>
+        <v>695872</v>
       </c>
       <c r="R34" t="n">
-        <v>6617179</v>
+        <v>6617462</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,6 +4083,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4085,10 +4102,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171375</v>
+        <v>129171412</v>
       </c>
       <c r="B35" t="n">
-        <v>91313</v>
+        <v>86961</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4096,21 +4113,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4120,10 +4137,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695740</v>
+        <v>695978</v>
       </c>
       <c r="R35" t="n">
-        <v>6617273</v>
+        <v>6617179</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4182,10 +4199,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171406</v>
+        <v>129171375</v>
       </c>
       <c r="B36" t="n">
-        <v>8439</v>
+        <v>91316</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4193,43 +4210,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>3215</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695870</v>
+        <v>695740</v>
       </c>
       <c r="R36" t="n">
-        <v>6617363</v>
+        <v>6617273</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4278,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4289,50 +4296,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171391</v>
+        <v>129171406</v>
       </c>
       <c r="B37" t="n">
-        <v>98706</v>
+        <v>8439</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695872</v>
+        <v>695870</v>
       </c>
       <c r="R37" t="n">
-        <v>6617462</v>
+        <v>6617363</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4406,7 +4406,7 @@
         <v>129171394</v>
       </c>
       <c r="B38" t="n">
-        <v>91001</v>
+        <v>91004</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129171393</v>
       </c>
       <c r="B39" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>129171377</v>
       </c>
       <c r="B40" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>129171411</v>
       </c>
       <c r="B41" t="n">
-        <v>86958</v>
+        <v>86961</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>129171384</v>
       </c>
       <c r="B42" t="n">
-        <v>98740</v>
+        <v>98744</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4906,49 +4906,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129171382</v>
+        <v>129171369</v>
       </c>
       <c r="B43" t="n">
-        <v>98740</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695889</v>
+        <v>695729</v>
       </c>
       <c r="R43" t="n">
-        <v>6617161</v>
+        <v>6617282</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,7 +4985,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5008,45 +5003,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129171369</v>
+        <v>129171382</v>
       </c>
       <c r="B44" t="n">
-        <v>57887</v>
+        <v>98744</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695729</v>
+        <v>695889</v>
       </c>
       <c r="R44" t="n">
-        <v>6617282</v>
+        <v>6617161</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5087,6 +5086,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171378</v>
+        <v>129171379</v>
       </c>
       <c r="B45" t="n">
-        <v>92814</v>
+        <v>86949</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>6003296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695821</v>
+        <v>696222</v>
       </c>
       <c r="R45" t="n">
-        <v>6617383</v>
+        <v>6617388</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5184,6 +5184,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5205,7 +5206,7 @@
         <v>129171417</v>
       </c>
       <c r="B46" t="n">
-        <v>86958</v>
+        <v>86961</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5299,32 +5300,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171379</v>
+        <v>129171378</v>
       </c>
       <c r="B47" t="n">
-        <v>86946</v>
+        <v>92817</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003296</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5334,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696222</v>
+        <v>695821</v>
       </c>
       <c r="R47" t="n">
-        <v>6617388</v>
+        <v>6617383</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,7 +5379,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1143,43 +1143,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171407</v>
+        <v>129171368</v>
       </c>
       <c r="B6" t="n">
-        <v>8439</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695742</v>
+        <v>695888</v>
       </c>
       <c r="R6" t="n">
-        <v>6617264</v>
+        <v>6617461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1230,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,42 +1248,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171368</v>
+        <v>129171407</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>8439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1293,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695888</v>
+        <v>695742</v>
       </c>
       <c r="R7" t="n">
-        <v>6617461</v>
+        <v>6617264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,6 +1336,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2799,45 +2799,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174973</v>
+        <v>129174969</v>
       </c>
       <c r="B22" t="n">
-        <v>75161</v>
+        <v>98710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695810</v>
+        <v>696014</v>
       </c>
       <c r="R22" t="n">
-        <v>6617339</v>
+        <v>6617322</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2878,6 +2890,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2896,57 +2909,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129174969</v>
+        <v>129174973</v>
       </c>
       <c r="B23" t="n">
-        <v>98710</v>
+        <v>75161</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696014</v>
+        <v>695810</v>
       </c>
       <c r="R23" t="n">
-        <v>6617322</v>
+        <v>6617339</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2988,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3503,45 +3503,44 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171363</v>
+        <v>129171395</v>
       </c>
       <c r="B29" t="n">
-        <v>91543</v>
+        <v>87064</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>3624</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695974</v>
+        <v>696012</v>
       </c>
       <c r="R29" t="n">
-        <v>6617238</v>
+        <v>6617292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,6 +3581,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171395</v>
+        <v>129171413</v>
       </c>
       <c r="B30" t="n">
-        <v>87064</v>
+        <v>86961</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,33 +3611,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3624</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696012</v>
+        <v>695981</v>
       </c>
       <c r="R30" t="n">
-        <v>6617292</v>
+        <v>6617228</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,7 +3679,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171413</v>
+        <v>129171363</v>
       </c>
       <c r="B31" t="n">
-        <v>86961</v>
+        <v>91543</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695981</v>
+        <v>695974</v>
       </c>
       <c r="R31" t="n">
-        <v>6617228</v>
+        <v>6617238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4906,45 +4906,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129171369</v>
+        <v>129171382</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>98744</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695729</v>
+        <v>695889</v>
       </c>
       <c r="R43" t="n">
-        <v>6617282</v>
+        <v>6617161</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4985,6 +4989,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5003,49 +5008,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129171382</v>
+        <v>129171369</v>
       </c>
       <c r="B44" t="n">
-        <v>98744</v>
+        <v>57887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695889</v>
+        <v>695729</v>
       </c>
       <c r="R44" t="n">
-        <v>6617161</v>
+        <v>6617282</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5087,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171379</v>
+        <v>129171417</v>
       </c>
       <c r="B45" t="n">
-        <v>86949</v>
+        <v>86961</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003296</v>
+        <v>3674</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696222</v>
+        <v>696217</v>
       </c>
       <c r="R45" t="n">
-        <v>6617388</v>
+        <v>6617368</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5184,7 +5184,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5203,32 +5202,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129171417</v>
+        <v>129171378</v>
       </c>
       <c r="B46" t="n">
-        <v>86961</v>
+        <v>92817</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3674</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5238,10 +5237,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696217</v>
+        <v>695821</v>
       </c>
       <c r="R46" t="n">
-        <v>6617368</v>
+        <v>6617383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5300,32 +5299,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171378</v>
+        <v>129171379</v>
       </c>
       <c r="B47" t="n">
-        <v>92817</v>
+        <v>86949</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>6003296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5335,10 +5334,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>695821</v>
+        <v>696222</v>
       </c>
       <c r="R47" t="n">
-        <v>6617383</v>
+        <v>6617388</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5379,6 +5378,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>129171415</v>
       </c>
       <c r="B5" t="n">
-        <v>86961</v>
+        <v>86963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,42 +1143,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171368</v>
+        <v>129171407</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>8439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695888</v>
+        <v>695742</v>
       </c>
       <c r="R6" t="n">
-        <v>6617461</v>
+        <v>6617264</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,6 +1231,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1248,43 +1250,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171407</v>
+        <v>129171368</v>
       </c>
       <c r="B7" t="n">
-        <v>8439</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1292,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695742</v>
+        <v>695888</v>
       </c>
       <c r="R7" t="n">
-        <v>6617264</v>
+        <v>6617461</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1337,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>129171403</v>
       </c>
       <c r="B8" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>129174965</v>
       </c>
       <c r="B9" t="n">
-        <v>104179</v>
+        <v>104181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>129171360</v>
       </c>
       <c r="B11" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129174970</v>
+        <v>129171392</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1905,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696187</v>
+        <v>695840</v>
       </c>
       <c r="R13" t="n">
-        <v>6617372</v>
+        <v>6617459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,55 +1960,58 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171404</v>
+        <v>129174970</v>
       </c>
       <c r="B14" t="n">
-        <v>8439</v>
+        <v>98712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2012,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695939</v>
+        <v>696187</v>
       </c>
       <c r="R14" t="n">
-        <v>6617438</v>
+        <v>6617372</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,19 +2070,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171405</v>
+        <v>129171404</v>
       </c>
       <c r="B15" t="n">
         <v>8439</v>
@@ -2119,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695875</v>
+        <v>695939</v>
       </c>
       <c r="R15" t="n">
-        <v>6617394</v>
+        <v>6617438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2182,50 +2189,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129171392</v>
+        <v>129171405</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>8439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695840</v>
+        <v>695875</v>
       </c>
       <c r="R16" t="n">
-        <v>6617459</v>
+        <v>6617394</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,45 +2296,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129171402</v>
+        <v>129171373</v>
       </c>
       <c r="B17" t="n">
-        <v>88794</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4405</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>695905</v>
+        <v>695846</v>
       </c>
       <c r="R17" t="n">
-        <v>6617158</v>
+        <v>6617165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,53 +2401,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129171373</v>
+        <v>129171402</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>88796</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>4405</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695846</v>
+        <v>695905</v>
       </c>
       <c r="R18" t="n">
-        <v>6617165</v>
+        <v>6617158</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
         <v>129171416</v>
       </c>
       <c r="B19" t="n">
-        <v>86961</v>
+        <v>86963</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>129171385</v>
       </c>
       <c r="B20" t="n">
-        <v>98744</v>
+        <v>98746</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>129174969</v>
       </c>
       <c r="B22" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>129171383</v>
       </c>
       <c r="B24" t="n">
-        <v>98744</v>
+        <v>98746</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129174972</v>
+        <v>129171401</v>
       </c>
       <c r="B25" t="n">
-        <v>75161</v>
+        <v>92863</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,34 +3114,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695758</v>
+        <v>695690</v>
       </c>
       <c r="R25" t="n">
-        <v>6617314</v>
+        <v>6617259</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3182,28 +3185,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129171386</v>
+        <v>129174972</v>
       </c>
       <c r="B26" t="n">
-        <v>58097</v>
+        <v>75161</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3211,21 +3215,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3239,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696062</v>
+        <v>695758</v>
       </c>
       <c r="R26" t="n">
-        <v>6617338</v>
+        <v>6617314</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3285,65 +3289,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171367</v>
+        <v>129171386</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>58097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696155</v>
+        <v>696062</v>
       </c>
       <c r="R27" t="n">
-        <v>6617505</v>
+        <v>6617338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,37 +3398,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171401</v>
+        <v>129171367</v>
       </c>
       <c r="B28" t="n">
-        <v>92861</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3440,10 +3441,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695690</v>
+        <v>696155</v>
       </c>
       <c r="R28" t="n">
-        <v>6617259</v>
+        <v>6617505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,7 +3485,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171395</v>
+        <v>129171413</v>
       </c>
       <c r="B29" t="n">
-        <v>87064</v>
+        <v>86963</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,33 +3514,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3624</v>
+        <v>3674</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696012</v>
+        <v>695981</v>
       </c>
       <c r="R29" t="n">
-        <v>6617292</v>
+        <v>6617228</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,7 +3582,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171413</v>
+        <v>129171395</v>
       </c>
       <c r="B30" t="n">
-        <v>86961</v>
+        <v>87066</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,34 +3611,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3674</v>
+        <v>3624</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695981</v>
+        <v>696012</v>
       </c>
       <c r="R30" t="n">
-        <v>6617228</v>
+        <v>6617292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,6 +3678,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>129171363</v>
       </c>
       <c r="B31" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>129171371</v>
       </c>
       <c r="B32" t="n">
-        <v>96056</v>
+        <v>96058</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>129171414</v>
       </c>
       <c r="B33" t="n">
-        <v>86961</v>
+        <v>86963</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>129171391</v>
       </c>
       <c r="B34" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171412</v>
+        <v>129171406</v>
       </c>
       <c r="B35" t="n">
-        <v>86961</v>
+        <v>8439</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4113,34 +4113,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695978</v>
+        <v>695870</v>
       </c>
       <c r="R35" t="n">
-        <v>6617179</v>
+        <v>6617363</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4181,6 +4190,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4199,10 +4209,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171375</v>
+        <v>129171412</v>
       </c>
       <c r="B36" t="n">
-        <v>91316</v>
+        <v>86963</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4210,21 +4220,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4234,10 +4244,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695740</v>
+        <v>695978</v>
       </c>
       <c r="R36" t="n">
-        <v>6617273</v>
+        <v>6617179</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4296,10 +4306,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171406</v>
+        <v>129171375</v>
       </c>
       <c r="B37" t="n">
-        <v>8439</v>
+        <v>91318</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4307,43 +4317,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>3215</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695870</v>
+        <v>695740</v>
       </c>
       <c r="R37" t="n">
-        <v>6617363</v>
+        <v>6617273</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4384,7 +4385,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>129171394</v>
       </c>
       <c r="B38" t="n">
-        <v>91004</v>
+        <v>91006</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129171393</v>
       </c>
       <c r="B39" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171377</v>
+        <v>129171384</v>
       </c>
       <c r="B40" t="n">
-        <v>91316</v>
+        <v>98746</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696216</v>
+        <v>695740</v>
       </c>
       <c r="R40" t="n">
-        <v>6617354</v>
+        <v>6617273</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129171411</v>
+        <v>129171377</v>
       </c>
       <c r="B41" t="n">
-        <v>86961</v>
+        <v>91318</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695740</v>
+        <v>696216</v>
       </c>
       <c r="R41" t="n">
-        <v>6617275</v>
+        <v>6617354</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129171384</v>
+        <v>129171411</v>
       </c>
       <c r="B42" t="n">
-        <v>98744</v>
+        <v>86963</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         <v>695740</v>
       </c>
       <c r="R42" t="n">
-        <v>6617273</v>
+        <v>6617275</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4906,49 +4906,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129171382</v>
+        <v>129171369</v>
       </c>
       <c r="B43" t="n">
-        <v>98744</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695889</v>
+        <v>695729</v>
       </c>
       <c r="R43" t="n">
-        <v>6617161</v>
+        <v>6617282</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,7 +4985,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5008,45 +5003,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129171369</v>
+        <v>129171382</v>
       </c>
       <c r="B44" t="n">
-        <v>57887</v>
+        <v>98746</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695729</v>
+        <v>695889</v>
       </c>
       <c r="R44" t="n">
-        <v>6617282</v>
+        <v>6617161</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5087,6 +5086,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>129171417</v>
       </c>
       <c r="B45" t="n">
-        <v>86961</v>
+        <v>86963</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>129171378</v>
       </c>
       <c r="B46" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>129171379</v>
       </c>
       <c r="B47" t="n">
-        <v>86949</v>
+        <v>86951</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171415</v>
+        <v>129171407</v>
       </c>
       <c r="B5" t="n">
-        <v>86963</v>
+        <v>8439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,34 +1057,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696173</v>
+        <v>695742</v>
       </c>
       <c r="R5" t="n">
-        <v>6617344</v>
+        <v>6617264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,6 +1134,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,43 +1153,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171407</v>
+        <v>129171368</v>
       </c>
       <c r="B6" t="n">
-        <v>8439</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695742</v>
+        <v>695888</v>
       </c>
       <c r="R6" t="n">
-        <v>6617264</v>
+        <v>6617461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1240,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1243,60 +1251,52 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171368</v>
+        <v>129171403</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>100905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695888</v>
+        <v>696219</v>
       </c>
       <c r="R7" t="n">
-        <v>6617461</v>
+        <v>6617372</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171403</v>
+        <v>129174965</v>
       </c>
       <c r="B8" t="n">
-        <v>100901</v>
+        <v>104185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696219</v>
+        <v>696247</v>
       </c>
       <c r="R8" t="n">
-        <v>6617372</v>
+        <v>6617382</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,22 +1440,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129174965</v>
+        <v>129171415</v>
       </c>
       <c r="B9" t="n">
-        <v>104181</v>
+        <v>86967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696247</v>
+        <v>696173</v>
       </c>
       <c r="R9" t="n">
-        <v>6617382</v>
+        <v>6617344</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,12 +1537,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1659,7 +1659,7 @@
         <v>129171360</v>
       </c>
       <c r="B11" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1861,7 +1861,7 @@
         <v>129171392</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>129174970</v>
       </c>
       <c r="B14" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2296,53 +2296,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129171373</v>
+        <v>129171402</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>88800</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>4405</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>695846</v>
+        <v>695905</v>
       </c>
       <c r="R17" t="n">
-        <v>6617165</v>
+        <v>6617158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,45 +2393,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129171402</v>
+        <v>129171373</v>
       </c>
       <c r="B18" t="n">
-        <v>88796</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4405</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695905</v>
+        <v>695846</v>
       </c>
       <c r="R18" t="n">
-        <v>6617158</v>
+        <v>6617165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
         <v>129171416</v>
       </c>
       <c r="B19" t="n">
-        <v>86963</v>
+        <v>86967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171385</v>
+        <v>129171409</v>
       </c>
       <c r="B20" t="n">
-        <v>98746</v>
+        <v>8439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,34 +2606,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696217</v>
+        <v>696020</v>
       </c>
       <c r="R20" t="n">
-        <v>6617392</v>
+        <v>6617274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2674,6 +2683,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2692,10 +2702,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171409</v>
+        <v>129171385</v>
       </c>
       <c r="B21" t="n">
-        <v>8439</v>
+        <v>98750</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,43 +2713,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696020</v>
+        <v>696217</v>
       </c>
       <c r="R21" t="n">
-        <v>6617274</v>
+        <v>6617392</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,7 +2781,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2799,57 +2799,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174969</v>
+        <v>129174973</v>
       </c>
       <c r="B22" t="n">
-        <v>98712</v>
+        <v>75161</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696014</v>
+        <v>695810</v>
       </c>
       <c r="R22" t="n">
-        <v>6617322</v>
+        <v>6617339</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2878,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2909,45 +2896,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129174973</v>
+        <v>129174969</v>
       </c>
       <c r="B23" t="n">
-        <v>75161</v>
+        <v>98716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695810</v>
+        <v>696014</v>
       </c>
       <c r="R23" t="n">
-        <v>6617339</v>
+        <v>6617322</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,6 +2987,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>129171383</v>
       </c>
       <c r="B24" t="n">
-        <v>98746</v>
+        <v>98750</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>129171401</v>
       </c>
       <c r="B25" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,45 +3301,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171386</v>
+        <v>129171367</v>
       </c>
       <c r="B27" t="n">
-        <v>58097</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696062</v>
+        <v>696155</v>
       </c>
       <c r="R27" t="n">
-        <v>6617338</v>
+        <v>6617505</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3391,60 +3399,52 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171367</v>
+        <v>129171386</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>58097</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696155</v>
+        <v>696062</v>
       </c>
       <c r="R28" t="n">
-        <v>6617505</v>
+        <v>6617338</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,32 +3503,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171413</v>
+        <v>129171363</v>
       </c>
       <c r="B29" t="n">
-        <v>86963</v>
+        <v>91549</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695981</v>
+        <v>695974</v>
       </c>
       <c r="R29" t="n">
-        <v>6617228</v>
+        <v>6617238</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3603,7 +3603,7 @@
         <v>129171395</v>
       </c>
       <c r="B30" t="n">
-        <v>87066</v>
+        <v>87070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171363</v>
+        <v>129171413</v>
       </c>
       <c r="B31" t="n">
-        <v>91545</v>
+        <v>86967</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695974</v>
+        <v>695981</v>
       </c>
       <c r="R31" t="n">
-        <v>6617238</v>
+        <v>6617228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3797,7 +3797,7 @@
         <v>129171371</v>
       </c>
       <c r="B32" t="n">
-        <v>96058</v>
+        <v>96062</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>129171414</v>
       </c>
       <c r="B33" t="n">
-        <v>86963</v>
+        <v>86967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3988,61 +3988,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171391</v>
+        <v>129171412</v>
       </c>
       <c r="B34" t="n">
-        <v>98712</v>
+        <v>86967</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695872</v>
+        <v>695978</v>
       </c>
       <c r="R34" t="n">
-        <v>6617462</v>
+        <v>6617179</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4083,7 +4067,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4102,10 +4085,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171406</v>
+        <v>129171375</v>
       </c>
       <c r="B35" t="n">
-        <v>8439</v>
+        <v>91322</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4113,43 +4096,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>3215</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695870</v>
+        <v>695740</v>
       </c>
       <c r="R35" t="n">
-        <v>6617363</v>
+        <v>6617273</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4190,7 +4164,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4209,45 +4182,61 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171412</v>
+        <v>129171391</v>
       </c>
       <c r="B36" t="n">
-        <v>86963</v>
+        <v>98716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695978</v>
+        <v>695872</v>
       </c>
       <c r="R36" t="n">
-        <v>6617179</v>
+        <v>6617462</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4288,6 +4277,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4306,10 +4296,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171375</v>
+        <v>129171406</v>
       </c>
       <c r="B37" t="n">
-        <v>91318</v>
+        <v>8439</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4317,34 +4307,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3215</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695740</v>
+        <v>695870</v>
       </c>
       <c r="R37" t="n">
-        <v>6617273</v>
+        <v>6617363</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4385,6 +4384,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>129171394</v>
       </c>
       <c r="B38" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129171393</v>
       </c>
       <c r="B39" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>129171384</v>
       </c>
       <c r="B40" t="n">
-        <v>98746</v>
+        <v>98750</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>129171377</v>
       </c>
       <c r="B41" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>129171411</v>
       </c>
       <c r="B42" t="n">
-        <v>86963</v>
+        <v>86967</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
         <v>129171382</v>
       </c>
       <c r="B44" t="n">
-        <v>98746</v>
+        <v>98750</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>129171417</v>
       </c>
       <c r="B45" t="n">
-        <v>86963</v>
+        <v>86967</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5202,32 +5202,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129171378</v>
+        <v>129171379</v>
       </c>
       <c r="B46" t="n">
-        <v>92819</v>
+        <v>86955</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>6003296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695821</v>
+        <v>696222</v>
       </c>
       <c r="R46" t="n">
-        <v>6617383</v>
+        <v>6617388</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5281,6 +5281,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5299,32 +5300,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171379</v>
+        <v>129171378</v>
       </c>
       <c r="B47" t="n">
-        <v>86951</v>
+        <v>92823</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003296</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5334,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696222</v>
+        <v>695821</v>
       </c>
       <c r="R47" t="n">
-        <v>6617388</v>
+        <v>6617383</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,7 +5379,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,43 +1046,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171407</v>
+        <v>129171368</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695742</v>
+        <v>695888</v>
       </c>
       <c r="R5" t="n">
-        <v>6617264</v>
+        <v>6617461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,7 +1133,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1153,53 +1151,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171368</v>
+        <v>129174965</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>104195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695888</v>
+        <v>696247</v>
       </c>
       <c r="R6" t="n">
-        <v>6617461</v>
+        <v>6617382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,22 +1236,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171403</v>
+        <v>129171415</v>
       </c>
       <c r="B7" t="n">
-        <v>100905</v>
+        <v>86968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,21 +1259,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696219</v>
+        <v>696173</v>
       </c>
       <c r="R7" t="n">
-        <v>6617372</v>
+        <v>6617344</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129174965</v>
+        <v>129171407</v>
       </c>
       <c r="B8" t="n">
-        <v>104185</v>
+        <v>8439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,34 +1356,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696247</v>
+        <v>695742</v>
       </c>
       <c r="R8" t="n">
-        <v>6617382</v>
+        <v>6617264</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,28 +1433,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171415</v>
+        <v>129171403</v>
       </c>
       <c r="B9" t="n">
-        <v>86967</v>
+        <v>100913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3674</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696173</v>
+        <v>696219</v>
       </c>
       <c r="R9" t="n">
-        <v>6617344</v>
+        <v>6617372</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
         <v>129171360</v>
       </c>
       <c r="B11" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,49 +1746,57 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171374</v>
+        <v>129171392</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696142</v>
+        <v>695840</v>
       </c>
       <c r="R12" t="n">
-        <v>6617341</v>
+        <v>6617459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,6 +1848,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1858,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171392</v>
+        <v>129174970</v>
       </c>
       <c r="B13" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,11 +1905,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1909,10 +1914,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695840</v>
+        <v>696187</v>
       </c>
       <c r="R13" t="n">
-        <v>6617459</v>
+        <v>6617372</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,58 +1965,55 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129174970</v>
+        <v>129171404</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>8439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2019,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696187</v>
+        <v>695939</v>
       </c>
       <c r="R14" t="n">
-        <v>6617372</v>
+        <v>6617438</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,19 +2072,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171404</v>
+        <v>129171405</v>
       </c>
       <c r="B15" t="n">
         <v>8439</v>
@@ -2126,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695939</v>
+        <v>695875</v>
       </c>
       <c r="R15" t="n">
-        <v>6617438</v>
+        <v>6617394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,41 +2191,40 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129171405</v>
+        <v>129171374</v>
       </c>
       <c r="B16" t="n">
-        <v>8439</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2233,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695875</v>
+        <v>696142</v>
       </c>
       <c r="R16" t="n">
-        <v>6617394</v>
+        <v>6617341</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2278,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>129171402</v>
       </c>
       <c r="B17" t="n">
-        <v>88800</v>
+        <v>88801</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>129171416</v>
       </c>
       <c r="B19" t="n">
-        <v>86967</v>
+        <v>86968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171409</v>
+        <v>129171385</v>
       </c>
       <c r="B20" t="n">
-        <v>8439</v>
+        <v>98758</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,43 +2606,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696020</v>
+        <v>696217</v>
       </c>
       <c r="R20" t="n">
-        <v>6617274</v>
+        <v>6617392</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2674,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2702,10 +2692,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171385</v>
+        <v>129171409</v>
       </c>
       <c r="B21" t="n">
-        <v>98750</v>
+        <v>8439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,34 +2703,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696217</v>
+        <v>696020</v>
       </c>
       <c r="R21" t="n">
-        <v>6617392</v>
+        <v>6617274</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2781,6 +2780,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>129174969</v>
       </c>
       <c r="B23" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>129171383</v>
       </c>
       <c r="B24" t="n">
-        <v>98750</v>
+        <v>98758</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129171401</v>
+        <v>129174972</v>
       </c>
       <c r="B25" t="n">
-        <v>92867</v>
+        <v>75161</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,37 +3114,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695690</v>
+        <v>695758</v>
       </c>
       <c r="R25" t="n">
-        <v>6617259</v>
+        <v>6617314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,29 +3182,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129174972</v>
+        <v>129171401</v>
       </c>
       <c r="B26" t="n">
-        <v>75161</v>
+        <v>92868</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3215,34 +3211,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695758</v>
+        <v>695690</v>
       </c>
       <c r="R26" t="n">
-        <v>6617314</v>
+        <v>6617259</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3283,18 +3282,19 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3506,7 +3506,7 @@
         <v>129171363</v>
       </c>
       <c r="B29" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3603,7 +3603,7 @@
         <v>129171395</v>
       </c>
       <c r="B30" t="n">
-        <v>87070</v>
+        <v>87071</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>129171413</v>
       </c>
       <c r="B31" t="n">
-        <v>86967</v>
+        <v>86968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129171371</v>
+        <v>129171414</v>
       </c>
       <c r="B32" t="n">
-        <v>96062</v>
+        <v>86968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695971</v>
+        <v>696014</v>
       </c>
       <c r="R32" t="n">
-        <v>6617182</v>
+        <v>6617265</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129171414</v>
+        <v>129171371</v>
       </c>
       <c r="B33" t="n">
-        <v>86967</v>
+        <v>96070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696014</v>
+        <v>695971</v>
       </c>
       <c r="R33" t="n">
-        <v>6617265</v>
+        <v>6617182</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3988,45 +3988,61 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171412</v>
+        <v>129171391</v>
       </c>
       <c r="B34" t="n">
-        <v>86967</v>
+        <v>98724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695978</v>
+        <v>695872</v>
       </c>
       <c r="R34" t="n">
-        <v>6617179</v>
+        <v>6617462</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,6 +4083,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4085,10 +4102,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171375</v>
+        <v>129171412</v>
       </c>
       <c r="B35" t="n">
-        <v>91322</v>
+        <v>86968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4096,21 +4113,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4120,10 +4137,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695740</v>
+        <v>695978</v>
       </c>
       <c r="R35" t="n">
-        <v>6617273</v>
+        <v>6617179</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4182,61 +4199,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171391</v>
+        <v>129171375</v>
       </c>
       <c r="B36" t="n">
-        <v>98716</v>
+        <v>91323</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695872</v>
+        <v>695740</v>
       </c>
       <c r="R36" t="n">
-        <v>6617462</v>
+        <v>6617273</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4277,7 +4278,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>129171394</v>
       </c>
       <c r="B38" t="n">
-        <v>91010</v>
+        <v>91011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129171393</v>
       </c>
       <c r="B39" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171384</v>
+        <v>129171411</v>
       </c>
       <c r="B40" t="n">
-        <v>98750</v>
+        <v>86968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4653,7 +4653,7 @@
         <v>695740</v>
       </c>
       <c r="R40" t="n">
-        <v>6617273</v>
+        <v>6617275</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4715,7 +4715,7 @@
         <v>129171377</v>
       </c>
       <c r="B41" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129171411</v>
+        <v>129171384</v>
       </c>
       <c r="B42" t="n">
-        <v>86967</v>
+        <v>98758</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         <v>695740</v>
       </c>
       <c r="R42" t="n">
-        <v>6617275</v>
+        <v>6617273</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
         <v>129171382</v>
       </c>
       <c r="B44" t="n">
-        <v>98750</v>
+        <v>98758</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171417</v>
+        <v>129171378</v>
       </c>
       <c r="B45" t="n">
-        <v>86967</v>
+        <v>92824</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3674</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696217</v>
+        <v>695821</v>
       </c>
       <c r="R45" t="n">
-        <v>6617368</v>
+        <v>6617383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5202,32 +5202,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129171379</v>
+        <v>129171417</v>
       </c>
       <c r="B46" t="n">
-        <v>86955</v>
+        <v>86968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003296</v>
+        <v>3674</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696222</v>
+        <v>696217</v>
       </c>
       <c r="R46" t="n">
-        <v>6617388</v>
+        <v>6617368</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5281,7 +5281,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5300,32 +5299,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171378</v>
+        <v>129171379</v>
       </c>
       <c r="B47" t="n">
-        <v>92823</v>
+        <v>86956</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>6003296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5335,10 +5334,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>695821</v>
+        <v>696222</v>
       </c>
       <c r="R47" t="n">
-        <v>6617383</v>
+        <v>6617388</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5379,6 +5378,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,53 +1046,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171368</v>
+        <v>129171415</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>86968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695888</v>
+        <v>696173</v>
       </c>
       <c r="R5" t="n">
-        <v>6617461</v>
+        <v>6617344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,45 +1143,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129174965</v>
+        <v>129171368</v>
       </c>
       <c r="B6" t="n">
-        <v>104195</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696247</v>
+        <v>695888</v>
       </c>
       <c r="R6" t="n">
-        <v>6617382</v>
+        <v>6617461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,22 +1236,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171415</v>
+        <v>129171403</v>
       </c>
       <c r="B7" t="n">
-        <v>86968</v>
+        <v>100913</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,21 +1259,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696173</v>
+        <v>696219</v>
       </c>
       <c r="R7" t="n">
-        <v>6617344</v>
+        <v>6617372</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171407</v>
+        <v>129174965</v>
       </c>
       <c r="B8" t="n">
-        <v>8439</v>
+        <v>104195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,43 +1356,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695742</v>
+        <v>696247</v>
       </c>
       <c r="R8" t="n">
-        <v>6617264</v>
+        <v>6617382</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,29 +1424,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171403</v>
+        <v>129171407</v>
       </c>
       <c r="B9" t="n">
-        <v>100913</v>
+        <v>8439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,34 +1453,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696219</v>
+        <v>695742</v>
       </c>
       <c r="R9" t="n">
-        <v>6617372</v>
+        <v>6617264</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,6 +1530,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171392</v>
+        <v>129174970</v>
       </c>
       <c r="B12" t="n">
         <v>98724</v>
@@ -1791,11 +1791,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1804,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695840</v>
+        <v>696187</v>
       </c>
       <c r="R12" t="n">
-        <v>6617459</v>
+        <v>6617372</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,58 +1851,55 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129174970</v>
+        <v>129171404</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>8439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1914,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696187</v>
+        <v>695939</v>
       </c>
       <c r="R13" t="n">
-        <v>6617372</v>
+        <v>6617438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,19 +1958,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171404</v>
+        <v>129171405</v>
       </c>
       <c r="B14" t="n">
         <v>8439</v>
@@ -2021,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695939</v>
+        <v>695875</v>
       </c>
       <c r="R14" t="n">
-        <v>6617438</v>
+        <v>6617394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,41 +2077,40 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171405</v>
+        <v>129171374</v>
       </c>
       <c r="B15" t="n">
-        <v>8439</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2128,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695875</v>
+        <v>696142</v>
       </c>
       <c r="R15" t="n">
-        <v>6617394</v>
+        <v>6617341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,7 +2164,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2191,42 +2182,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129171374</v>
+        <v>129171392</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2234,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696142</v>
+        <v>695840</v>
       </c>
       <c r="R16" t="n">
-        <v>6617341</v>
+        <v>6617459</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,6 +2277,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129171414</v>
+        <v>129171371</v>
       </c>
       <c r="B32" t="n">
-        <v>86968</v>
+        <v>96070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>2818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696014</v>
+        <v>695971</v>
       </c>
       <c r="R32" t="n">
-        <v>6617265</v>
+        <v>6617182</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129171371</v>
+        <v>129171414</v>
       </c>
       <c r="B33" t="n">
-        <v>96070</v>
+        <v>86968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2818</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695971</v>
+        <v>696014</v>
       </c>
       <c r="R33" t="n">
-        <v>6617182</v>
+        <v>6617265</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171412</v>
+        <v>129171406</v>
       </c>
       <c r="B35" t="n">
-        <v>86968</v>
+        <v>8439</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4113,34 +4113,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695978</v>
+        <v>695870</v>
       </c>
       <c r="R35" t="n">
-        <v>6617179</v>
+        <v>6617363</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4181,6 +4190,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4199,10 +4209,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171375</v>
+        <v>129171412</v>
       </c>
       <c r="B36" t="n">
-        <v>91323</v>
+        <v>86968</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4210,21 +4220,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4234,10 +4244,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695740</v>
+        <v>695978</v>
       </c>
       <c r="R36" t="n">
-        <v>6617273</v>
+        <v>6617179</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4296,10 +4306,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171406</v>
+        <v>129171375</v>
       </c>
       <c r="B37" t="n">
-        <v>8439</v>
+        <v>91323</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4307,43 +4317,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>3215</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695870</v>
+        <v>695740</v>
       </c>
       <c r="R37" t="n">
-        <v>6617363</v>
+        <v>6617273</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4384,7 +4385,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171411</v>
+        <v>129171377</v>
       </c>
       <c r="B40" t="n">
-        <v>86968</v>
+        <v>91323</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695740</v>
+        <v>696216</v>
       </c>
       <c r="R40" t="n">
-        <v>6617275</v>
+        <v>6617354</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129171377</v>
+        <v>129171411</v>
       </c>
       <c r="B41" t="n">
-        <v>91323</v>
+        <v>86968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696216</v>
+        <v>695740</v>
       </c>
       <c r="R41" t="n">
-        <v>6617354</v>
+        <v>6617275</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1753,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129174970</v>
+        <v>129171392</v>
       </c>
       <c r="B12" t="n">
         <v>98724</v>
@@ -1791,7 +1791,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1800,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696187</v>
+        <v>695840</v>
       </c>
       <c r="R12" t="n">
-        <v>6617372</v>
+        <v>6617459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,55 +1855,58 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171404</v>
+        <v>129174970</v>
       </c>
       <c r="B13" t="n">
-        <v>8439</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1907,10 +1914,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695939</v>
+        <v>696187</v>
       </c>
       <c r="R13" t="n">
-        <v>6617438</v>
+        <v>6617372</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,19 +1965,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171405</v>
+        <v>129171404</v>
       </c>
       <c r="B14" t="n">
         <v>8439</v>
@@ -2014,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695875</v>
+        <v>695939</v>
       </c>
       <c r="R14" t="n">
-        <v>6617394</v>
+        <v>6617438</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,40 +2084,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171374</v>
+        <v>129171405</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>8439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2120,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696142</v>
+        <v>695875</v>
       </c>
       <c r="R15" t="n">
-        <v>6617341</v>
+        <v>6617394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,6 +2172,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2182,50 +2191,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129171392</v>
+        <v>129171374</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695840</v>
+        <v>696142</v>
       </c>
       <c r="R16" t="n">
-        <v>6617459</v>
+        <v>6617341</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2278,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -3200,37 +3200,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129171401</v>
+        <v>129171367</v>
       </c>
       <c r="B26" t="n">
-        <v>92868</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3238,10 +3243,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695690</v>
+        <v>696155</v>
       </c>
       <c r="R26" t="n">
-        <v>6617259</v>
+        <v>6617505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3282,7 +3287,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3301,42 +3305,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171367</v>
+        <v>129171401</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>92868</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3344,10 +3343,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696155</v>
+        <v>695690</v>
       </c>
       <c r="R27" t="n">
-        <v>6617505</v>
+        <v>6617259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,6 +3387,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3988,61 +3988,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171391</v>
+        <v>129171375</v>
       </c>
       <c r="B34" t="n">
-        <v>98724</v>
+        <v>91323</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695872</v>
+        <v>695740</v>
       </c>
       <c r="R34" t="n">
-        <v>6617462</v>
+        <v>6617273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4083,7 +4067,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4102,43 +4085,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171406</v>
+        <v>129171391</v>
       </c>
       <c r="B35" t="n">
-        <v>8439</v>
+        <v>98724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4146,10 +4136,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695870</v>
+        <v>695872</v>
       </c>
       <c r="R35" t="n">
-        <v>6617363</v>
+        <v>6617462</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4209,10 +4199,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171412</v>
+        <v>129171406</v>
       </c>
       <c r="B36" t="n">
-        <v>86968</v>
+        <v>8439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4220,34 +4210,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695978</v>
+        <v>695870</v>
       </c>
       <c r="R36" t="n">
-        <v>6617179</v>
+        <v>6617363</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4288,6 +4287,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171375</v>
+        <v>129171412</v>
       </c>
       <c r="B37" t="n">
-        <v>91323</v>
+        <v>86968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4317,21 +4317,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695740</v>
+        <v>695978</v>
       </c>
       <c r="R37" t="n">
-        <v>6617273</v>
+        <v>6617179</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171403</v>
+        <v>129171407</v>
       </c>
       <c r="B7" t="n">
-        <v>100913</v>
+        <v>8439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,34 +1259,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696219</v>
+        <v>695742</v>
       </c>
       <c r="R7" t="n">
-        <v>6617372</v>
+        <v>6617264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,6 +1336,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1345,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129174965</v>
+        <v>129171403</v>
       </c>
       <c r="B8" t="n">
-        <v>104195</v>
+        <v>100916</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696247</v>
+        <v>696219</v>
       </c>
       <c r="R8" t="n">
-        <v>6617382</v>
+        <v>6617372</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,22 +1440,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171407</v>
+        <v>129174965</v>
       </c>
       <c r="B9" t="n">
-        <v>8439</v>
+        <v>104198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,43 +1463,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>695742</v>
+        <v>696247</v>
       </c>
       <c r="R9" t="n">
-        <v>6617264</v>
+        <v>6617382</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,19 +1531,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1659,7 +1659,7 @@
         <v>129171360</v>
       </c>
       <c r="B11" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,50 +1753,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171392</v>
+        <v>129171374</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1804,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695840</v>
+        <v>696142</v>
       </c>
       <c r="R12" t="n">
-        <v>6617459</v>
+        <v>6617341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1840,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1867,46 +1858,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129174970</v>
+        <v>129171404</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>8439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1914,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696187</v>
+        <v>695939</v>
       </c>
       <c r="R13" t="n">
-        <v>6617372</v>
+        <v>6617438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,19 +1953,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171404</v>
+        <v>129171405</v>
       </c>
       <c r="B14" t="n">
         <v>8439</v>
@@ -2021,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695939</v>
+        <v>695875</v>
       </c>
       <c r="R14" t="n">
-        <v>6617438</v>
+        <v>6617394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,43 +2072,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171405</v>
+        <v>129171392</v>
       </c>
       <c r="B15" t="n">
-        <v>8439</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2128,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695875</v>
+        <v>695840</v>
       </c>
       <c r="R15" t="n">
-        <v>6617394</v>
+        <v>6617459</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,42 +2186,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129171374</v>
+        <v>129174970</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2234,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696142</v>
+        <v>696187</v>
       </c>
       <c r="R16" t="n">
-        <v>6617341</v>
+        <v>6617372</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,18 +2277,19 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2598,7 +2598,7 @@
         <v>129171385</v>
       </c>
       <c r="B20" t="n">
-        <v>98758</v>
+        <v>98761</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>129174969</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>129171383</v>
       </c>
       <c r="B24" t="n">
-        <v>98758</v>
+        <v>98761</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3200,42 +3200,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129171367</v>
+        <v>129171401</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>92871</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3243,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696155</v>
+        <v>695690</v>
       </c>
       <c r="R26" t="n">
-        <v>6617505</v>
+        <v>6617259</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3287,6 +3282,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3305,10 +3301,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171401</v>
+        <v>129171386</v>
       </c>
       <c r="B27" t="n">
-        <v>92868</v>
+        <v>58097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3316,37 +3312,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695690</v>
+        <v>696062</v>
       </c>
       <c r="R27" t="n">
-        <v>6617259</v>
+        <v>6617338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,7 +3380,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3406,45 +3398,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171386</v>
+        <v>129171367</v>
       </c>
       <c r="B28" t="n">
-        <v>58097</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696062</v>
+        <v>696155</v>
       </c>
       <c r="R28" t="n">
-        <v>6617338</v>
+        <v>6617505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,45 +3503,44 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171363</v>
+        <v>129171395</v>
       </c>
       <c r="B29" t="n">
-        <v>91550</v>
+        <v>87071</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>3624</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695974</v>
+        <v>696012</v>
       </c>
       <c r="R29" t="n">
-        <v>6617238</v>
+        <v>6617292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,6 +3581,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171395</v>
+        <v>129171413</v>
       </c>
       <c r="B30" t="n">
-        <v>87071</v>
+        <v>86968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,33 +3611,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3624</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696012</v>
+        <v>695981</v>
       </c>
       <c r="R30" t="n">
-        <v>6617292</v>
+        <v>6617228</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,7 +3679,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171413</v>
+        <v>129171363</v>
       </c>
       <c r="B31" t="n">
-        <v>86968</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695981</v>
+        <v>695974</v>
       </c>
       <c r="R31" t="n">
-        <v>6617228</v>
+        <v>6617238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129171371</v>
+        <v>129171414</v>
       </c>
       <c r="B32" t="n">
-        <v>96070</v>
+        <v>86968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695971</v>
+        <v>696014</v>
       </c>
       <c r="R32" t="n">
-        <v>6617182</v>
+        <v>6617265</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129171414</v>
+        <v>129171371</v>
       </c>
       <c r="B33" t="n">
-        <v>86968</v>
+        <v>96073</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696014</v>
+        <v>695971</v>
       </c>
       <c r="R33" t="n">
-        <v>6617265</v>
+        <v>6617182</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171375</v>
+        <v>129171412</v>
       </c>
       <c r="B34" t="n">
-        <v>91323</v>
+        <v>86968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695740</v>
+        <v>695978</v>
       </c>
       <c r="R34" t="n">
-        <v>6617273</v>
+        <v>6617179</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4085,50 +4085,43 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171391</v>
+        <v>129171406</v>
       </c>
       <c r="B35" t="n">
-        <v>98724</v>
+        <v>8439</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4136,10 +4129,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695872</v>
+        <v>695870</v>
       </c>
       <c r="R35" t="n">
-        <v>6617462</v>
+        <v>6617363</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4199,43 +4192,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171406</v>
+        <v>129171391</v>
       </c>
       <c r="B36" t="n">
-        <v>8439</v>
+        <v>98727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695870</v>
+        <v>695872</v>
       </c>
       <c r="R36" t="n">
-        <v>6617363</v>
+        <v>6617462</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171412</v>
+        <v>129171375</v>
       </c>
       <c r="B37" t="n">
-        <v>86968</v>
+        <v>91326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4317,21 +4317,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695978</v>
+        <v>695740</v>
       </c>
       <c r="R37" t="n">
-        <v>6617179</v>
+        <v>6617273</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4406,7 +4406,7 @@
         <v>129171394</v>
       </c>
       <c r="B38" t="n">
-        <v>91011</v>
+        <v>91014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129171393</v>
       </c>
       <c r="B39" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>129171377</v>
       </c>
       <c r="B40" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>129171384</v>
       </c>
       <c r="B42" t="n">
-        <v>98758</v>
+        <v>98761</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>129171382</v>
       </c>
       <c r="B44" t="n">
-        <v>98758</v>
+        <v>98761</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171378</v>
+        <v>129171379</v>
       </c>
       <c r="B45" t="n">
-        <v>92824</v>
+        <v>86956</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>6003296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695821</v>
+        <v>696222</v>
       </c>
       <c r="R45" t="n">
-        <v>6617383</v>
+        <v>6617388</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5184,6 +5184,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5202,32 +5203,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129171417</v>
+        <v>129171378</v>
       </c>
       <c r="B46" t="n">
-        <v>86968</v>
+        <v>92827</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3674</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5237,10 +5238,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696217</v>
+        <v>695821</v>
       </c>
       <c r="R46" t="n">
-        <v>6617368</v>
+        <v>6617383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5299,32 +5300,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171379</v>
+        <v>129171417</v>
       </c>
       <c r="B47" t="n">
-        <v>86956</v>
+        <v>86968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003296</v>
+        <v>3674</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5334,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696222</v>
+        <v>696217</v>
       </c>
       <c r="R47" t="n">
-        <v>6617388</v>
+        <v>6617368</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,7 +5379,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171415</v>
+        <v>129171403</v>
       </c>
       <c r="B5" t="n">
-        <v>86968</v>
+        <v>100916</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696173</v>
+        <v>696219</v>
       </c>
       <c r="R5" t="n">
-        <v>6617344</v>
+        <v>6617372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,53 +1143,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171368</v>
+        <v>129174965</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>104198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695888</v>
+        <v>696247</v>
       </c>
       <c r="R6" t="n">
-        <v>6617461</v>
+        <v>6617382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,55 +1228,54 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171407</v>
+        <v>129171368</v>
       </c>
       <c r="B7" t="n">
-        <v>8439</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1292,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695742</v>
+        <v>695888</v>
       </c>
       <c r="R7" t="n">
-        <v>6617264</v>
+        <v>6617461</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1327,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1355,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171403</v>
+        <v>129171415</v>
       </c>
       <c r="B8" t="n">
-        <v>100916</v>
+        <v>86968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1356,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696219</v>
+        <v>696173</v>
       </c>
       <c r="R8" t="n">
-        <v>6617372</v>
+        <v>6617344</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129174965</v>
+        <v>129171407</v>
       </c>
       <c r="B9" t="n">
-        <v>104198</v>
+        <v>8439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,34 +1453,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696247</v>
+        <v>695742</v>
       </c>
       <c r="R9" t="n">
-        <v>6617382</v>
+        <v>6617264</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,18 +1530,19 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1753,40 +1753,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171374</v>
+        <v>129171405</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>8439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1796,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696142</v>
+        <v>695875</v>
       </c>
       <c r="R12" t="n">
-        <v>6617341</v>
+        <v>6617394</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,6 +1841,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1965,41 +1967,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171405</v>
+        <v>129171374</v>
       </c>
       <c r="B14" t="n">
-        <v>8439</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2009,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695875</v>
+        <v>696142</v>
       </c>
       <c r="R14" t="n">
-        <v>6617394</v>
+        <v>6617341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2054,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171385</v>
+        <v>129171409</v>
       </c>
       <c r="B20" t="n">
-        <v>98761</v>
+        <v>8439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,34 +2606,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696217</v>
+        <v>696020</v>
       </c>
       <c r="R20" t="n">
-        <v>6617392</v>
+        <v>6617274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2674,6 +2683,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2692,10 +2702,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171409</v>
+        <v>129171385</v>
       </c>
       <c r="B21" t="n">
-        <v>8439</v>
+        <v>98761</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,43 +2713,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696020</v>
+        <v>696217</v>
       </c>
       <c r="R21" t="n">
-        <v>6617274</v>
+        <v>6617392</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,7 +2781,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129174972</v>
+        <v>129171401</v>
       </c>
       <c r="B25" t="n">
-        <v>75161</v>
+        <v>92871</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,34 +3114,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695758</v>
+        <v>695690</v>
       </c>
       <c r="R25" t="n">
-        <v>6617314</v>
+        <v>6617259</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3182,28 +3185,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129171401</v>
+        <v>129174972</v>
       </c>
       <c r="B26" t="n">
-        <v>92871</v>
+        <v>75161</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3211,37 +3215,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695690</v>
+        <v>695758</v>
       </c>
       <c r="R26" t="n">
-        <v>6617259</v>
+        <v>6617314</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3282,19 +3283,18 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3503,44 +3503,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171395</v>
+        <v>129171363</v>
       </c>
       <c r="B29" t="n">
-        <v>87071</v>
+        <v>91553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3624</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696012</v>
+        <v>695974</v>
       </c>
       <c r="R29" t="n">
-        <v>6617292</v>
+        <v>6617238</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,7 +3582,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171413</v>
+        <v>129171395</v>
       </c>
       <c r="B30" t="n">
-        <v>86968</v>
+        <v>87071</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,34 +3611,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3674</v>
+        <v>3624</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695981</v>
+        <v>696012</v>
       </c>
       <c r="R30" t="n">
-        <v>6617228</v>
+        <v>6617292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,6 +3678,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171363</v>
+        <v>129171413</v>
       </c>
       <c r="B31" t="n">
-        <v>91553</v>
+        <v>86968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695974</v>
+        <v>695981</v>
       </c>
       <c r="R31" t="n">
-        <v>6617238</v>
+        <v>6617228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129171414</v>
+        <v>129171371</v>
       </c>
       <c r="B32" t="n">
-        <v>86968</v>
+        <v>96073</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>2818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696014</v>
+        <v>695971</v>
       </c>
       <c r="R32" t="n">
-        <v>6617265</v>
+        <v>6617182</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129171371</v>
+        <v>129171414</v>
       </c>
       <c r="B33" t="n">
-        <v>96073</v>
+        <v>86968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2818</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695971</v>
+        <v>696014</v>
       </c>
       <c r="R33" t="n">
-        <v>6617182</v>
+        <v>6617265</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171412</v>
+        <v>129171375</v>
       </c>
       <c r="B34" t="n">
-        <v>86968</v>
+        <v>91326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695978</v>
+        <v>695740</v>
       </c>
       <c r="R34" t="n">
-        <v>6617179</v>
+        <v>6617273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171406</v>
+        <v>129171412</v>
       </c>
       <c r="B35" t="n">
-        <v>8439</v>
+        <v>86968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4096,43 +4096,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695870</v>
+        <v>695978</v>
       </c>
       <c r="R35" t="n">
-        <v>6617363</v>
+        <v>6617179</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,7 +4164,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4306,10 +4296,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171375</v>
+        <v>129171406</v>
       </c>
       <c r="B37" t="n">
-        <v>91326</v>
+        <v>8439</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4317,34 +4307,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3215</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695740</v>
+        <v>695870</v>
       </c>
       <c r="R37" t="n">
-        <v>6617273</v>
+        <v>6617363</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4385,6 +4384,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171377</v>
+        <v>129171411</v>
       </c>
       <c r="B40" t="n">
-        <v>91326</v>
+        <v>86968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696216</v>
+        <v>695740</v>
       </c>
       <c r="R40" t="n">
-        <v>6617354</v>
+        <v>6617275</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129171411</v>
+        <v>129171377</v>
       </c>
       <c r="B41" t="n">
-        <v>86968</v>
+        <v>91326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695740</v>
+        <v>696216</v>
       </c>
       <c r="R41" t="n">
-        <v>6617275</v>
+        <v>6617354</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171403</v>
+        <v>129171415</v>
       </c>
       <c r="B5" t="n">
-        <v>100916</v>
+        <v>86968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696219</v>
+        <v>696173</v>
       </c>
       <c r="R5" t="n">
-        <v>6617372</v>
+        <v>6617344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129174965</v>
+        <v>129171403</v>
       </c>
       <c r="B6" t="n">
-        <v>104198</v>
+        <v>100916</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696247</v>
+        <v>696219</v>
       </c>
       <c r="R6" t="n">
-        <v>6617382</v>
+        <v>6617372</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,65 +1228,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171368</v>
+        <v>129174965</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>104198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695888</v>
+        <v>696247</v>
       </c>
       <c r="R7" t="n">
-        <v>6617461</v>
+        <v>6617382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,22 +1325,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171415</v>
+        <v>129171407</v>
       </c>
       <c r="B8" t="n">
-        <v>86968</v>
+        <v>8439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,34 +1348,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696173</v>
+        <v>695742</v>
       </c>
       <c r="R8" t="n">
-        <v>6617344</v>
+        <v>6617264</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,6 +1425,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1442,43 +1444,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171407</v>
+        <v>129171368</v>
       </c>
       <c r="B9" t="n">
-        <v>8439</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1486,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>695742</v>
+        <v>695888</v>
       </c>
       <c r="R9" t="n">
-        <v>6617264</v>
+        <v>6617461</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1531,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1753,41 +1753,40 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171405</v>
+        <v>129171374</v>
       </c>
       <c r="B12" t="n">
-        <v>8439</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1797,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695875</v>
+        <v>696142</v>
       </c>
       <c r="R12" t="n">
-        <v>6617394</v>
+        <v>6617341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1840,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1860,43 +1858,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171404</v>
+        <v>129171392</v>
       </c>
       <c r="B13" t="n">
-        <v>8439</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1904,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695939</v>
+        <v>695840</v>
       </c>
       <c r="R13" t="n">
-        <v>6617438</v>
+        <v>6617459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,42 +1972,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171374</v>
+        <v>129174970</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2010,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696142</v>
+        <v>696187</v>
       </c>
       <c r="R14" t="n">
-        <v>6617341</v>
+        <v>6617372</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,68 +2063,62 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171392</v>
+        <v>129171404</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>8439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2123,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695840</v>
+        <v>695939</v>
       </c>
       <c r="R15" t="n">
-        <v>6617459</v>
+        <v>6617438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,46 +2189,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129174970</v>
+        <v>129171405</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>8439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696187</v>
+        <v>695875</v>
       </c>
       <c r="R16" t="n">
-        <v>6617372</v>
+        <v>6617394</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,12 +2284,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171409</v>
+        <v>129171385</v>
       </c>
       <c r="B20" t="n">
-        <v>8439</v>
+        <v>98761</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,43 +2606,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696020</v>
+        <v>696217</v>
       </c>
       <c r="R20" t="n">
-        <v>6617274</v>
+        <v>6617392</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2674,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2702,10 +2692,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171385</v>
+        <v>129171409</v>
       </c>
       <c r="B21" t="n">
-        <v>98761</v>
+        <v>8439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,34 +2703,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696217</v>
+        <v>696020</v>
       </c>
       <c r="R21" t="n">
-        <v>6617392</v>
+        <v>6617274</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2781,6 +2780,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3301,45 +3301,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171386</v>
+        <v>129171367</v>
       </c>
       <c r="B27" t="n">
-        <v>58097</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696062</v>
+        <v>696155</v>
       </c>
       <c r="R27" t="n">
-        <v>6617338</v>
+        <v>6617505</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3398,53 +3406,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171367</v>
+        <v>129171386</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>58097</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696155</v>
+        <v>696062</v>
       </c>
       <c r="R28" t="n">
-        <v>6617505</v>
+        <v>6617338</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,45 +3503,44 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171363</v>
+        <v>129171395</v>
       </c>
       <c r="B29" t="n">
-        <v>91553</v>
+        <v>87071</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>3624</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695974</v>
+        <v>696012</v>
       </c>
       <c r="R29" t="n">
-        <v>6617238</v>
+        <v>6617292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,6 +3581,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171395</v>
+        <v>129171413</v>
       </c>
       <c r="B30" t="n">
-        <v>87071</v>
+        <v>86968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,33 +3611,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3624</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696012</v>
+        <v>695981</v>
       </c>
       <c r="R30" t="n">
-        <v>6617292</v>
+        <v>6617228</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,7 +3679,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171413</v>
+        <v>129171363</v>
       </c>
       <c r="B31" t="n">
-        <v>86968</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695981</v>
+        <v>695974</v>
       </c>
       <c r="R31" t="n">
-        <v>6617228</v>
+        <v>6617238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3988,45 +3988,61 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171375</v>
+        <v>129171391</v>
       </c>
       <c r="B34" t="n">
-        <v>91326</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695740</v>
+        <v>695872</v>
       </c>
       <c r="R34" t="n">
-        <v>6617273</v>
+        <v>6617462</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,6 +4083,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4182,61 +4199,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171391</v>
+        <v>129171375</v>
       </c>
       <c r="B36" t="n">
-        <v>98727</v>
+        <v>91326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695872</v>
+        <v>695740</v>
       </c>
       <c r="R36" t="n">
-        <v>6617462</v>
+        <v>6617273</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4277,7 +4278,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171411</v>
+        <v>129171377</v>
       </c>
       <c r="B40" t="n">
-        <v>86968</v>
+        <v>91326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695740</v>
+        <v>696216</v>
       </c>
       <c r="R40" t="n">
-        <v>6617275</v>
+        <v>6617354</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129171377</v>
+        <v>129171411</v>
       </c>
       <c r="B41" t="n">
-        <v>91326</v>
+        <v>86968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696216</v>
+        <v>695740</v>
       </c>
       <c r="R41" t="n">
-        <v>6617354</v>
+        <v>6617275</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4906,45 +4906,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129171369</v>
+        <v>129171382</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>98761</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695729</v>
+        <v>695889</v>
       </c>
       <c r="R43" t="n">
-        <v>6617282</v>
+        <v>6617161</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4985,6 +4989,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5003,49 +5008,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129171382</v>
+        <v>129171369</v>
       </c>
       <c r="B44" t="n">
-        <v>98761</v>
+        <v>57887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695889</v>
+        <v>695729</v>
       </c>
       <c r="R44" t="n">
-        <v>6617161</v>
+        <v>6617282</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5087,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1143,45 +1143,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171403</v>
+        <v>129171368</v>
       </c>
       <c r="B6" t="n">
-        <v>100916</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696219</v>
+        <v>695888</v>
       </c>
       <c r="R6" t="n">
-        <v>6617372</v>
+        <v>6617461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129174965</v>
+        <v>129171403</v>
       </c>
       <c r="B7" t="n">
-        <v>104198</v>
+        <v>100916</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1259,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696247</v>
+        <v>696219</v>
       </c>
       <c r="R7" t="n">
-        <v>6617382</v>
+        <v>6617372</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,22 +1333,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171407</v>
+        <v>129174965</v>
       </c>
       <c r="B8" t="n">
-        <v>8439</v>
+        <v>104198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,43 +1356,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695742</v>
+        <v>696247</v>
       </c>
       <c r="R8" t="n">
-        <v>6617264</v>
+        <v>6617382</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,61 +1424,61 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171368</v>
+        <v>129171407</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>8439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1487,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>695888</v>
+        <v>695742</v>
       </c>
       <c r="R9" t="n">
-        <v>6617461</v>
+        <v>6617264</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,6 +1530,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1753,42 +1753,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171374</v>
+        <v>129174970</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696142</v>
+        <v>696187</v>
       </c>
       <c r="R12" t="n">
-        <v>6617341</v>
+        <v>6617372</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,68 +1844,61 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171392</v>
+        <v>129171374</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1909,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695840</v>
+        <v>696142</v>
       </c>
       <c r="R13" t="n">
-        <v>6617459</v>
+        <v>6617341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,7 +1950,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1972,46 +1968,43 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129174970</v>
+        <v>129171404</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>8439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2019,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696187</v>
+        <v>695939</v>
       </c>
       <c r="R14" t="n">
-        <v>6617372</v>
+        <v>6617438</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,19 +2063,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171404</v>
+        <v>129171405</v>
       </c>
       <c r="B15" t="n">
         <v>8439</v>
@@ -2126,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695939</v>
+        <v>695875</v>
       </c>
       <c r="R15" t="n">
-        <v>6617438</v>
+        <v>6617394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,43 +2182,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129171405</v>
+        <v>129171392</v>
       </c>
       <c r="B16" t="n">
-        <v>8439</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695875</v>
+        <v>695840</v>
       </c>
       <c r="R16" t="n">
-        <v>6617394</v>
+        <v>6617459</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171385</v>
+        <v>129171409</v>
       </c>
       <c r="B20" t="n">
-        <v>98761</v>
+        <v>8439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,34 +2606,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696217</v>
+        <v>696020</v>
       </c>
       <c r="R20" t="n">
-        <v>6617392</v>
+        <v>6617274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2674,6 +2683,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2692,10 +2702,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171409</v>
+        <v>129171385</v>
       </c>
       <c r="B21" t="n">
-        <v>8439</v>
+        <v>98761</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,43 +2713,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696020</v>
+        <v>696217</v>
       </c>
       <c r="R21" t="n">
-        <v>6617274</v>
+        <v>6617392</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,7 +2781,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3301,53 +3301,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171367</v>
+        <v>129171386</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>58097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696155</v>
+        <v>696062</v>
       </c>
       <c r="R27" t="n">
-        <v>6617505</v>
+        <v>6617338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,45 +3398,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171386</v>
+        <v>129171367</v>
       </c>
       <c r="B28" t="n">
-        <v>58097</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696062</v>
+        <v>696155</v>
       </c>
       <c r="R28" t="n">
-        <v>6617338</v>
+        <v>6617505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3988,61 +3988,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171391</v>
+        <v>129171412</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>86968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695872</v>
+        <v>695978</v>
       </c>
       <c r="R34" t="n">
-        <v>6617462</v>
+        <v>6617179</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4083,7 +4067,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4102,10 +4085,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171412</v>
+        <v>129171375</v>
       </c>
       <c r="B35" t="n">
-        <v>86968</v>
+        <v>91326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4113,21 +4096,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4137,10 +4120,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695978</v>
+        <v>695740</v>
       </c>
       <c r="R35" t="n">
-        <v>6617179</v>
+        <v>6617273</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4199,10 +4182,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171375</v>
+        <v>129171406</v>
       </c>
       <c r="B36" t="n">
-        <v>91326</v>
+        <v>8439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4210,34 +4193,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695740</v>
+        <v>695870</v>
       </c>
       <c r="R36" t="n">
-        <v>6617273</v>
+        <v>6617363</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4278,6 +4270,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4296,43 +4289,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171406</v>
+        <v>129171391</v>
       </c>
       <c r="B37" t="n">
-        <v>8439</v>
+        <v>98727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695870</v>
+        <v>695872</v>
       </c>
       <c r="R37" t="n">
-        <v>6617363</v>
+        <v>6617462</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171379</v>
+        <v>129171378</v>
       </c>
       <c r="B45" t="n">
-        <v>86956</v>
+        <v>92827</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003296</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696222</v>
+        <v>695821</v>
       </c>
       <c r="R45" t="n">
-        <v>6617388</v>
+        <v>6617383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5184,7 +5184,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5203,32 +5202,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129171378</v>
+        <v>129171417</v>
       </c>
       <c r="B46" t="n">
-        <v>92827</v>
+        <v>86968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>3674</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5238,10 +5237,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695821</v>
+        <v>696217</v>
       </c>
       <c r="R46" t="n">
-        <v>6617383</v>
+        <v>6617368</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5300,32 +5299,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171417</v>
+        <v>129171379</v>
       </c>
       <c r="B47" t="n">
-        <v>86968</v>
+        <v>86956</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>6003296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5335,10 +5334,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696217</v>
+        <v>696222</v>
       </c>
       <c r="R47" t="n">
-        <v>6617368</v>
+        <v>6617388</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5379,6 +5378,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171415</v>
+        <v>129171403</v>
       </c>
       <c r="B5" t="n">
-        <v>86968</v>
+        <v>100916</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696173</v>
+        <v>696219</v>
       </c>
       <c r="R5" t="n">
-        <v>6617344</v>
+        <v>6617372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,53 +1143,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171368</v>
+        <v>129174965</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>104198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695888</v>
+        <v>696247</v>
       </c>
       <c r="R6" t="n">
-        <v>6617461</v>
+        <v>6617382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171403</v>
+        <v>129171415</v>
       </c>
       <c r="B7" t="n">
-        <v>100916</v>
+        <v>86968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1283,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696219</v>
+        <v>696173</v>
       </c>
       <c r="R7" t="n">
-        <v>6617372</v>
+        <v>6617344</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,45 +1337,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129174965</v>
+        <v>129171368</v>
       </c>
       <c r="B8" t="n">
-        <v>104198</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696247</v>
+        <v>695888</v>
       </c>
       <c r="R8" t="n">
-        <v>6617382</v>
+        <v>6617461</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,12 +1430,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1753,46 +1753,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129174970</v>
+        <v>129171374</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1800,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696187</v>
+        <v>696142</v>
       </c>
       <c r="R12" t="n">
-        <v>6617372</v>
+        <v>6617341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,59 +1840,59 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171374</v>
+        <v>129171404</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>8439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1906,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696142</v>
+        <v>695939</v>
       </c>
       <c r="R13" t="n">
-        <v>6617341</v>
+        <v>6617438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,6 +1946,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1968,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171404</v>
+        <v>129171405</v>
       </c>
       <c r="B14" t="n">
         <v>8439</v>
@@ -2012,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695939</v>
+        <v>695875</v>
       </c>
       <c r="R14" t="n">
-        <v>6617438</v>
+        <v>6617394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2075,43 +2072,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171405</v>
+        <v>129171392</v>
       </c>
       <c r="B15" t="n">
-        <v>8439</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2119,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695875</v>
+        <v>695840</v>
       </c>
       <c r="R15" t="n">
-        <v>6617394</v>
+        <v>6617459</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2182,7 +2186,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129171392</v>
+        <v>129174970</v>
       </c>
       <c r="B16" t="n">
         <v>98727</v>
@@ -2220,11 +2224,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695840</v>
+        <v>696187</v>
       </c>
       <c r="R16" t="n">
-        <v>6617459</v>
+        <v>6617372</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,57 +2284,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129171402</v>
+        <v>129171373</v>
       </c>
       <c r="B17" t="n">
-        <v>88801</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4405</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>695905</v>
+        <v>695846</v>
       </c>
       <c r="R17" t="n">
-        <v>6617158</v>
+        <v>6617165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,53 +2401,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129171373</v>
+        <v>129171402</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>88801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>4405</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695846</v>
+        <v>695905</v>
       </c>
       <c r="R18" t="n">
-        <v>6617165</v>
+        <v>6617158</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129171416</v>
+        <v>129171385</v>
       </c>
       <c r="B19" t="n">
-        <v>86968</v>
+        <v>98761</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,21 +2509,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696215</v>
+        <v>696217</v>
       </c>
       <c r="R19" t="n">
-        <v>6617356</v>
+        <v>6617392</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171409</v>
+        <v>129171416</v>
       </c>
       <c r="B20" t="n">
-        <v>8439</v>
+        <v>86968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,43 +2606,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696020</v>
+        <v>696215</v>
       </c>
       <c r="R20" t="n">
-        <v>6617274</v>
+        <v>6617356</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2674,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2702,10 +2692,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171385</v>
+        <v>129171409</v>
       </c>
       <c r="B21" t="n">
-        <v>98761</v>
+        <v>8439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,34 +2703,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696217</v>
+        <v>696020</v>
       </c>
       <c r="R21" t="n">
-        <v>6617392</v>
+        <v>6617274</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2781,6 +2780,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2799,45 +2799,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174973</v>
+        <v>129174969</v>
       </c>
       <c r="B22" t="n">
-        <v>75161</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695810</v>
+        <v>696014</v>
       </c>
       <c r="R22" t="n">
-        <v>6617339</v>
+        <v>6617322</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2878,6 +2890,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2896,57 +2909,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129174969</v>
+        <v>129174973</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>75161</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696014</v>
+        <v>695810</v>
       </c>
       <c r="R23" t="n">
-        <v>6617322</v>
+        <v>6617339</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2988,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3503,44 +3503,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171395</v>
+        <v>129171363</v>
       </c>
       <c r="B29" t="n">
-        <v>87071</v>
+        <v>91553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3624</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696012</v>
+        <v>695974</v>
       </c>
       <c r="R29" t="n">
-        <v>6617292</v>
+        <v>6617238</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,7 +3582,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171413</v>
+        <v>129171395</v>
       </c>
       <c r="B30" t="n">
-        <v>86968</v>
+        <v>87071</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,34 +3611,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3674</v>
+        <v>3624</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695981</v>
+        <v>696012</v>
       </c>
       <c r="R30" t="n">
-        <v>6617228</v>
+        <v>6617292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,6 +3678,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171363</v>
+        <v>129171413</v>
       </c>
       <c r="B31" t="n">
-        <v>91553</v>
+        <v>86968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695974</v>
+        <v>695981</v>
       </c>
       <c r="R31" t="n">
-        <v>6617238</v>
+        <v>6617228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171412</v>
+        <v>129171406</v>
       </c>
       <c r="B34" t="n">
-        <v>86968</v>
+        <v>8439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,34 +3999,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695978</v>
+        <v>695870</v>
       </c>
       <c r="R34" t="n">
-        <v>6617179</v>
+        <v>6617363</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,6 +4076,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4085,10 +4095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171375</v>
+        <v>129171412</v>
       </c>
       <c r="B35" t="n">
-        <v>91326</v>
+        <v>86968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4096,21 +4106,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4120,10 +4130,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695740</v>
+        <v>695978</v>
       </c>
       <c r="R35" t="n">
-        <v>6617273</v>
+        <v>6617179</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4182,10 +4192,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171406</v>
+        <v>129171375</v>
       </c>
       <c r="B36" t="n">
-        <v>8439</v>
+        <v>91326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4193,43 +4203,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>3215</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695870</v>
+        <v>695740</v>
       </c>
       <c r="R36" t="n">
-        <v>6617363</v>
+        <v>6617273</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4271,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4906,49 +4906,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129171382</v>
+        <v>129171369</v>
       </c>
       <c r="B43" t="n">
-        <v>98761</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695889</v>
+        <v>695729</v>
       </c>
       <c r="R43" t="n">
-        <v>6617161</v>
+        <v>6617282</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,7 +4985,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5008,45 +5003,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129171369</v>
+        <v>129171382</v>
       </c>
       <c r="B44" t="n">
-        <v>57887</v>
+        <v>98761</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695729</v>
+        <v>695889</v>
       </c>
       <c r="R44" t="n">
-        <v>6617282</v>
+        <v>6617161</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5087,6 +5086,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129174965</v>
+        <v>129171415</v>
       </c>
       <c r="B6" t="n">
-        <v>104198</v>
+        <v>86968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696247</v>
+        <v>696173</v>
       </c>
       <c r="R6" t="n">
-        <v>6617382</v>
+        <v>6617344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,57 +1228,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171415</v>
+        <v>129171368</v>
       </c>
       <c r="B7" t="n">
-        <v>86968</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696173</v>
+        <v>695888</v>
       </c>
       <c r="R7" t="n">
-        <v>6617344</v>
+        <v>6617461</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,42 +1345,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171368</v>
+        <v>129171407</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>8439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1380,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695888</v>
+        <v>695742</v>
       </c>
       <c r="R8" t="n">
-        <v>6617461</v>
+        <v>6617264</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,6 +1433,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1442,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171407</v>
+        <v>129174965</v>
       </c>
       <c r="B9" t="n">
-        <v>8439</v>
+        <v>104198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,43 +1463,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>695742</v>
+        <v>696247</v>
       </c>
       <c r="R9" t="n">
-        <v>6617264</v>
+        <v>6617382</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,19 +1531,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1858,43 +1858,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171404</v>
+        <v>129171392</v>
       </c>
       <c r="B13" t="n">
-        <v>8439</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1902,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695939</v>
+        <v>695840</v>
       </c>
       <c r="R13" t="n">
-        <v>6617438</v>
+        <v>6617459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,43 +1972,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171405</v>
+        <v>129174970</v>
       </c>
       <c r="B14" t="n">
-        <v>8439</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2009,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695875</v>
+        <v>696187</v>
       </c>
       <c r="R14" t="n">
-        <v>6617394</v>
+        <v>6617372</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,62 +2070,55 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171392</v>
+        <v>129171404</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>8439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2123,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695840</v>
+        <v>695939</v>
       </c>
       <c r="R15" t="n">
-        <v>6617459</v>
+        <v>6617438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,46 +2189,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129174970</v>
+        <v>129171405</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>8439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696187</v>
+        <v>695875</v>
       </c>
       <c r="R16" t="n">
-        <v>6617372</v>
+        <v>6617394</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,12 +2284,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129171385</v>
+        <v>129171416</v>
       </c>
       <c r="B19" t="n">
-        <v>98761</v>
+        <v>86968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,21 +2509,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696217</v>
+        <v>696215</v>
       </c>
       <c r="R19" t="n">
-        <v>6617392</v>
+        <v>6617356</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171416</v>
+        <v>129171409</v>
       </c>
       <c r="B20" t="n">
-        <v>86968</v>
+        <v>8439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,34 +2606,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696215</v>
+        <v>696020</v>
       </c>
       <c r="R20" t="n">
-        <v>6617356</v>
+        <v>6617274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2674,6 +2683,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2692,10 +2702,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171409</v>
+        <v>129171385</v>
       </c>
       <c r="B21" t="n">
-        <v>8439</v>
+        <v>98761</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,43 +2713,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696020</v>
+        <v>696217</v>
       </c>
       <c r="R21" t="n">
-        <v>6617274</v>
+        <v>6617392</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,7 +2781,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3301,45 +3301,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171386</v>
+        <v>129171367</v>
       </c>
       <c r="B27" t="n">
-        <v>58097</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696062</v>
+        <v>696155</v>
       </c>
       <c r="R27" t="n">
-        <v>6617338</v>
+        <v>6617505</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3398,53 +3406,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171367</v>
+        <v>129171386</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>58097</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696155</v>
+        <v>696062</v>
       </c>
       <c r="R28" t="n">
-        <v>6617505</v>
+        <v>6617338</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,45 +3503,44 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171363</v>
+        <v>129171395</v>
       </c>
       <c r="B29" t="n">
-        <v>91553</v>
+        <v>87071</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>3624</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695974</v>
+        <v>696012</v>
       </c>
       <c r="R29" t="n">
-        <v>6617238</v>
+        <v>6617292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,6 +3581,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171395</v>
+        <v>129171413</v>
       </c>
       <c r="B30" t="n">
-        <v>87071</v>
+        <v>86968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,33 +3611,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3624</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696012</v>
+        <v>695981</v>
       </c>
       <c r="R30" t="n">
-        <v>6617292</v>
+        <v>6617228</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,7 +3679,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171413</v>
+        <v>129171363</v>
       </c>
       <c r="B31" t="n">
-        <v>86968</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695981</v>
+        <v>695974</v>
       </c>
       <c r="R31" t="n">
-        <v>6617228</v>
+        <v>6617238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171406</v>
+        <v>129171375</v>
       </c>
       <c r="B34" t="n">
-        <v>8439</v>
+        <v>91326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,43 +3999,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>3215</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695870</v>
+        <v>695740</v>
       </c>
       <c r="R34" t="n">
-        <v>6617363</v>
+        <v>6617273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,7 +4067,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4095,45 +4085,61 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171412</v>
+        <v>129171391</v>
       </c>
       <c r="B35" t="n">
-        <v>86968</v>
+        <v>98727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695978</v>
+        <v>695872</v>
       </c>
       <c r="R35" t="n">
-        <v>6617179</v>
+        <v>6617462</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4174,6 +4180,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4192,10 +4199,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171375</v>
+        <v>129171406</v>
       </c>
       <c r="B36" t="n">
-        <v>91326</v>
+        <v>8439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4203,34 +4210,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695740</v>
+        <v>695870</v>
       </c>
       <c r="R36" t="n">
-        <v>6617273</v>
+        <v>6617363</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4271,6 +4287,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4289,61 +4306,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171391</v>
+        <v>129171412</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>86968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695872</v>
+        <v>695978</v>
       </c>
       <c r="R37" t="n">
-        <v>6617462</v>
+        <v>6617179</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4384,7 +4385,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171378</v>
+        <v>129171379</v>
       </c>
       <c r="B45" t="n">
-        <v>92827</v>
+        <v>86956</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>6003296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695821</v>
+        <v>696222</v>
       </c>
       <c r="R45" t="n">
-        <v>6617383</v>
+        <v>6617388</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5184,6 +5184,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5202,32 +5203,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129171417</v>
+        <v>129171378</v>
       </c>
       <c r="B46" t="n">
-        <v>86968</v>
+        <v>92827</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3674</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5237,10 +5238,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696217</v>
+        <v>695821</v>
       </c>
       <c r="R46" t="n">
-        <v>6617368</v>
+        <v>6617383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5299,32 +5300,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171379</v>
+        <v>129171417</v>
       </c>
       <c r="B47" t="n">
-        <v>86956</v>
+        <v>86968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003296</v>
+        <v>3674</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5334,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696222</v>
+        <v>696217</v>
       </c>
       <c r="R47" t="n">
-        <v>6617388</v>
+        <v>6617368</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,7 +5379,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171403</v>
+        <v>129171415</v>
       </c>
       <c r="B5" t="n">
-        <v>100916</v>
+        <v>86996</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696219</v>
+        <v>696173</v>
       </c>
       <c r="R5" t="n">
-        <v>6617372</v>
+        <v>6617344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,45 +1143,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171415</v>
+        <v>129171368</v>
       </c>
       <c r="B6" t="n">
-        <v>86968</v>
+        <v>57890</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696173</v>
+        <v>695888</v>
       </c>
       <c r="R6" t="n">
-        <v>6617344</v>
+        <v>6617461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,53 +1248,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171368</v>
+        <v>129174965</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>104227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695888</v>
+        <v>696247</v>
       </c>
       <c r="R7" t="n">
-        <v>6617461</v>
+        <v>6617382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,22 +1333,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171407</v>
+        <v>129171403</v>
       </c>
       <c r="B8" t="n">
-        <v>8439</v>
+        <v>100945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,43 +1356,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695742</v>
+        <v>696219</v>
       </c>
       <c r="R8" t="n">
-        <v>6617264</v>
+        <v>6617372</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1424,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1452,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129174965</v>
+        <v>129171407</v>
       </c>
       <c r="B9" t="n">
-        <v>104198</v>
+        <v>8439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,34 +1453,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696247</v>
+        <v>695742</v>
       </c>
       <c r="R9" t="n">
-        <v>6617382</v>
+        <v>6617264</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,18 +1530,19 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1659,7 +1659,7 @@
         <v>129171360</v>
       </c>
       <c r="B11" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,40 +1753,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171374</v>
+        <v>129171404</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>8439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1796,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696142</v>
+        <v>695939</v>
       </c>
       <c r="R12" t="n">
-        <v>6617341</v>
+        <v>6617438</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,6 +1841,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1858,50 +1860,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171392</v>
+        <v>129171405</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>8439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1909,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695840</v>
+        <v>695875</v>
       </c>
       <c r="R13" t="n">
-        <v>6617459</v>
+        <v>6617394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,46 +1967,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129174970</v>
+        <v>129171374</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2019,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696187</v>
+        <v>696142</v>
       </c>
       <c r="R14" t="n">
-        <v>6617372</v>
+        <v>6617341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,62 +2054,68 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171404</v>
+        <v>129171392</v>
       </c>
       <c r="B15" t="n">
-        <v>8439</v>
+        <v>98756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2126,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695939</v>
+        <v>695840</v>
       </c>
       <c r="R15" t="n">
-        <v>6617438</v>
+        <v>6617459</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,43 +2186,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129171405</v>
+        <v>129174970</v>
       </c>
       <c r="B16" t="n">
-        <v>8439</v>
+        <v>98756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695875</v>
+        <v>696187</v>
       </c>
       <c r="R16" t="n">
-        <v>6617394</v>
+        <v>6617372</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,12 +2284,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2299,7 +2299,7 @@
         <v>129171373</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>129171402</v>
       </c>
       <c r="B18" t="n">
-        <v>88801</v>
+        <v>88829</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>129171416</v>
       </c>
       <c r="B19" t="n">
-        <v>86968</v>
+        <v>86996</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171409</v>
+        <v>129171385</v>
       </c>
       <c r="B20" t="n">
-        <v>8439</v>
+        <v>98790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,43 +2606,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696020</v>
+        <v>696217</v>
       </c>
       <c r="R20" t="n">
-        <v>6617274</v>
+        <v>6617392</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2674,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2702,10 +2692,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171385</v>
+        <v>129171409</v>
       </c>
       <c r="B21" t="n">
-        <v>98761</v>
+        <v>8439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,34 +2703,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696217</v>
+        <v>696020</v>
       </c>
       <c r="R21" t="n">
-        <v>6617392</v>
+        <v>6617274</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2781,6 +2780,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>129174969</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>129174973</v>
       </c>
       <c r="B23" t="n">
-        <v>75161</v>
+        <v>75182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>129171383</v>
       </c>
       <c r="B24" t="n">
-        <v>98761</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>129171401</v>
       </c>
       <c r="B25" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>129174972</v>
       </c>
       <c r="B26" t="n">
-        <v>75161</v>
+        <v>75182</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>129171367</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>129171386</v>
       </c>
       <c r="B28" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,44 +3503,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171395</v>
+        <v>129171363</v>
       </c>
       <c r="B29" t="n">
-        <v>87071</v>
+        <v>91581</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3624</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696012</v>
+        <v>695974</v>
       </c>
       <c r="R29" t="n">
-        <v>6617292</v>
+        <v>6617238</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,7 +3582,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171413</v>
+        <v>129171395</v>
       </c>
       <c r="B30" t="n">
-        <v>86968</v>
+        <v>87099</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,34 +3611,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3674</v>
+        <v>3624</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695981</v>
+        <v>696012</v>
       </c>
       <c r="R30" t="n">
-        <v>6617228</v>
+        <v>6617292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,6 +3678,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171363</v>
+        <v>129171413</v>
       </c>
       <c r="B31" t="n">
-        <v>91553</v>
+        <v>86996</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695974</v>
+        <v>695981</v>
       </c>
       <c r="R31" t="n">
-        <v>6617238</v>
+        <v>6617228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129171371</v>
+        <v>129171414</v>
       </c>
       <c r="B32" t="n">
-        <v>96073</v>
+        <v>86996</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695971</v>
+        <v>696014</v>
       </c>
       <c r="R32" t="n">
-        <v>6617182</v>
+        <v>6617265</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129171414</v>
+        <v>129171371</v>
       </c>
       <c r="B33" t="n">
-        <v>86968</v>
+        <v>96102</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696014</v>
+        <v>695971</v>
       </c>
       <c r="R33" t="n">
-        <v>6617265</v>
+        <v>6617182</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171375</v>
+        <v>129171406</v>
       </c>
       <c r="B34" t="n">
-        <v>91326</v>
+        <v>8439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,34 +3999,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3215</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695740</v>
+        <v>695870</v>
       </c>
       <c r="R34" t="n">
-        <v>6617273</v>
+        <v>6617363</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,6 +4076,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4088,7 +4098,7 @@
         <v>129171391</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4199,10 +4209,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171406</v>
+        <v>129171412</v>
       </c>
       <c r="B36" t="n">
-        <v>8439</v>
+        <v>86996</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4210,43 +4220,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695870</v>
+        <v>695978</v>
       </c>
       <c r="R36" t="n">
-        <v>6617363</v>
+        <v>6617179</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4287,7 +4288,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171412</v>
+        <v>129171375</v>
       </c>
       <c r="B37" t="n">
-        <v>86968</v>
+        <v>91354</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4317,21 +4317,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695978</v>
+        <v>695740</v>
       </c>
       <c r="R37" t="n">
-        <v>6617179</v>
+        <v>6617273</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4406,7 +4406,7 @@
         <v>129171394</v>
       </c>
       <c r="B38" t="n">
-        <v>91014</v>
+        <v>91042</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129171393</v>
       </c>
       <c r="B39" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171377</v>
+        <v>129171384</v>
       </c>
       <c r="B40" t="n">
-        <v>91326</v>
+        <v>98790</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696216</v>
+        <v>695740</v>
       </c>
       <c r="R40" t="n">
-        <v>6617354</v>
+        <v>6617273</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129171411</v>
+        <v>129171377</v>
       </c>
       <c r="B41" t="n">
-        <v>86968</v>
+        <v>91354</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695740</v>
+        <v>696216</v>
       </c>
       <c r="R41" t="n">
-        <v>6617275</v>
+        <v>6617354</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129171384</v>
+        <v>129171411</v>
       </c>
       <c r="B42" t="n">
-        <v>98761</v>
+        <v>86996</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         <v>695740</v>
       </c>
       <c r="R42" t="n">
-        <v>6617273</v>
+        <v>6617275</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4909,7 +4909,7 @@
         <v>129171369</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>129171382</v>
       </c>
       <c r="B44" t="n">
-        <v>98761</v>
+        <v>98790</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171379</v>
+        <v>129171417</v>
       </c>
       <c r="B45" t="n">
-        <v>86956</v>
+        <v>86996</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003296</v>
+        <v>3674</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696222</v>
+        <v>696217</v>
       </c>
       <c r="R45" t="n">
-        <v>6617388</v>
+        <v>6617368</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5184,7 +5184,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5206,7 +5205,7 @@
         <v>129171378</v>
       </c>
       <c r="B46" t="n">
-        <v>92827</v>
+        <v>92855</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5300,32 +5299,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171417</v>
+        <v>129171379</v>
       </c>
       <c r="B47" t="n">
-        <v>86968</v>
+        <v>86984</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>6003296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5335,10 +5334,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696217</v>
+        <v>696222</v>
       </c>
       <c r="R47" t="n">
-        <v>6617368</v>
+        <v>6617388</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5379,6 +5378,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171415</v>
+        <v>129171407</v>
       </c>
       <c r="B5" t="n">
-        <v>86996</v>
+        <v>8439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,34 +1057,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696173</v>
+        <v>695742</v>
       </c>
       <c r="R5" t="n">
-        <v>6617344</v>
+        <v>6617264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,6 +1134,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,53 +1153,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171368</v>
+        <v>129171415</v>
       </c>
       <c r="B6" t="n">
-        <v>57890</v>
+        <v>86996</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695888</v>
+        <v>696173</v>
       </c>
       <c r="R6" t="n">
-        <v>6617461</v>
+        <v>6617344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,45 +1250,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129174965</v>
+        <v>129171368</v>
       </c>
       <c r="B7" t="n">
-        <v>104227</v>
+        <v>57890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696247</v>
+        <v>695888</v>
       </c>
       <c r="R7" t="n">
-        <v>6617382</v>
+        <v>6617461</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,22 +1343,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171403</v>
+        <v>129174965</v>
       </c>
       <c r="B8" t="n">
-        <v>100945</v>
+        <v>104227</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696219</v>
+        <v>696247</v>
       </c>
       <c r="R8" t="n">
-        <v>6617372</v>
+        <v>6617382</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,22 +1440,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171407</v>
+        <v>129171403</v>
       </c>
       <c r="B9" t="n">
-        <v>8439</v>
+        <v>100945</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,43 +1463,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>695742</v>
+        <v>696219</v>
       </c>
       <c r="R9" t="n">
-        <v>6617264</v>
+        <v>6617372</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1531,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -3503,45 +3503,44 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171363</v>
+        <v>129171395</v>
       </c>
       <c r="B29" t="n">
-        <v>91581</v>
+        <v>87099</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>3624</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695974</v>
+        <v>696012</v>
       </c>
       <c r="R29" t="n">
-        <v>6617238</v>
+        <v>6617292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,6 +3581,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171395</v>
+        <v>129171413</v>
       </c>
       <c r="B30" t="n">
-        <v>87099</v>
+        <v>86996</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,33 +3611,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3624</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696012</v>
+        <v>695981</v>
       </c>
       <c r="R30" t="n">
-        <v>6617292</v>
+        <v>6617228</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,7 +3679,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171413</v>
+        <v>129171363</v>
       </c>
       <c r="B31" t="n">
-        <v>86996</v>
+        <v>91581</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695981</v>
+        <v>695974</v>
       </c>
       <c r="R31" t="n">
-        <v>6617228</v>
+        <v>6617238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171406</v>
+        <v>129171412</v>
       </c>
       <c r="B34" t="n">
-        <v>8439</v>
+        <v>86996</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,43 +3999,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695870</v>
+        <v>695978</v>
       </c>
       <c r="R34" t="n">
-        <v>6617363</v>
+        <v>6617179</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,7 +4067,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4095,61 +4085,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171391</v>
+        <v>129171375</v>
       </c>
       <c r="B35" t="n">
-        <v>98756</v>
+        <v>91354</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695872</v>
+        <v>695740</v>
       </c>
       <c r="R35" t="n">
-        <v>6617462</v>
+        <v>6617273</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4190,7 +4164,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4209,10 +4182,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171412</v>
+        <v>129171406</v>
       </c>
       <c r="B36" t="n">
-        <v>86996</v>
+        <v>8439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4220,34 +4193,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695978</v>
+        <v>695870</v>
       </c>
       <c r="R36" t="n">
-        <v>6617179</v>
+        <v>6617363</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4288,6 +4270,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4306,45 +4289,61 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171375</v>
+        <v>129171391</v>
       </c>
       <c r="B37" t="n">
-        <v>91354</v>
+        <v>98756</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695740</v>
+        <v>695872</v>
       </c>
       <c r="R37" t="n">
-        <v>6617273</v>
+        <v>6617462</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4385,6 +4384,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171384</v>
+        <v>129171377</v>
       </c>
       <c r="B40" t="n">
-        <v>98790</v>
+        <v>91354</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695740</v>
+        <v>696216</v>
       </c>
       <c r="R40" t="n">
-        <v>6617273</v>
+        <v>6617354</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129171377</v>
+        <v>129171411</v>
       </c>
       <c r="B41" t="n">
-        <v>91354</v>
+        <v>86996</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696216</v>
+        <v>695740</v>
       </c>
       <c r="R41" t="n">
-        <v>6617354</v>
+        <v>6617275</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129171411</v>
+        <v>129171384</v>
       </c>
       <c r="B42" t="n">
-        <v>86996</v>
+        <v>98790</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         <v>695740</v>
       </c>
       <c r="R42" t="n">
-        <v>6617275</v>
+        <v>6617273</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5105,32 +5105,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171417</v>
+        <v>129171379</v>
       </c>
       <c r="B45" t="n">
-        <v>86996</v>
+        <v>86984</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3674</v>
+        <v>6003296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696217</v>
+        <v>696222</v>
       </c>
       <c r="R45" t="n">
-        <v>6617368</v>
+        <v>6617388</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5184,6 +5184,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5299,32 +5300,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171379</v>
+        <v>129171417</v>
       </c>
       <c r="B47" t="n">
-        <v>86984</v>
+        <v>86996</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003296</v>
+        <v>3674</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5334,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696222</v>
+        <v>696217</v>
       </c>
       <c r="R47" t="n">
-        <v>6617388</v>
+        <v>6617368</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,7 +5379,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5395,6 +5395,126 @@
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129939229</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>112</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Ledinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>695794</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6617333</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Utbredd över flera dm2 på undersidan av granlåga</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -5400,7 +5400,7 @@
         <v>129939229</v>
       </c>
       <c r="B48" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -5400,7 +5400,7 @@
         <v>129939229</v>
       </c>
       <c r="B48" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -5400,7 +5400,7 @@
         <v>129939229</v>
       </c>
       <c r="B48" t="n">
-        <v>91556</v>
+        <v>91557</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -5400,7 +5400,7 @@
         <v>129939229</v>
       </c>
       <c r="B48" t="n">
-        <v>91557</v>
+        <v>91574</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -5400,7 +5400,7 @@
         <v>129939229</v>
       </c>
       <c r="B48" t="n">
-        <v>91590</v>
+        <v>91592</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -5400,7 +5400,7 @@
         <v>129939229</v>
       </c>
       <c r="B48" t="n">
-        <v>91592</v>
+        <v>91679</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -5400,7 +5400,7 @@
         <v>129939229</v>
       </c>
       <c r="B48" t="n">
-        <v>91679</v>
+        <v>91592</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2909,10 +2909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129174973</v>
+        <v>131728875</v>
       </c>
       <c r="B23" t="n">
-        <v>75182</v>
+        <v>75366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -2950,7 +2950,7 @@
         <v>6617339</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2994,12 +2994,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -5515,6 +5515,1558 @@
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131728893</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91280</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>695933</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6617193</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131728890</v>
+      </c>
+      <c r="B50" t="n">
+        <v>8442</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>695745</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6617268</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131728903</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97899</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>696207</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6617386</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131728888</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99070</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>695741</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6617275</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131728873</v>
+      </c>
+      <c r="B53" t="n">
+        <v>8442</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>695750</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6617315</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131728904</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99070</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>696216</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6617396</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131728905</v>
+      </c>
+      <c r="B55" t="n">
+        <v>101238</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>696224</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6617389</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131728895</v>
+      </c>
+      <c r="B56" t="n">
+        <v>8442</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>696026</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6617277</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>131728889</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91599</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>695742</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6617273</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>131728883</v>
+      </c>
+      <c r="B58" t="n">
+        <v>97899</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>695877</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6617367</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>131728900</v>
+      </c>
+      <c r="B59" t="n">
+        <v>87230</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>696214</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6617357</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131728894</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>695978</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6617240</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131728892</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99070</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>695888</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6617156</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131728874</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>695873</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6617461</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131728901</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91599</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>696216</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6617369</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131728907</v>
+      </c>
+      <c r="B64" t="n">
+        <v>97899</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>696238</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6617405</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -5711,10 +5711,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131728903</v>
+        <v>131728888</v>
       </c>
       <c r="B51" t="n">
-        <v>97899</v>
+        <v>99070</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696207</v>
+        <v>695741</v>
       </c>
       <c r="R51" t="n">
-        <v>6617386</v>
+        <v>6617275</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5808,10 +5808,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131728888</v>
+        <v>131728903</v>
       </c>
       <c r="B52" t="n">
-        <v>99070</v>
+        <v>97899</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>695741</v>
+        <v>696207</v>
       </c>
       <c r="R52" t="n">
-        <v>6617275</v>
+        <v>6617386</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6099,10 +6099,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131728905</v>
+        <v>131728895</v>
       </c>
       <c r="B55" t="n">
-        <v>101238</v>
+        <v>8442</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6110,21 +6110,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696224</v>
+        <v>696026</v>
       </c>
       <c r="R55" t="n">
-        <v>6617389</v>
+        <v>6617277</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6196,10 +6196,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131728895</v>
+        <v>131728905</v>
       </c>
       <c r="B56" t="n">
-        <v>8442</v>
+        <v>101238</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6207,21 +6207,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696026</v>
+        <v>696224</v>
       </c>
       <c r="R56" t="n">
-        <v>6617277</v>
+        <v>6617389</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6487,10 +6487,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131728900</v>
+        <v>131728892</v>
       </c>
       <c r="B59" t="n">
-        <v>87230</v>
+        <v>99070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6498,21 +6498,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696214</v>
+        <v>695888</v>
       </c>
       <c r="R59" t="n">
-        <v>6617357</v>
+        <v>6617156</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6584,32 +6584,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131728894</v>
+        <v>131728900</v>
       </c>
       <c r="B60" t="n">
-        <v>91828</v>
+        <v>87230</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>695978</v>
+        <v>696214</v>
       </c>
       <c r="R60" t="n">
-        <v>6617240</v>
+        <v>6617357</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6681,32 +6681,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728892</v>
+        <v>131728894</v>
       </c>
       <c r="B61" t="n">
-        <v>99070</v>
+        <v>91828</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695888</v>
+        <v>695978</v>
       </c>
       <c r="R61" t="n">
-        <v>6617156</v>
+        <v>6617240</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>131728875</v>
       </c>
       <c r="B23" t="n">
-        <v>75366</v>
+        <v>75367</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>131728893</v>
       </c>
       <c r="B49" t="n">
-        <v>91280</v>
+        <v>91281</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>131728890</v>
       </c>
       <c r="B50" t="n">
-        <v>8442</v>
+        <v>8443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>131728888</v>
       </c>
       <c r="B51" t="n">
-        <v>99070</v>
+        <v>99071</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>131728903</v>
       </c>
       <c r="B52" t="n">
-        <v>97899</v>
+        <v>97900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>131728873</v>
       </c>
       <c r="B53" t="n">
-        <v>8442</v>
+        <v>8443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>131728904</v>
       </c>
       <c r="B54" t="n">
-        <v>99070</v>
+        <v>99071</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>131728895</v>
       </c>
       <c r="B55" t="n">
-        <v>8442</v>
+        <v>8443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>131728905</v>
       </c>
       <c r="B56" t="n">
-        <v>101238</v>
+        <v>101239</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>131728889</v>
       </c>
       <c r="B57" t="n">
-        <v>91599</v>
+        <v>91600</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>131728883</v>
       </c>
       <c r="B58" t="n">
-        <v>97899</v>
+        <v>97900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6487,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131728892</v>
+        <v>131728894</v>
       </c>
       <c r="B59" t="n">
-        <v>99070</v>
+        <v>91829</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695888</v>
+        <v>695978</v>
       </c>
       <c r="R59" t="n">
-        <v>6617156</v>
+        <v>6617240</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6587,7 +6587,7 @@
         <v>131728900</v>
       </c>
       <c r="B60" t="n">
-        <v>87230</v>
+        <v>87231</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6681,32 +6681,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728894</v>
+        <v>131728892</v>
       </c>
       <c r="B61" t="n">
-        <v>91828</v>
+        <v>99071</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695978</v>
+        <v>695888</v>
       </c>
       <c r="R61" t="n">
-        <v>6617240</v>
+        <v>6617156</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6781,7 +6781,7 @@
         <v>131728874</v>
       </c>
       <c r="B62" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>131728901</v>
       </c>
       <c r="B63" t="n">
-        <v>91599</v>
+        <v>91600</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>131728907</v>
       </c>
       <c r="B64" t="n">
-        <v>97899</v>
+        <v>97900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>131728875</v>
       </c>
       <c r="B23" t="n">
-        <v>75367</v>
+        <v>75370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>131728893</v>
       </c>
       <c r="B49" t="n">
-        <v>91281</v>
+        <v>91284</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>131728888</v>
       </c>
       <c r="B51" t="n">
-        <v>99071</v>
+        <v>99074</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>131728903</v>
       </c>
       <c r="B52" t="n">
-        <v>97900</v>
+        <v>97903</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>131728904</v>
       </c>
       <c r="B54" t="n">
-        <v>99071</v>
+        <v>99074</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>131728905</v>
       </c>
       <c r="B56" t="n">
-        <v>101239</v>
+        <v>101242</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>131728889</v>
       </c>
       <c r="B57" t="n">
-        <v>91600</v>
+        <v>91603</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>131728883</v>
       </c>
       <c r="B58" t="n">
-        <v>97900</v>
+        <v>97903</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>131728894</v>
       </c>
       <c r="B59" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>131728900</v>
       </c>
       <c r="B60" t="n">
-        <v>87231</v>
+        <v>87234</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>131728892</v>
       </c>
       <c r="B61" t="n">
-        <v>99071</v>
+        <v>99074</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>131728874</v>
       </c>
       <c r="B62" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>131728901</v>
       </c>
       <c r="B63" t="n">
-        <v>91600</v>
+        <v>91603</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>131728907</v>
       </c>
       <c r="B64" t="n">
-        <v>97900</v>
+        <v>97903</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -6199,7 +6199,7 @@
         <v>131728905</v>
       </c>
       <c r="B56" t="n">
-        <v>101242</v>
+        <v>101243</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6487,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131728894</v>
+        <v>131728900</v>
       </c>
       <c r="B59" t="n">
-        <v>91832</v>
+        <v>87234</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695978</v>
+        <v>696214</v>
       </c>
       <c r="R59" t="n">
-        <v>6617240</v>
+        <v>6617357</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131728900</v>
+        <v>131728892</v>
       </c>
       <c r="B60" t="n">
-        <v>87234</v>
+        <v>99074</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6595,21 +6595,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>696214</v>
+        <v>695888</v>
       </c>
       <c r="R60" t="n">
-        <v>6617357</v>
+        <v>6617156</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6681,32 +6681,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728892</v>
+        <v>131728894</v>
       </c>
       <c r="B61" t="n">
-        <v>99074</v>
+        <v>91832</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695888</v>
+        <v>695978</v>
       </c>
       <c r="R61" t="n">
-        <v>6617156</v>
+        <v>6617240</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -5711,10 +5711,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131728888</v>
+        <v>131728903</v>
       </c>
       <c r="B51" t="n">
-        <v>99074</v>
+        <v>97903</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>695741</v>
+        <v>696207</v>
       </c>
       <c r="R51" t="n">
-        <v>6617275</v>
+        <v>6617386</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5808,10 +5808,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131728903</v>
+        <v>131728888</v>
       </c>
       <c r="B52" t="n">
-        <v>97903</v>
+        <v>99073</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696207</v>
+        <v>695741</v>
       </c>
       <c r="R52" t="n">
-        <v>6617386</v>
+        <v>6617275</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6005,7 +6005,7 @@
         <v>131728904</v>
       </c>
       <c r="B54" t="n">
-        <v>99074</v>
+        <v>99073</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6099,10 +6099,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131728895</v>
+        <v>131728905</v>
       </c>
       <c r="B55" t="n">
-        <v>8443</v>
+        <v>101243</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6110,21 +6110,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696026</v>
+        <v>696224</v>
       </c>
       <c r="R55" t="n">
-        <v>6617277</v>
+        <v>6617389</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6196,10 +6196,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131728905</v>
+        <v>131728895</v>
       </c>
       <c r="B56" t="n">
-        <v>101243</v>
+        <v>8443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6207,21 +6207,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696224</v>
+        <v>696026</v>
       </c>
       <c r="R56" t="n">
-        <v>6617389</v>
+        <v>6617277</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6487,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131728900</v>
+        <v>131728894</v>
       </c>
       <c r="B59" t="n">
-        <v>87234</v>
+        <v>91832</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696214</v>
+        <v>695978</v>
       </c>
       <c r="R59" t="n">
-        <v>6617357</v>
+        <v>6617240</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6587,7 +6587,7 @@
         <v>131728892</v>
       </c>
       <c r="B60" t="n">
-        <v>99074</v>
+        <v>99073</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6681,32 +6681,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728894</v>
+        <v>131728900</v>
       </c>
       <c r="B61" t="n">
-        <v>91832</v>
+        <v>87234</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695978</v>
+        <v>696214</v>
       </c>
       <c r="R61" t="n">
-        <v>6617240</v>
+        <v>6617357</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>131728875</v>
       </c>
       <c r="B23" t="n">
-        <v>75370</v>
+        <v>75372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>131728893</v>
       </c>
       <c r="B49" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>131728903</v>
       </c>
       <c r="B51" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>131728888</v>
       </c>
       <c r="B52" t="n">
-        <v>99073</v>
+        <v>99079</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>131728904</v>
       </c>
       <c r="B54" t="n">
-        <v>99073</v>
+        <v>99079</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6099,10 +6099,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131728905</v>
+        <v>131728895</v>
       </c>
       <c r="B55" t="n">
-        <v>101243</v>
+        <v>8443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6110,21 +6110,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696224</v>
+        <v>696026</v>
       </c>
       <c r="R55" t="n">
-        <v>6617389</v>
+        <v>6617277</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6196,10 +6196,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131728895</v>
+        <v>131728905</v>
       </c>
       <c r="B56" t="n">
-        <v>8443</v>
+        <v>101249</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6207,21 +6207,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696026</v>
+        <v>696224</v>
       </c>
       <c r="R56" t="n">
-        <v>6617277</v>
+        <v>6617389</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6296,7 +6296,7 @@
         <v>131728889</v>
       </c>
       <c r="B57" t="n">
-        <v>91603</v>
+        <v>91609</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>131728883</v>
       </c>
       <c r="B58" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>131728894</v>
       </c>
       <c r="B59" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>131728892</v>
       </c>
       <c r="B60" t="n">
-        <v>99073</v>
+        <v>99079</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>131728900</v>
       </c>
       <c r="B61" t="n">
-        <v>87234</v>
+        <v>87240</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>131728874</v>
       </c>
       <c r="B62" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>131728901</v>
       </c>
       <c r="B63" t="n">
-        <v>91603</v>
+        <v>91609</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>131728907</v>
       </c>
       <c r="B64" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>131728875</v>
       </c>
       <c r="B23" t="n">
-        <v>75372</v>
+        <v>75375</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>131728893</v>
       </c>
       <c r="B49" t="n">
-        <v>91290</v>
+        <v>91293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>131728890</v>
       </c>
       <c r="B50" t="n">
-        <v>8443</v>
+        <v>8444</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5711,10 +5711,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131728903</v>
+        <v>131728888</v>
       </c>
       <c r="B51" t="n">
-        <v>97909</v>
+        <v>99082</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696207</v>
+        <v>695741</v>
       </c>
       <c r="R51" t="n">
-        <v>6617386</v>
+        <v>6617275</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5808,10 +5808,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131728888</v>
+        <v>131728903</v>
       </c>
       <c r="B52" t="n">
-        <v>99079</v>
+        <v>97912</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>695741</v>
+        <v>696207</v>
       </c>
       <c r="R52" t="n">
-        <v>6617275</v>
+        <v>6617386</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5908,7 +5908,7 @@
         <v>131728873</v>
       </c>
       <c r="B53" t="n">
-        <v>8443</v>
+        <v>8444</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>131728904</v>
       </c>
       <c r="B54" t="n">
-        <v>99079</v>
+        <v>99082</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6099,10 +6099,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131728895</v>
+        <v>131728905</v>
       </c>
       <c r="B55" t="n">
-        <v>8443</v>
+        <v>101252</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6110,21 +6110,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696026</v>
+        <v>696224</v>
       </c>
       <c r="R55" t="n">
-        <v>6617277</v>
+        <v>6617389</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6196,10 +6196,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131728905</v>
+        <v>131728895</v>
       </c>
       <c r="B56" t="n">
-        <v>101249</v>
+        <v>8444</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6207,21 +6207,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696224</v>
+        <v>696026</v>
       </c>
       <c r="R56" t="n">
-        <v>6617389</v>
+        <v>6617277</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6296,7 +6296,7 @@
         <v>131728889</v>
       </c>
       <c r="B57" t="n">
-        <v>91609</v>
+        <v>91612</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>131728883</v>
       </c>
       <c r="B58" t="n">
-        <v>97909</v>
+        <v>97912</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6487,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131728894</v>
+        <v>131728900</v>
       </c>
       <c r="B59" t="n">
-        <v>91838</v>
+        <v>87243</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695978</v>
+        <v>696214</v>
       </c>
       <c r="R59" t="n">
-        <v>6617240</v>
+        <v>6617357</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6584,32 +6584,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131728892</v>
+        <v>131728894</v>
       </c>
       <c r="B60" t="n">
-        <v>99079</v>
+        <v>91841</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>695888</v>
+        <v>695978</v>
       </c>
       <c r="R60" t="n">
-        <v>6617156</v>
+        <v>6617240</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728900</v>
+        <v>131728892</v>
       </c>
       <c r="B61" t="n">
-        <v>87240</v>
+        <v>99082</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,21 +6692,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696214</v>
+        <v>695888</v>
       </c>
       <c r="R61" t="n">
-        <v>6617357</v>
+        <v>6617156</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6781,7 +6781,7 @@
         <v>131728874</v>
       </c>
       <c r="B62" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>131728901</v>
       </c>
       <c r="B63" t="n">
-        <v>91609</v>
+        <v>91612</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>131728907</v>
       </c>
       <c r="B64" t="n">
-        <v>97909</v>
+        <v>97912</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>131728875</v>
       </c>
       <c r="B23" t="n">
-        <v>75375</v>
+        <v>75380</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>131728893</v>
       </c>
       <c r="B49" t="n">
-        <v>91293</v>
+        <v>91298</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>131728888</v>
       </c>
       <c r="B51" t="n">
-        <v>99082</v>
+        <v>99087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>131728903</v>
       </c>
       <c r="B52" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>131728904</v>
       </c>
       <c r="B54" t="n">
-        <v>99082</v>
+        <v>99087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6099,10 +6099,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131728905</v>
+        <v>131728895</v>
       </c>
       <c r="B55" t="n">
-        <v>101252</v>
+        <v>8444</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6110,21 +6110,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696224</v>
+        <v>696026</v>
       </c>
       <c r="R55" t="n">
-        <v>6617389</v>
+        <v>6617277</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6196,10 +6196,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131728895</v>
+        <v>131728905</v>
       </c>
       <c r="B56" t="n">
-        <v>8444</v>
+        <v>101257</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6207,21 +6207,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696026</v>
+        <v>696224</v>
       </c>
       <c r="R56" t="n">
-        <v>6617277</v>
+        <v>6617389</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6296,7 +6296,7 @@
         <v>131728889</v>
       </c>
       <c r="B57" t="n">
-        <v>91612</v>
+        <v>91617</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>131728883</v>
       </c>
       <c r="B58" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>131728900</v>
       </c>
       <c r="B59" t="n">
-        <v>87243</v>
+        <v>87248</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6584,32 +6584,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131728894</v>
+        <v>131728892</v>
       </c>
       <c r="B60" t="n">
-        <v>91841</v>
+        <v>99087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>695978</v>
+        <v>695888</v>
       </c>
       <c r="R60" t="n">
-        <v>6617240</v>
+        <v>6617156</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6681,32 +6681,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728892</v>
+        <v>131728894</v>
       </c>
       <c r="B61" t="n">
-        <v>99082</v>
+        <v>91846</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695888</v>
+        <v>695978</v>
       </c>
       <c r="R61" t="n">
-        <v>6617156</v>
+        <v>6617240</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6781,7 +6781,7 @@
         <v>131728874</v>
       </c>
       <c r="B62" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>131728901</v>
       </c>
       <c r="B63" t="n">
-        <v>91612</v>
+        <v>91617</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>131728907</v>
       </c>
       <c r="B64" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>131728875</v>
       </c>
       <c r="B23" t="n">
-        <v>75380</v>
+        <v>75382</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>131728893</v>
       </c>
       <c r="B49" t="n">
-        <v>91298</v>
+        <v>91300</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>131728888</v>
       </c>
       <c r="B51" t="n">
-        <v>99087</v>
+        <v>99089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>131728903</v>
       </c>
       <c r="B52" t="n">
-        <v>97917</v>
+        <v>97919</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>131728904</v>
       </c>
       <c r="B54" t="n">
-        <v>99087</v>
+        <v>99089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>131728905</v>
       </c>
       <c r="B56" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>131728889</v>
       </c>
       <c r="B57" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>131728883</v>
       </c>
       <c r="B58" t="n">
-        <v>97917</v>
+        <v>97919</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6487,10 +6487,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131728900</v>
+        <v>131728892</v>
       </c>
       <c r="B59" t="n">
-        <v>87248</v>
+        <v>99089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6498,21 +6498,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696214</v>
+        <v>695888</v>
       </c>
       <c r="R59" t="n">
-        <v>6617357</v>
+        <v>6617156</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6584,32 +6584,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131728892</v>
+        <v>131728894</v>
       </c>
       <c r="B60" t="n">
-        <v>99087</v>
+        <v>91848</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>695888</v>
+        <v>695978</v>
       </c>
       <c r="R60" t="n">
-        <v>6617156</v>
+        <v>6617240</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6681,32 +6681,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728894</v>
+        <v>131728900</v>
       </c>
       <c r="B61" t="n">
-        <v>91846</v>
+        <v>87250</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695978</v>
+        <v>696214</v>
       </c>
       <c r="R61" t="n">
-        <v>6617240</v>
+        <v>6617357</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6781,7 +6781,7 @@
         <v>131728874</v>
       </c>
       <c r="B62" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>131728901</v>
       </c>
       <c r="B63" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>131728907</v>
       </c>
       <c r="B64" t="n">
-        <v>97917</v>
+        <v>97919</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -6099,10 +6099,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131728895</v>
+        <v>131728905</v>
       </c>
       <c r="B55" t="n">
-        <v>8444</v>
+        <v>101260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6110,21 +6110,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696026</v>
+        <v>696224</v>
       </c>
       <c r="R55" t="n">
-        <v>6617277</v>
+        <v>6617389</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6196,10 +6196,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131728905</v>
+        <v>131728895</v>
       </c>
       <c r="B56" t="n">
-        <v>101260</v>
+        <v>8444</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6207,21 +6207,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696224</v>
+        <v>696026</v>
       </c>
       <c r="R56" t="n">
-        <v>6617389</v>
+        <v>6617277</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6487,10 +6487,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131728892</v>
+        <v>131728900</v>
       </c>
       <c r="B59" t="n">
-        <v>99089</v>
+        <v>87250</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6498,21 +6498,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695888</v>
+        <v>696214</v>
       </c>
       <c r="R59" t="n">
-        <v>6617156</v>
+        <v>6617357</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728900</v>
+        <v>131728892</v>
       </c>
       <c r="B61" t="n">
-        <v>87250</v>
+        <v>99089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,21 +6692,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696214</v>
+        <v>695888</v>
       </c>
       <c r="R61" t="n">
-        <v>6617357</v>
+        <v>6617156</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -6487,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131728900</v>
+        <v>131728894</v>
       </c>
       <c r="B59" t="n">
-        <v>87250</v>
+        <v>91848</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696214</v>
+        <v>695978</v>
       </c>
       <c r="R59" t="n">
-        <v>6617357</v>
+        <v>6617240</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6584,32 +6584,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131728894</v>
+        <v>131728892</v>
       </c>
       <c r="B60" t="n">
-        <v>91848</v>
+        <v>99089</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>695978</v>
+        <v>695888</v>
       </c>
       <c r="R60" t="n">
-        <v>6617240</v>
+        <v>6617156</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728892</v>
+        <v>131728900</v>
       </c>
       <c r="B61" t="n">
-        <v>99089</v>
+        <v>87250</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,21 +6692,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695888</v>
+        <v>696214</v>
       </c>
       <c r="R61" t="n">
-        <v>6617156</v>
+        <v>6617357</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -5711,10 +5711,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131728888</v>
+        <v>131728903</v>
       </c>
       <c r="B51" t="n">
-        <v>99089</v>
+        <v>97919</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>695741</v>
+        <v>696207</v>
       </c>
       <c r="R51" t="n">
-        <v>6617275</v>
+        <v>6617386</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5808,10 +5808,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131728903</v>
+        <v>131728888</v>
       </c>
       <c r="B52" t="n">
-        <v>97919</v>
+        <v>99089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696207</v>
+        <v>695741</v>
       </c>
       <c r="R52" t="n">
-        <v>6617386</v>
+        <v>6617275</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6099,10 +6099,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131728905</v>
+        <v>131728895</v>
       </c>
       <c r="B55" t="n">
-        <v>101260</v>
+        <v>8444</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6110,21 +6110,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696224</v>
+        <v>696026</v>
       </c>
       <c r="R55" t="n">
-        <v>6617389</v>
+        <v>6617277</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6196,10 +6196,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131728895</v>
+        <v>131728905</v>
       </c>
       <c r="B56" t="n">
-        <v>8444</v>
+        <v>101260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6207,21 +6207,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696026</v>
+        <v>696224</v>
       </c>
       <c r="R56" t="n">
-        <v>6617277</v>
+        <v>6617389</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131728892</v>
+        <v>131728900</v>
       </c>
       <c r="B60" t="n">
-        <v>99089</v>
+        <v>87250</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6595,21 +6595,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>695888</v>
+        <v>696214</v>
       </c>
       <c r="R60" t="n">
-        <v>6617156</v>
+        <v>6617357</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728900</v>
+        <v>131728892</v>
       </c>
       <c r="B61" t="n">
-        <v>87250</v>
+        <v>99089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,21 +6692,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696214</v>
+        <v>695888</v>
       </c>
       <c r="R61" t="n">
-        <v>6617357</v>
+        <v>6617156</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -5711,10 +5711,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131728903</v>
+        <v>131728888</v>
       </c>
       <c r="B51" t="n">
-        <v>97919</v>
+        <v>99089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696207</v>
+        <v>695741</v>
       </c>
       <c r="R51" t="n">
-        <v>6617386</v>
+        <v>6617275</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5808,10 +5808,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131728888</v>
+        <v>131728903</v>
       </c>
       <c r="B52" t="n">
-        <v>99089</v>
+        <v>97919</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>695741</v>
+        <v>696207</v>
       </c>
       <c r="R52" t="n">
-        <v>6617275</v>
+        <v>6617386</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6487,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131728894</v>
+        <v>131728892</v>
       </c>
       <c r="B59" t="n">
-        <v>91848</v>
+        <v>99089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695978</v>
+        <v>695888</v>
       </c>
       <c r="R59" t="n">
-        <v>6617240</v>
+        <v>6617156</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6584,32 +6584,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131728900</v>
+        <v>131728894</v>
       </c>
       <c r="B60" t="n">
-        <v>87250</v>
+        <v>91848</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>696214</v>
+        <v>695978</v>
       </c>
       <c r="R60" t="n">
-        <v>6617357</v>
+        <v>6617240</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728892</v>
+        <v>131728900</v>
       </c>
       <c r="B61" t="n">
-        <v>99089</v>
+        <v>87250</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,21 +6692,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695888</v>
+        <v>696214</v>
       </c>
       <c r="R61" t="n">
-        <v>6617156</v>
+        <v>6617357</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -5711,10 +5711,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131728888</v>
+        <v>131728903</v>
       </c>
       <c r="B51" t="n">
-        <v>99089</v>
+        <v>97919</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>695741</v>
+        <v>696207</v>
       </c>
       <c r="R51" t="n">
-        <v>6617275</v>
+        <v>6617386</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5808,10 +5808,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131728903</v>
+        <v>131728888</v>
       </c>
       <c r="B52" t="n">
-        <v>97919</v>
+        <v>99089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696207</v>
+        <v>695741</v>
       </c>
       <c r="R52" t="n">
-        <v>6617386</v>
+        <v>6617275</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6487,10 +6487,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131728892</v>
+        <v>131728900</v>
       </c>
       <c r="B59" t="n">
-        <v>99089</v>
+        <v>87250</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6498,21 +6498,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695888</v>
+        <v>696214</v>
       </c>
       <c r="R59" t="n">
-        <v>6617156</v>
+        <v>6617357</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728900</v>
+        <v>131728892</v>
       </c>
       <c r="B61" t="n">
-        <v>87250</v>
+        <v>99089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,21 +6692,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696214</v>
+        <v>695888</v>
       </c>
       <c r="R61" t="n">
-        <v>6617357</v>
+        <v>6617156</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>131728875</v>
       </c>
       <c r="B23" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>131728893</v>
       </c>
       <c r="B49" t="n">
-        <v>91341</v>
+        <v>91344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5711,10 +5711,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131728903</v>
+        <v>131728888</v>
       </c>
       <c r="B51" t="n">
-        <v>97960</v>
+        <v>99133</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696207</v>
+        <v>695741</v>
       </c>
       <c r="R51" t="n">
-        <v>6617386</v>
+        <v>6617275</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5808,10 +5808,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131728888</v>
+        <v>131728903</v>
       </c>
       <c r="B52" t="n">
-        <v>99130</v>
+        <v>97963</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>695741</v>
+        <v>696207</v>
       </c>
       <c r="R52" t="n">
-        <v>6617275</v>
+        <v>6617386</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6005,7 +6005,7 @@
         <v>131728904</v>
       </c>
       <c r="B54" t="n">
-        <v>99130</v>
+        <v>99133</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>131728905</v>
       </c>
       <c r="B56" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>131728889</v>
       </c>
       <c r="B57" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>131728883</v>
       </c>
       <c r="B58" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>131728894</v>
       </c>
       <c r="B59" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131728900</v>
+        <v>131728892</v>
       </c>
       <c r="B60" t="n">
-        <v>87291</v>
+        <v>99133</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6595,21 +6595,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>696214</v>
+        <v>695888</v>
       </c>
       <c r="R60" t="n">
-        <v>6617357</v>
+        <v>6617156</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728892</v>
+        <v>131728900</v>
       </c>
       <c r="B61" t="n">
-        <v>99130</v>
+        <v>87294</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,21 +6692,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695888</v>
+        <v>696214</v>
       </c>
       <c r="R61" t="n">
-        <v>6617156</v>
+        <v>6617357</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6781,7 +6781,7 @@
         <v>131728874</v>
       </c>
       <c r="B62" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>131728901</v>
       </c>
       <c r="B63" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>131728907</v>
       </c>
       <c r="B64" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -6487,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131728894</v>
+        <v>131728900</v>
       </c>
       <c r="B59" t="n">
-        <v>91892</v>
+        <v>87294</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695978</v>
+        <v>696214</v>
       </c>
       <c r="R59" t="n">
-        <v>6617240</v>
+        <v>6617357</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6681,32 +6681,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728900</v>
+        <v>131728894</v>
       </c>
       <c r="B61" t="n">
-        <v>87294</v>
+        <v>91892</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3674</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696214</v>
+        <v>695978</v>
       </c>
       <c r="R61" t="n">
-        <v>6617357</v>
+        <v>6617240</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -6099,10 +6099,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131728895</v>
+        <v>131728905</v>
       </c>
       <c r="B55" t="n">
-        <v>8444</v>
+        <v>101304</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6110,21 +6110,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696026</v>
+        <v>696224</v>
       </c>
       <c r="R55" t="n">
-        <v>6617277</v>
+        <v>6617389</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6196,10 +6196,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131728905</v>
+        <v>131728895</v>
       </c>
       <c r="B56" t="n">
-        <v>101304</v>
+        <v>8444</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6207,21 +6207,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696224</v>
+        <v>696026</v>
       </c>
       <c r="R56" t="n">
-        <v>6617389</v>
+        <v>6617277</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114979227</v>
+        <v>129939229</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hållvastby grustag, Upl</t>
+          <t>Ledinge, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>695999</v>
+        <v>695794</v>
       </c>
       <c r="R2" t="n">
         <v>6617333</v>
@@ -755,22 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Utbredd över flera dm2 på undersidan av granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,76 +766,74 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktor Lund, Lukas Bommelin, Martin Axegård</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114978574</v>
+        <v>129171363</v>
       </c>
       <c r="B3" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hållvastby grustag, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>695923</v>
+        <v>695974</v>
       </c>
       <c r="R3" t="n">
-        <v>6617459</v>
+        <v>6617238</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,77 +880,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktor Lund, Lukas Bommelin, Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326341</v>
+        <v>131728894</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hållvastby grustag (*knärot* /stjälk/), Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>695999</v>
+        <v>695978</v>
       </c>
       <c r="R4" t="n">
-        <v>6617334</v>
+        <v>6617240</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,24 +955,14 @@
           <t>Riala</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>AB-Nor-1895</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hållvastby grustag, Obskoord: 6617245/1650707/10 m ().</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,33 +971,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård, Lukas Bommelin, Viktor Lund</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171407</v>
+        <v>114979373</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>92564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,43 +1000,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hållvastby grustag, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695742</v>
+        <v>696034</v>
       </c>
       <c r="R5" t="n">
-        <v>6617264</v>
+        <v>6617396</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,12 +1055,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,29 +1079,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Lukas Bommelin, Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171415</v>
+        <v>131728899</v>
       </c>
       <c r="B6" t="n">
-        <v>86996</v>
+        <v>96410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,37 +1108,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696173</v>
+        <v>696172</v>
       </c>
       <c r="R6" t="n">
-        <v>6617344</v>
+        <v>6617338</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,12 +1162,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,65 +1182,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171368</v>
+        <v>129171371</v>
       </c>
       <c r="B7" t="n">
-        <v>57890</v>
+        <v>96458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695888</v>
+        <v>695971</v>
       </c>
       <c r="R7" t="n">
-        <v>6617461</v>
+        <v>6617182</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129174965</v>
+        <v>130210058</v>
       </c>
       <c r="B8" t="n">
-        <v>104227</v>
+        <v>97231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,37 +1302,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696247</v>
+        <v>695928</v>
       </c>
       <c r="R8" t="n">
-        <v>6617382</v>
+        <v>6617519</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,22 +1376,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171403</v>
+        <v>129171375</v>
       </c>
       <c r="B9" t="n">
-        <v>100945</v>
+        <v>91680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1399,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696219</v>
+        <v>695740</v>
       </c>
       <c r="R9" t="n">
-        <v>6617372</v>
+        <v>6617273</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129171408</v>
+        <v>129171376</v>
       </c>
       <c r="B10" t="n">
-        <v>8439</v>
+        <v>91680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,43 +1496,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>695749</v>
+        <v>695908</v>
       </c>
       <c r="R10" t="n">
-        <v>6617315</v>
+        <v>6617223</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1564,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1656,10 +1582,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129171360</v>
+        <v>129171377</v>
       </c>
       <c r="B11" t="n">
-        <v>91545</v>
+        <v>91680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,21 +1593,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1691,10 +1617,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>695791</v>
+        <v>696216</v>
       </c>
       <c r="R11" t="n">
-        <v>6617334</v>
+        <v>6617354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,10 +1679,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171404</v>
+        <v>131728889</v>
       </c>
       <c r="B12" t="n">
-        <v>8439</v>
+        <v>91745</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,46 +1690,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>3215</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695939</v>
+        <v>695742</v>
       </c>
       <c r="R12" t="n">
-        <v>6617438</v>
+        <v>6617273</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1744,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,29 +1758,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171405</v>
+        <v>131728901</v>
       </c>
       <c r="B13" t="n">
-        <v>8439</v>
+        <v>91745</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,46 +1787,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695875</v>
+        <v>696216</v>
       </c>
       <c r="R13" t="n">
-        <v>6617394</v>
+        <v>6617369</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1934,12 +1841,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1948,29 +1855,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171374</v>
+        <v>129171394</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>91361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,42 +1884,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>3286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696142</v>
+        <v>695956</v>
       </c>
       <c r="R14" t="n">
-        <v>6617341</v>
+        <v>6617156</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,6 +1952,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2072,64 +1971,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171392</v>
+        <v>131728893</v>
       </c>
       <c r="B15" t="n">
-        <v>98756</v>
+        <v>91426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>3286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695840</v>
+        <v>695933</v>
       </c>
       <c r="R15" t="n">
-        <v>6617459</v>
+        <v>6617193</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2153,12 +2036,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,65 +2050,51 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129174970</v>
+        <v>129171395</v>
       </c>
       <c r="B16" t="n">
-        <v>98756</v>
+        <v>87412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>3624</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696187</v>
+        <v>696012</v>
       </c>
       <c r="R16" t="n">
-        <v>6617372</v>
+        <v>6617292</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,65 +2153,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129171373</v>
+        <v>129171411</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>87309</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>695846</v>
+        <v>695740</v>
       </c>
       <c r="R17" t="n">
-        <v>6617165</v>
+        <v>6617275</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,10 +2262,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129171402</v>
+        <v>129171412</v>
       </c>
       <c r="B18" t="n">
-        <v>88829</v>
+        <v>87309</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,21 +2273,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4405</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695905</v>
+        <v>695978</v>
       </c>
       <c r="R18" t="n">
-        <v>6617158</v>
+        <v>6617179</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,10 +2359,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129171416</v>
+        <v>129171413</v>
       </c>
       <c r="B19" t="n">
-        <v>86996</v>
+        <v>87309</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,10 +2394,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696215</v>
+        <v>695981</v>
       </c>
       <c r="R19" t="n">
-        <v>6617356</v>
+        <v>6617228</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,10 +2456,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171385</v>
+        <v>129171414</v>
       </c>
       <c r="B20" t="n">
-        <v>98790</v>
+        <v>87309</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,21 +2467,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2630,10 +2491,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696217</v>
+        <v>696014</v>
       </c>
       <c r="R20" t="n">
-        <v>6617392</v>
+        <v>6617265</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,10 +2553,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171409</v>
+        <v>129171415</v>
       </c>
       <c r="B21" t="n">
-        <v>8439</v>
+        <v>87309</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,43 +2564,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696020</v>
+        <v>696173</v>
       </c>
       <c r="R21" t="n">
-        <v>6617274</v>
+        <v>6617344</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,7 +2632,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2799,57 +2650,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174969</v>
+        <v>129171416</v>
       </c>
       <c r="B22" t="n">
-        <v>98756</v>
+        <v>87309</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696014</v>
+        <v>696215</v>
       </c>
       <c r="R22" t="n">
-        <v>6617322</v>
+        <v>6617356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,29 +2729,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131728875</v>
+        <v>129171417</v>
       </c>
       <c r="B23" t="n">
-        <v>75423</v>
+        <v>87309</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,37 +2758,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695810</v>
+        <v>696217</v>
       </c>
       <c r="R23" t="n">
-        <v>6617339</v>
+        <v>6617368</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2974,12 +2812,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2994,22 +2832,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129171383</v>
+        <v>131728900</v>
       </c>
       <c r="B24" t="n">
-        <v>98790</v>
+        <v>87371</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3017,37 +2855,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695894</v>
+        <v>696214</v>
       </c>
       <c r="R24" t="n">
-        <v>6617351</v>
+        <v>6617357</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3071,12 +2909,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3091,60 +2929,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129171401</v>
+        <v>129171378</v>
       </c>
       <c r="B25" t="n">
-        <v>92899</v>
+        <v>93189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695690</v>
+        <v>695821</v>
       </c>
       <c r="R25" t="n">
-        <v>6617259</v>
+        <v>6617383</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,7 +3020,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3204,45 +3038,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129174972</v>
+        <v>129174966</v>
       </c>
       <c r="B26" t="n">
-        <v>75182</v>
+        <v>93189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695758</v>
+        <v>695824</v>
       </c>
       <c r="R26" t="n">
-        <v>6617314</v>
+        <v>6617390</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3283,6 +3120,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3301,10 +3139,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171367</v>
+        <v>131727962</v>
       </c>
       <c r="B27" t="n">
-        <v>57890</v>
+        <v>93271</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3312,45 +3150,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696155</v>
+        <v>695918</v>
       </c>
       <c r="R27" t="n">
-        <v>6617505</v>
+        <v>6617539</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3374,12 +3204,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Förmodligen dropptaggsvamp, men frusen så svårt att avgöra. Mycelmatta fanns.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3394,22 +3229,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129171386</v>
+        <v>129171402</v>
       </c>
       <c r="B28" t="n">
-        <v>58100</v>
+        <v>89143</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3417,21 +3252,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>4405</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3441,10 +3276,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696062</v>
+        <v>695905</v>
       </c>
       <c r="R28" t="n">
-        <v>6617338</v>
+        <v>6617158</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,47 +3338,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129171395</v>
+        <v>131727953</v>
       </c>
       <c r="B29" t="n">
-        <v>87099</v>
+        <v>91995</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3624</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696012</v>
+        <v>695816</v>
       </c>
       <c r="R29" t="n">
-        <v>6617292</v>
+        <v>6617457</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3567,12 +3403,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3581,29 +3417,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129171413</v>
+        <v>129171360</v>
       </c>
       <c r="B30" t="n">
-        <v>86996</v>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,21 +3446,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3674</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3635,10 +3470,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695981</v>
+        <v>695791</v>
       </c>
       <c r="R30" t="n">
-        <v>6617228</v>
+        <v>6617334</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3697,48 +3532,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129171363</v>
+        <v>131728877</v>
       </c>
       <c r="B31" t="n">
-        <v>91581</v>
+        <v>91937</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695974</v>
+        <v>695911</v>
       </c>
       <c r="R31" t="n">
-        <v>6617238</v>
+        <v>6617284</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3762,12 +3597,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3782,57 +3617,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129171414</v>
+        <v>129171401</v>
       </c>
       <c r="B32" t="n">
-        <v>86996</v>
+        <v>93233</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696014</v>
+        <v>695690</v>
       </c>
       <c r="R32" t="n">
-        <v>6617265</v>
+        <v>6617259</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3873,6 +3711,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3891,32 +3730,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129171371</v>
+        <v>129174968</v>
       </c>
       <c r="B33" t="n">
-        <v>96102</v>
+        <v>93235</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2818</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,10 +3765,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695971</v>
+        <v>696008</v>
       </c>
       <c r="R33" t="n">
-        <v>6617182</v>
+        <v>6617464</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3976,60 +3815,64 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129171412</v>
+        <v>131727954</v>
       </c>
       <c r="B34" t="n">
-        <v>86996</v>
+        <v>93309</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695978</v>
+        <v>695812</v>
       </c>
       <c r="R34" t="n">
-        <v>6617179</v>
+        <v>6617457</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4053,12 +3896,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4073,60 +3916,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129171375</v>
+        <v>131727959</v>
       </c>
       <c r="B35" t="n">
-        <v>91354</v>
+        <v>93309</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695740</v>
+        <v>695849</v>
       </c>
       <c r="R35" t="n">
-        <v>6617273</v>
+        <v>6617506</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4150,12 +3993,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4170,69 +4013,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129171406</v>
+        <v>131728879</v>
       </c>
       <c r="B36" t="n">
-        <v>8439</v>
+        <v>93309</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695870</v>
+        <v>696050</v>
       </c>
       <c r="R36" t="n">
-        <v>6617363</v>
+        <v>6617469</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4256,12 +4090,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4270,83 +4104,70 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129171391</v>
+        <v>131728882</v>
       </c>
       <c r="B37" t="n">
-        <v>98756</v>
+        <v>93309</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695872</v>
+        <v>696010</v>
       </c>
       <c r="R37" t="n">
-        <v>6617462</v>
+        <v>6617472</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4370,12 +4191,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4384,67 +4205,66 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129171394</v>
+        <v>131727955</v>
       </c>
       <c r="B38" t="n">
-        <v>91042</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3286</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695956</v>
+        <v>695828</v>
       </c>
       <c r="R38" t="n">
-        <v>6617156</v>
+        <v>6617459</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4468,12 +4288,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4482,80 +4302,63 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129171393</v>
+        <v>129174972</v>
       </c>
       <c r="B39" t="n">
-        <v>98756</v>
+        <v>75428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695996</v>
+        <v>695758</v>
       </c>
       <c r="R39" t="n">
-        <v>6617333</v>
+        <v>6617314</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4596,67 +4399,66 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129171377</v>
+        <v>131728875</v>
       </c>
       <c r="B40" t="n">
-        <v>91354</v>
+        <v>75468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3215</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696216</v>
+        <v>695810</v>
       </c>
       <c r="R40" t="n">
-        <v>6617354</v>
+        <v>6617339</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4680,12 +4482,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4700,60 +4502,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129171411</v>
+        <v>131727947</v>
       </c>
       <c r="B41" t="n">
-        <v>86996</v>
+        <v>75468</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695740</v>
+        <v>695684</v>
       </c>
       <c r="R41" t="n">
-        <v>6617275</v>
+        <v>6617302</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4777,12 +4579,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4797,22 +4599,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129171384</v>
+        <v>129171373</v>
       </c>
       <c r="B42" t="n">
-        <v>98790</v>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4820,34 +4622,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695740</v>
+        <v>695846</v>
       </c>
       <c r="R42" t="n">
-        <v>6617273</v>
+        <v>6617165</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4906,45 +4716,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129171369</v>
+        <v>129171374</v>
       </c>
       <c r="B43" t="n">
-        <v>57890</v>
+        <v>57950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695729</v>
+        <v>696142</v>
       </c>
       <c r="R43" t="n">
-        <v>6617282</v>
+        <v>6617341</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5003,10 +4821,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129171382</v>
+        <v>114978574</v>
       </c>
       <c r="B44" t="n">
-        <v>98790</v>
+        <v>57141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5014,38 +4832,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hållvastby grustag, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695889</v>
+        <v>695923</v>
       </c>
       <c r="R44" t="n">
-        <v>6617161</v>
+        <v>6617459</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5072,12 +4894,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5086,51 +4918,50 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Lukas Bommelin, Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129171379</v>
+        <v>129171386</v>
       </c>
       <c r="B45" t="n">
-        <v>86984</v>
+        <v>58327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003296</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +4971,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696222</v>
+        <v>696062</v>
       </c>
       <c r="R45" t="n">
-        <v>6617388</v>
+        <v>6617338</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5184,7 +5015,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5203,10 +5033,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129171378</v>
+        <v>129171367</v>
       </c>
       <c r="B46" t="n">
-        <v>92855</v>
+        <v>58114</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5214,34 +5044,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695821</v>
+        <v>696155</v>
       </c>
       <c r="R46" t="n">
-        <v>6617383</v>
+        <v>6617505</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5300,45 +5138,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129171417</v>
+        <v>129171368</v>
       </c>
       <c r="B47" t="n">
-        <v>86996</v>
+        <v>58114</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696217</v>
+        <v>695888</v>
       </c>
       <c r="R47" t="n">
-        <v>6617368</v>
+        <v>6617461</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5397,10 +5243,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129939229</v>
+        <v>129171369</v>
       </c>
       <c r="B48" t="n">
-        <v>91679</v>
+        <v>58114</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5408,41 +5254,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>112</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ledinge, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>695794</v>
+        <v>695729</v>
       </c>
       <c r="R48" t="n">
-        <v>6617333</v>
+        <v>6617282</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,17 +5308,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Utbredd över flera dm2 på undersidan av granlåga</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5488,77 +5322,75 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AV48" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131728893</v>
+        <v>129171404</v>
       </c>
       <c r="B49" t="n">
-        <v>91344</v>
+        <v>8444</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3286</v>
+        <v>106554</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>695933</v>
+        <v>695939</v>
       </c>
       <c r="R49" t="n">
-        <v>6617193</v>
+        <v>6617438</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5582,12 +5414,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5596,25 +5428,26 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131728890</v>
+        <v>129171405</v>
       </c>
       <c r="B50" t="n">
         <v>8444</v>
@@ -5643,19 +5476,28 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>695745</v>
+        <v>695875</v>
       </c>
       <c r="R50" t="n">
-        <v>6617268</v>
+        <v>6617394</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5679,12 +5521,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5693,28 +5535,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131728888</v>
+        <v>129171406</v>
       </c>
       <c r="B51" t="n">
-        <v>99133</v>
+        <v>8444</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5722,37 +5565,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>695741</v>
+        <v>695870</v>
       </c>
       <c r="R51" t="n">
-        <v>6617275</v>
+        <v>6617363</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5776,12 +5628,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5790,28 +5642,29 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131728903</v>
+        <v>129171407</v>
       </c>
       <c r="B52" t="n">
-        <v>97963</v>
+        <v>8444</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5819,37 +5672,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696207</v>
+        <v>695742</v>
       </c>
       <c r="R52" t="n">
-        <v>6617386</v>
+        <v>6617264</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5873,12 +5735,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5887,25 +5749,26 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131728873</v>
+        <v>129171408</v>
       </c>
       <c r="B53" t="n">
         <v>8444</v>
@@ -5934,19 +5797,28 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>695750</v>
+        <v>695749</v>
       </c>
       <c r="R53" t="n">
         <v>6617315</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5970,12 +5842,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5984,28 +5856,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131728904</v>
+        <v>129171409</v>
       </c>
       <c r="B54" t="n">
-        <v>99133</v>
+        <v>8444</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6013,37 +5886,46 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696216</v>
+        <v>696020</v>
       </c>
       <c r="R54" t="n">
-        <v>6617396</v>
+        <v>6617274</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6067,12 +5949,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6081,28 +5963,29 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131728905</v>
+        <v>131728873</v>
       </c>
       <c r="B55" t="n">
-        <v>101304</v>
+        <v>8449</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6110,21 +5993,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6134,10 +6017,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696224</v>
+        <v>695750</v>
       </c>
       <c r="R55" t="n">
-        <v>6617389</v>
+        <v>6617315</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6196,10 +6079,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131728895</v>
+        <v>131728890</v>
       </c>
       <c r="B56" t="n">
-        <v>8444</v>
+        <v>8449</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6231,10 +6114,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696026</v>
+        <v>695745</v>
       </c>
       <c r="R56" t="n">
-        <v>6617277</v>
+        <v>6617268</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6293,10 +6176,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131728889</v>
+        <v>131728895</v>
       </c>
       <c r="B57" t="n">
-        <v>91663</v>
+        <v>8449</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6304,21 +6187,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3215</v>
+        <v>106554</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6328,10 +6211,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>695742</v>
+        <v>696026</v>
       </c>
       <c r="R57" t="n">
-        <v>6617273</v>
+        <v>6617277</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6390,10 +6273,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131728883</v>
+        <v>129171381</v>
       </c>
       <c r="B58" t="n">
-        <v>97963</v>
+        <v>99153</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6401,37 +6284,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>695877</v>
+        <v>695910</v>
       </c>
       <c r="R58" t="n">
-        <v>6617367</v>
+        <v>6617222</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6455,12 +6342,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6469,28 +6356,29 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131728900</v>
+        <v>129171382</v>
       </c>
       <c r="B59" t="n">
-        <v>87294</v>
+        <v>99153</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6498,37 +6386,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696214</v>
+        <v>695889</v>
       </c>
       <c r="R59" t="n">
-        <v>6617357</v>
+        <v>6617161</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6552,12 +6444,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6566,28 +6458,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131728892</v>
+        <v>129171383</v>
       </c>
       <c r="B60" t="n">
-        <v>99133</v>
+        <v>99153</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6615,17 +6508,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>695888</v>
+        <v>695894</v>
       </c>
       <c r="R60" t="n">
-        <v>6617156</v>
+        <v>6617351</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6649,12 +6542,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6669,60 +6562,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131728894</v>
+        <v>129171384</v>
       </c>
       <c r="B61" t="n">
-        <v>91892</v>
+        <v>99153</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695978</v>
+        <v>695740</v>
       </c>
       <c r="R61" t="n">
-        <v>6617240</v>
+        <v>6617273</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6746,12 +6639,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6766,60 +6659,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131728874</v>
+        <v>129171385</v>
       </c>
       <c r="B62" t="n">
-        <v>99098</v>
+        <v>99153</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>695873</v>
+        <v>696217</v>
       </c>
       <c r="R62" t="n">
-        <v>6617461</v>
+        <v>6617392</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6843,12 +6736,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6863,22 +6756,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131728901</v>
+        <v>131728886</v>
       </c>
       <c r="B63" t="n">
-        <v>91663</v>
+        <v>99230</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6886,21 +6779,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6910,10 +6803,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696216</v>
+        <v>695853</v>
       </c>
       <c r="R63" t="n">
-        <v>6617369</v>
+        <v>6617248</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6972,10 +6865,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131728907</v>
+        <v>131728888</v>
       </c>
       <c r="B64" t="n">
-        <v>97963</v>
+        <v>99230</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6983,21 +6876,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7007,10 +6900,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>696238</v>
+        <v>695741</v>
       </c>
       <c r="R64" t="n">
-        <v>6617405</v>
+        <v>6617275</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7066,6 +6959,2172 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131728892</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99230</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>695888</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6617156</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131728904</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99230</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>696216</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6617396</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>131728906</v>
+      </c>
+      <c r="B67" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>696245</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6617382</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>114979227</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hållvastby grustag, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>695999</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6617333</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Lukas Bommelin, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>121326341</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hållvastby grustag (*knärot* /stjälk/), Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>695999</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6617334</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>AB-Nor-1895</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hållvastby grustag, Obskoord: 6617245/1650707/10 m ().</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Martin Axegård, Lukas Bommelin, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129171391</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>695872</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6617462</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129171392</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>695840</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6617459</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129171393</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>695996</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6617333</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129174969</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>696014</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6617322</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129174970</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>696187</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6617372</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131727945</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>695657</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6617293</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>131728874</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>695873</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6617461</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>131728883</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>695877</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6617367</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>131728896</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>696076</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6617305</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>131728897</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>696117</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6617310</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>131728903</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>696207</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6617386</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>131728907</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>696238</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6617405</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129174965</v>
+      </c>
+      <c r="B82" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>696247</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6617382</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129171403</v>
+      </c>
+      <c r="B83" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>696219</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6617372</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>131728905</v>
+      </c>
+      <c r="B84" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>696224</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6617389</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129171379</v>
+      </c>
+      <c r="B85" t="n">
+        <v>87297</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6003296</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Stor odörspindling</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Cortinarius mussivus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>696222</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6617388</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25731-2025 artfynd.xlsx
+++ b/artfynd/A 25731-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AZ85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129939229</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171363</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728894</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114979373</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728899</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171371</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210058</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,6 +1522,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171375</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1579,6 +1624,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171376</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1676,6 +1726,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171377</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1773,6 +1828,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728889</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1870,6 +1930,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728901</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171394</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2065,6 +2135,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728893</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171395</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171411</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2356,6 +2441,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171412</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2453,6 +2543,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171413</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2550,6 +2645,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171414</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2647,6 +2747,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171415</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2744,6 +2849,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171416</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2841,6 +2951,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171417</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2938,6 +3053,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728900</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3035,6 +3155,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171378</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3136,6 +3261,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174966</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3238,6 +3368,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131727962</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3335,6 +3470,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171402</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3432,6 +3572,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131727953</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3529,6 +3674,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171360</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3626,6 +3776,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728877</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3727,6 +3882,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171401</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3824,6 +3984,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174968</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3925,6 +4090,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131727954</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4022,6 +4192,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131727959</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4119,6 +4294,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728879</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4220,6 +4400,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728882</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4317,6 +4502,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131727955</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4414,6 +4604,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174972</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4511,6 +4706,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728875</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4608,6 +4808,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131727947</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4713,6 +4918,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171373</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4818,6 +5028,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171374</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4933,6 +5148,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114978574</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5030,6 +5250,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171386</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5135,6 +5360,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171367</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5240,6 +5470,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171368</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5337,6 +5572,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171369</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5444,6 +5684,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171404</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5551,6 +5796,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171405</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5658,6 +5908,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171406</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5765,6 +6020,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171407</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5872,6 +6132,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171408</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5979,6 +6244,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171409</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6076,6 +6346,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728873</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6173,6 +6448,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728890</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6270,6 +6550,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728895</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6372,6 +6657,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171381</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6474,6 +6764,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171382</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6571,6 +6866,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171383</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6668,6 +6968,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171384</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6765,6 +7070,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171385</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6862,6 +7172,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728886</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6959,6 +7274,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728888</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7056,6 +7376,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728892</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7153,6 +7478,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728904</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7250,6 +7580,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728906</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7367,6 +7702,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114979227</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7491,6 +7831,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121326341</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7605,6 +7950,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171391</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7719,6 +8069,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171392</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7833,6 +8188,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171393</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7943,6 +8303,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174969</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8053,6 +8418,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174970</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8154,6 +8524,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131727945</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8251,6 +8626,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728874</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8348,6 +8728,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728883</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8445,6 +8830,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728896</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8542,6 +8932,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728897</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8639,6 +9034,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728903</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8736,6 +9136,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728907</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8833,6 +9238,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174965</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8930,6 +9340,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171403</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9027,6 +9442,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728905</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9125,8 +9545,99 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171379</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>